--- a/eBike_controller/Results.xlsx
+++ b/eBike_controller/Results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrea/Documents/GitHub/HECATE-Bikes/Replication_Package/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrea/Documents/GitHub/HECATE_BikeAndDrone/eBike_controller/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2863260D-D530-5448-960E-794E30FECBC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21180B4-1CD2-F243-8528-1A4F8C19F792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="117">
   <si>
     <t>SA_TALIRO</t>
   </si>
@@ -371,20 +371,46 @@
   </si>
   <si>
     <t>Lower Wisker</t>
+  </si>
+  <si>
+    <t>REQ_4</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>BUCK R4</t>
+  </si>
+  <si>
+    <t>PWM R4</t>
+  </si>
+  <si>
+    <t>Buck R4</t>
+  </si>
+  <si>
+    <t>1.4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -617,17 +643,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -654,7 +680,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -679,7 +705,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -694,13 +720,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -709,77 +735,38 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -790,26 +777,140 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1085,131 +1186,169 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:AH23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="1.6640625" customWidth="1"/>
     <col min="7" max="7" width="1" customWidth="1"/>
-    <col min="11" max="11" width="1" customWidth="1"/>
-    <col min="19" max="19" width="1.33203125" customWidth="1"/>
-    <col min="23" max="23" width="1.5" customWidth="1"/>
+    <col min="11" max="11" width="0.83203125" style="79" customWidth="1"/>
+    <col min="15" max="15" width="1" customWidth="1"/>
+    <col min="23" max="23" width="1.33203125" customWidth="1"/>
+    <col min="27" max="27" width="0.6640625" style="79" customWidth="1"/>
+    <col min="31" max="31" width="1.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1" s="53" t="s">
+    <row r="1" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="P1" s="53" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="T1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-      <c r="Y1" s="53"/>
-      <c r="Z1" s="53"/>
-    </row>
-    <row r="2" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="53"/>
-      <c r="X2" s="53"/>
-      <c r="Y2" s="53"/>
-      <c r="Z2" s="53"/>
-    </row>
-    <row r="3" spans="1:26" ht="16" x14ac:dyDescent="0.2">
-      <c r="D3" s="47" t="s">
+      <c r="U1" s="44"/>
+      <c r="V1" s="44"/>
+      <c r="W1" s="44"/>
+      <c r="X1" s="44"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="44"/>
+      <c r="AA1" s="44"/>
+      <c r="AB1" s="44"/>
+      <c r="AC1" s="44"/>
+      <c r="AD1" s="44"/>
+      <c r="AE1" s="44"/>
+      <c r="AF1" s="44"/>
+      <c r="AG1" s="44"/>
+      <c r="AH1" s="44"/>
+    </row>
+    <row r="2" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="44"/>
+      <c r="V2" s="44"/>
+      <c r="W2" s="44"/>
+      <c r="X2" s="44"/>
+      <c r="Y2" s="44"/>
+      <c r="Z2" s="44"/>
+      <c r="AA2" s="44"/>
+      <c r="AB2" s="44"/>
+      <c r="AC2" s="44"/>
+      <c r="AD2" s="44"/>
+      <c r="AE2" s="44"/>
+      <c r="AF2" s="44"/>
+      <c r="AG2" s="44"/>
+      <c r="AH2" s="44"/>
+    </row>
+    <row r="3" spans="1:34" ht="16" x14ac:dyDescent="0.2">
+      <c r="D3" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="48"/>
-      <c r="F3" s="49"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="56"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="47" t="s">
+      <c r="H3" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="48"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="47" t="s">
+      <c r="I3" s="55"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="48"/>
-      <c r="N3" s="49"/>
-      <c r="P3" s="47" t="s">
+      <c r="M3" s="55"/>
+      <c r="N3" s="56"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q3" s="55"/>
+      <c r="R3" s="56"/>
+      <c r="T3" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="47" t="s">
+      <c r="U3" s="55"/>
+      <c r="V3" s="56"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="48"/>
-      <c r="V3" s="49"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="47" t="s">
+      <c r="Y3" s="55"/>
+      <c r="Z3" s="56"/>
+      <c r="AA3" s="84"/>
+      <c r="AB3" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="Y3" s="48"/>
-      <c r="Z3" s="49"/>
-    </row>
-    <row r="4" spans="1:26" ht="16" x14ac:dyDescent="0.2">
-      <c r="D4" s="50"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="52"/>
+      <c r="AC3" s="55"/>
+      <c r="AD3" s="56"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG3" s="72"/>
+      <c r="AH3" s="73"/>
+    </row>
+    <row r="4" spans="1:34" ht="16" x14ac:dyDescent="0.2">
+      <c r="D4" s="57"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="59"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="51"/>
-      <c r="N4" s="52"/>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="51"/>
-      <c r="R4" s="52"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="51"/>
-      <c r="V4" s="52"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="57"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="59"/>
+      <c r="T4" s="57"/>
+      <c r="U4" s="58"/>
+      <c r="V4" s="59"/>
       <c r="W4" s="3"/>
-      <c r="X4" s="50"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="52"/>
-    </row>
-    <row r="5" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+      <c r="X4" s="57"/>
+      <c r="Y4" s="58"/>
+      <c r="Z4" s="59"/>
+      <c r="AA4" s="84"/>
+      <c r="AB4" s="57"/>
+      <c r="AC4" s="58"/>
+      <c r="AD4" s="59"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="74"/>
+      <c r="AG4" s="75"/>
+      <c r="AH4" s="76"/>
+    </row>
+    <row r="5" spans="1:34" ht="16" x14ac:dyDescent="0.2">
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
@@ -1217,14 +1356,14 @@
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
-      <c r="K5" s="3"/>
+      <c r="K5" s="77"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
+      <c r="O5" s="3"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
-      <c r="S5" s="3"/>
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
@@ -1232,8 +1371,16 @@
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
-    </row>
-    <row r="6" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+      <c r="AA5" s="77"/>
+      <c r="AB5" s="4"/>
+      <c r="AC5" s="4"/>
+      <c r="AD5" s="4"/>
+      <c r="AE5" s="3"/>
+      <c r="AF5" s="77"/>
+      <c r="AG5" s="77"/>
+      <c r="AH5" s="77"/>
+    </row>
+    <row r="6" spans="1:34" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
@@ -1259,7 +1406,7 @@
       <c r="J6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="3"/>
+      <c r="K6" s="84"/>
       <c r="L6" s="5" t="s">
         <v>7</v>
       </c>
@@ -1269,6 +1416,7 @@
       <c r="N6" s="5" t="s">
         <v>9</v>
       </c>
+      <c r="O6" s="3"/>
       <c r="P6" s="5" t="s">
         <v>7</v>
       </c>
@@ -1278,7 +1426,6 @@
       <c r="R6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="S6" s="3"/>
       <c r="T6" s="5" t="s">
         <v>7</v>
       </c>
@@ -1298,12 +1445,35 @@
       <c r="Z6" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+      <c r="AA6" s="84"/>
+      <c r="AB6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="78" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG6" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH6" s="78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4"/>
-    </row>
-    <row r="8" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="44" t="s">
+      <c r="AF7" s="79"/>
+      <c r="AG7" s="79"/>
+      <c r="AH7" s="79"/>
+    </row>
+    <row r="8" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="60" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1328,7 +1498,7 @@
       <c r="J8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K8" s="9"/>
+      <c r="K8" s="87"/>
       <c r="L8" s="11" t="s">
         <v>12</v>
       </c>
@@ -1338,38 +1508,46 @@
       <c r="N8" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="P8" s="11" t="s">
+      <c r="O8" s="9"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="68"/>
+      <c r="T8" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Q8" s="12" t="s">
+      <c r="U8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="R8" s="12" t="s">
+      <c r="V8" s="12" t="s">
         <v>17</v>
-      </c>
-      <c r="S8" s="9"/>
-      <c r="T8" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="U8" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="V8" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="W8" s="9"/>
       <c r="X8" s="13" t="s">
         <v>12</v>
       </c>
       <c r="Y8" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z8" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA8" s="85"/>
+      <c r="AB8" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC8" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="Z8" s="13" t="s">
+      <c r="AD8" s="13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="45"/>
+      <c r="AE8" s="9"/>
+      <c r="AF8" s="80"/>
+      <c r="AG8" s="80"/>
+      <c r="AH8" s="80"/>
+    </row>
+    <row r="9" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="61"/>
       <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
@@ -1392,7 +1570,7 @@
       <c r="J9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="9"/>
+      <c r="K9" s="88"/>
       <c r="L9" s="11" t="s">
         <v>12</v>
       </c>
@@ -1402,38 +1580,46 @@
       <c r="N9" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="P9" s="13" t="s">
+      <c r="O9" s="9"/>
+      <c r="P9" s="66"/>
+      <c r="Q9" s="68"/>
+      <c r="R9" s="68"/>
+      <c r="T9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="Q9" s="13" t="s">
+      <c r="U9" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="R9" s="13" t="s">
+      <c r="V9" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="S9" s="9"/>
-      <c r="T9" s="16" t="s">
+      <c r="W9" s="9"/>
+      <c r="X9" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="U9" s="17" t="s">
+      <c r="Y9" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="V9" s="16" t="s">
+      <c r="Z9" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="W9" s="9"/>
-      <c r="X9" s="13" t="s">
+      <c r="AA9" s="85"/>
+      <c r="AB9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="Y9" s="13" t="s">
+      <c r="AC9" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="Z9" s="13" t="s">
+      <c r="AD9" s="13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="45"/>
+      <c r="AE9" s="9"/>
+      <c r="AF9" s="80"/>
+      <c r="AG9" s="80"/>
+      <c r="AH9" s="80"/>
+    </row>
+    <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="61"/>
       <c r="B10" s="2" t="s">
         <v>27</v>
       </c>
@@ -1456,7 +1642,7 @@
       <c r="J10" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K10" s="9"/>
+      <c r="K10" s="89"/>
       <c r="L10" s="11" t="s">
         <v>12</v>
       </c>
@@ -1466,38 +1652,46 @@
       <c r="N10" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="P10" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q10" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="R10" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="S10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="66"/>
+      <c r="Q10" s="68"/>
+      <c r="R10" s="68"/>
       <c r="T10" s="13" t="s">
         <v>12</v>
       </c>
       <c r="U10" s="13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="V10" s="13" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="W10" s="9"/>
       <c r="X10" s="13" t="s">
         <v>12</v>
       </c>
       <c r="Y10" s="13" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="Z10" s="13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="45"/>
+      <c r="AA10" s="85"/>
+      <c r="AB10" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC10" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD10" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE10" s="9"/>
+      <c r="AF10" s="80"/>
+      <c r="AG10" s="80"/>
+      <c r="AH10" s="80"/>
+    </row>
+    <row r="11" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="61"/>
       <c r="B11" s="2"/>
       <c r="D11" s="9"/>
       <c r="E11" s="10"/>
@@ -1506,14 +1700,14 @@
       <c r="H11" s="9"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
-      <c r="K11" s="9"/>
+      <c r="K11" s="70"/>
       <c r="L11" s="9"/>
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="69"/>
+      <c r="Q11" s="70"/>
+      <c r="R11" s="70"/>
       <c r="T11" s="9"/>
       <c r="U11" s="10"/>
       <c r="V11" s="10"/>
@@ -1521,9 +1715,17 @@
       <c r="X11" s="9"/>
       <c r="Y11" s="10"/>
       <c r="Z11" s="10"/>
-    </row>
-    <row r="12" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="45"/>
+      <c r="AA11" s="70"/>
+      <c r="AB11" s="9"/>
+      <c r="AC11" s="10"/>
+      <c r="AD11" s="10"/>
+      <c r="AE11" s="9"/>
+      <c r="AF11" s="69"/>
+      <c r="AG11" s="70"/>
+      <c r="AH11" s="70"/>
+    </row>
+    <row r="12" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="61"/>
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
@@ -1546,7 +1748,7 @@
       <c r="J12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="9"/>
+      <c r="K12" s="89"/>
       <c r="L12" s="11" t="s">
         <v>12</v>
       </c>
@@ -1556,38 +1758,46 @@
       <c r="N12" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="P12" s="16" t="s">
+      <c r="O12" s="9"/>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="68"/>
+      <c r="R12" s="68"/>
+      <c r="T12" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="Q12" s="17" t="s">
+      <c r="U12" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="R12" s="16" t="s">
+      <c r="V12" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="S12" s="9"/>
-      <c r="T12" s="13" t="s">
+      <c r="W12" s="9"/>
+      <c r="X12" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="U12" s="13" t="s">
+      <c r="Y12" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="V12" s="13" t="s">
+      <c r="Z12" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="W12" s="9"/>
-      <c r="X12" s="16" t="s">
+      <c r="AA12" s="85"/>
+      <c r="AB12" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="Y12" s="16" t="s">
+      <c r="AC12" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="Z12" s="16" t="s">
+      <c r="AD12" s="16" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="45"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="80"/>
+      <c r="AG12" s="80"/>
+      <c r="AH12" s="80"/>
+    </row>
+    <row r="13" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="61"/>
       <c r="B13" s="2" t="s">
         <v>42</v>
       </c>
@@ -1610,7 +1820,7 @@
       <c r="J13" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="K13" s="9"/>
+      <c r="K13" s="89"/>
       <c r="L13" s="11" t="s">
         <v>12</v>
       </c>
@@ -1620,38 +1830,46 @@
       <c r="N13" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="P13" s="11" t="s">
+      <c r="O13" s="9"/>
+      <c r="P13" s="66"/>
+      <c r="Q13" s="68"/>
+      <c r="R13" s="68"/>
+      <c r="T13" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Q13" s="12" t="s">
+      <c r="U13" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="R13" s="12" t="s">
+      <c r="V13" s="12" t="s">
         <v>35</v>
-      </c>
-      <c r="S13" s="9"/>
-      <c r="T13" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="U13" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="V13" s="13" t="s">
-        <v>47</v>
       </c>
       <c r="W13" s="9"/>
       <c r="X13" s="13" t="s">
         <v>12</v>
       </c>
       <c r="Y13" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z13" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA13" s="85"/>
+      <c r="AB13" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC13" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="Z13" s="13" t="s">
+      <c r="AD13" s="13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="46"/>
+      <c r="AE13" s="9"/>
+      <c r="AF13" s="80"/>
+      <c r="AG13" s="80"/>
+      <c r="AH13" s="80"/>
+    </row>
+    <row r="14" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="62"/>
       <c r="B14" s="2" t="s">
         <v>48</v>
       </c>
@@ -1674,7 +1892,7 @@
       <c r="J14" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="K14" s="9"/>
+      <c r="K14" s="88"/>
       <c r="L14" s="11" t="s">
         <v>12</v>
       </c>
@@ -1684,37 +1902,45 @@
       <c r="N14" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="P14" s="16" t="s">
+      <c r="O14" s="9"/>
+      <c r="P14" s="66"/>
+      <c r="Q14" s="68"/>
+      <c r="R14" s="68"/>
+      <c r="T14" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="Q14" s="17" t="s">
+      <c r="U14" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="R14" s="16" t="s">
+      <c r="V14" s="16" t="s">
         <v>20</v>
-      </c>
-      <c r="S14" s="9"/>
-      <c r="T14" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="U14" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="V14" s="13" t="s">
-        <v>14</v>
       </c>
       <c r="W14" s="9"/>
       <c r="X14" s="13" t="s">
         <v>12</v>
       </c>
       <c r="Y14" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z14" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA14" s="85"/>
+      <c r="AB14" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC14" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="Z14" s="13" t="s">
+      <c r="AD14" s="13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+      <c r="AE14" s="9"/>
+      <c r="AF14" s="80"/>
+      <c r="AG14" s="80"/>
+      <c r="AH14" s="80"/>
+    </row>
+    <row r="15" spans="1:34" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
       <c r="D15" s="9"/>
       <c r="E15" s="10"/>
@@ -1723,14 +1949,14 @@
       <c r="H15" s="9"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
-      <c r="K15" s="9"/>
+      <c r="K15" s="70"/>
       <c r="L15" s="9"/>
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="69"/>
+      <c r="Q15" s="70"/>
+      <c r="R15" s="70"/>
       <c r="T15" s="9"/>
       <c r="U15" s="10"/>
       <c r="V15" s="10"/>
@@ -1738,8 +1964,16 @@
       <c r="X15" s="9"/>
       <c r="Y15" s="10"/>
       <c r="Z15" s="10"/>
-    </row>
-    <row r="16" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+      <c r="AA15" s="70"/>
+      <c r="AB15" s="9"/>
+      <c r="AC15" s="10"/>
+      <c r="AD15" s="10"/>
+      <c r="AE15" s="9"/>
+      <c r="AF15" s="69"/>
+      <c r="AG15" s="70"/>
+      <c r="AH15" s="70"/>
+    </row>
+    <row r="16" spans="1:34" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
       <c r="D16" s="9"/>
       <c r="E16" s="10"/>
@@ -1748,14 +1982,14 @@
       <c r="H16" s="9"/>
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
-      <c r="K16" s="9"/>
+      <c r="K16" s="70"/>
       <c r="L16" s="9"/>
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="69"/>
+      <c r="Q16" s="70"/>
+      <c r="R16" s="70"/>
       <c r="T16" s="9"/>
       <c r="U16" s="10"/>
       <c r="V16" s="10"/>
@@ -1763,9 +1997,17 @@
       <c r="X16" s="9"/>
       <c r="Y16" s="10"/>
       <c r="Z16" s="10"/>
-    </row>
-    <row r="17" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="44" t="s">
+      <c r="AA16" s="70"/>
+      <c r="AB16" s="9"/>
+      <c r="AC16" s="10"/>
+      <c r="AD16" s="10"/>
+      <c r="AE16" s="9"/>
+      <c r="AF16" s="69"/>
+      <c r="AG16" s="70"/>
+      <c r="AH16" s="70"/>
+    </row>
+    <row r="17" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="60" t="s">
         <v>54</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -1786,7 +2028,7 @@
       <c r="J17" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K17" s="9"/>
+      <c r="K17" s="88"/>
       <c r="L17" s="6" t="s">
         <v>12</v>
       </c>
@@ -1796,34 +2038,54 @@
       <c r="N17" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="P17" s="13" t="s">
+      <c r="O17" s="9"/>
+      <c r="P17" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q17" s="81" t="s">
+        <v>77</v>
+      </c>
+      <c r="R17" s="81" t="s">
+        <v>17</v>
+      </c>
+      <c r="T17" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="U17" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="V17" s="14" t="s">
-        <v>61</v>
-      </c>
+      <c r="U17" s="13"/>
+      <c r="V17" s="13"/>
       <c r="W17" s="9"/>
       <c r="X17" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y17" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z17" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA17" s="86"/>
+      <c r="AB17" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="Y17" s="14" t="s">
+      <c r="AC17" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="Z17" s="14" t="s">
+      <c r="AD17" s="14" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="45"/>
+      <c r="AE17" s="9"/>
+      <c r="AF17" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG17" s="81" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH17" s="81" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="61"/>
       <c r="B18" s="2" t="s">
         <v>22</v>
       </c>
@@ -1842,7 +2104,7 @@
       <c r="J18" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K18" s="9"/>
+      <c r="K18" s="87"/>
       <c r="L18" s="6" t="s">
         <v>12</v>
       </c>
@@ -1852,34 +2114,54 @@
       <c r="N18" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="P18" s="13" t="s">
+      <c r="O18" s="9"/>
+      <c r="P18" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R18" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="T18" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="U18" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="V18" s="13" t="s">
-        <v>68</v>
-      </c>
+      <c r="U18" s="13"/>
+      <c r="V18" s="13"/>
       <c r="W18" s="9"/>
       <c r="X18" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y18" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z18" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA18" s="85"/>
+      <c r="AB18" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="Y18" s="13" t="s">
+      <c r="AC18" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="Z18" s="13" t="s">
+      <c r="AD18" s="13" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="45"/>
+      <c r="AE18" s="9"/>
+      <c r="AF18" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG18" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH18" s="68" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="61"/>
       <c r="B19" s="2" t="s">
         <v>27</v>
       </c>
@@ -1898,7 +2180,7 @@
       <c r="J19" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="K19" s="9"/>
+      <c r="K19" s="89"/>
       <c r="L19" s="11" t="s">
         <v>12</v>
       </c>
@@ -1908,34 +2190,54 @@
       <c r="N19" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="P19" s="13" t="s">
+      <c r="O19" s="9"/>
+      <c r="P19" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q19" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R19" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="T19" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="16" t="s">
+      <c r="U19" s="13"/>
+      <c r="V19" s="13"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="U19" s="16" t="s">
+      <c r="Y19" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="V19" s="16" t="s">
+      <c r="Z19" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="W19" s="9"/>
-      <c r="X19" s="13" t="s">
+      <c r="AA19" s="85"/>
+      <c r="AB19" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="Y19" s="13" t="s">
+      <c r="AC19" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="Z19" s="13" t="s">
+      <c r="AD19" s="13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="45"/>
+      <c r="AE19" s="9"/>
+      <c r="AF19" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG19" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH19" s="68" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="61"/>
       <c r="B20" s="2"/>
       <c r="D20" s="9"/>
       <c r="E20" s="10"/>
@@ -1944,24 +2246,32 @@
       <c r="H20" s="9"/>
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
-      <c r="K20" s="9"/>
+      <c r="K20" s="70"/>
       <c r="L20" s="9"/>
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="9"/>
-      <c r="U20" s="10"/>
-      <c r="V20" s="10"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="69"/>
+      <c r="Q20" s="70"/>
+      <c r="R20" s="70"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
       <c r="W20" s="9"/>
       <c r="X20" s="9"/>
       <c r="Y20" s="10"/>
       <c r="Z20" s="10"/>
-    </row>
-    <row r="21" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="45"/>
+      <c r="AA20" s="70"/>
+      <c r="AB20" s="9"/>
+      <c r="AC20" s="10"/>
+      <c r="AD20" s="10"/>
+      <c r="AE20" s="9"/>
+      <c r="AF20" s="69"/>
+      <c r="AG20" s="70"/>
+      <c r="AH20" s="70"/>
+    </row>
+    <row r="21" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="61"/>
       <c r="B21" s="2" t="s">
         <v>33</v>
       </c>
@@ -1980,7 +2290,7 @@
       <c r="J21" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="K21" s="9"/>
+      <c r="K21" s="88"/>
       <c r="L21" s="11" t="s">
         <v>12</v>
       </c>
@@ -1990,34 +2300,54 @@
       <c r="N21" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="P21" s="13" t="s">
+      <c r="O21" s="9"/>
+      <c r="P21" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q21" s="67" t="s">
+        <v>116</v>
+      </c>
+      <c r="R21" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="T21" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="13"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="16" t="s">
+      <c r="U21" s="13"/>
+      <c r="V21" s="13"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="U21" s="17" t="s">
+      <c r="Y21" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="V21" s="16" t="s">
+      <c r="Z21" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="W21" s="9"/>
-      <c r="X21" s="11" t="s">
+      <c r="AA21" s="85"/>
+      <c r="AB21" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Y21" s="12" t="s">
+      <c r="AC21" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="Z21" s="12" t="s">
+      <c r="AD21" s="12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="45"/>
+      <c r="AE21" s="9"/>
+      <c r="AF21" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG21" s="67" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH21" s="67" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="61"/>
       <c r="B22" s="2" t="s">
         <v>42</v>
       </c>
@@ -2036,7 +2366,7 @@
       <c r="J22" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="K22" s="9"/>
+      <c r="K22" s="88"/>
       <c r="L22" s="11" t="s">
         <v>12</v>
       </c>
@@ -2046,34 +2376,54 @@
       <c r="N22" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="P22" s="13" t="s">
+      <c r="O22" s="9"/>
+      <c r="P22" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q22" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R22" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="T22" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="Q22" s="13"/>
-      <c r="R22" s="13"/>
-      <c r="S22" s="9"/>
-      <c r="T22" s="16" t="s">
+      <c r="U22" s="13"/>
+      <c r="V22" s="13"/>
+      <c r="W22" s="9"/>
+      <c r="X22" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="U22" s="17" t="s">
+      <c r="Y22" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="V22" s="16" t="s">
+      <c r="Z22" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="W22" s="9"/>
-      <c r="X22" s="11" t="s">
+      <c r="AA22" s="85"/>
+      <c r="AB22" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Y22" s="15" t="s">
+      <c r="AC22" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="Z22" s="15" t="s">
+      <c r="AD22" s="15" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="46"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG22" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH22" s="68" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="62"/>
       <c r="B23" s="2" t="s">
         <v>48</v>
       </c>
@@ -2092,7 +2442,7 @@
       <c r="J23" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="K23" s="9"/>
+      <c r="K23" s="85"/>
       <c r="L23" s="11" t="s">
         <v>12</v>
       </c>
@@ -2102,53 +2452,75 @@
       <c r="N23" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="P23" s="13" t="s">
+      <c r="O23" s="9"/>
+      <c r="P23" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q23" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R23" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="T23" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="Q23" s="13"/>
-      <c r="R23" s="13"/>
-      <c r="S23" s="9"/>
-      <c r="T23" s="13" t="s">
+      <c r="U23" s="13"/>
+      <c r="V23" s="13"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="U23" s="13" t="s">
+      <c r="Y23" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="V23" s="13" t="s">
+      <c r="Z23" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="W23" s="9"/>
-      <c r="X23" s="11" t="s">
+      <c r="AA23" s="85"/>
+      <c r="AB23" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Y23" s="15" t="s">
+      <c r="AC23" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="Z23" s="15" t="s">
+      <c r="AD23" s="15" t="s">
         <v>17</v>
       </c>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG23" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH23" s="68" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="D1:N2"/>
-    <mergeCell ref="P1:Z2"/>
-    <mergeCell ref="P3:R4"/>
-    <mergeCell ref="T3:V4"/>
-    <mergeCell ref="X3:Z4"/>
+  <mergeCells count="12">
     <mergeCell ref="A17:A23"/>
     <mergeCell ref="D3:F4"/>
     <mergeCell ref="H3:J4"/>
     <mergeCell ref="L3:N4"/>
     <mergeCell ref="A8:A14"/>
+    <mergeCell ref="D1:R2"/>
+    <mergeCell ref="T1:AH2"/>
+    <mergeCell ref="T3:V4"/>
+    <mergeCell ref="X3:Z4"/>
+    <mergeCell ref="AB3:AD4"/>
+    <mergeCell ref="P3:R4"/>
+    <mergeCell ref="AF3:AH4"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFEE9AEA-D75E-434A-978C-01541575A73F}">
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
@@ -2157,88 +2529,108 @@
     <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="1" customWidth="1"/>
     <col min="7" max="7" width="1" customWidth="1"/>
-    <col min="11" max="11" width="1.33203125" customWidth="1"/>
-    <col min="13" max="13" width="1.5" customWidth="1"/>
+    <col min="9" max="9" width="1.33203125" customWidth="1"/>
+    <col min="13" max="13" width="1.33203125" customWidth="1"/>
+    <col min="15" max="15" width="1.5" customWidth="1"/>
+    <col min="17" max="17" width="1.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="27"/>
-      <c r="D1" s="53" t="s">
+      <c r="D1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="J1" s="53" t="s">
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="L1" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-    </row>
-    <row r="2" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-    </row>
-    <row r="3" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="D3" s="56" t="s">
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+    </row>
+    <row r="2" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+    </row>
+    <row r="3" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="D3" s="45" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="45" t="s">
         <v>3</v>
       </c>
       <c r="G3" s="3"/>
-      <c r="H3" s="56" t="s">
+      <c r="H3" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="56" t="s">
+      <c r="J3" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="L3" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="56" t="s">
+      <c r="M3" s="3"/>
+      <c r="N3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="3"/>
-      <c r="N3" s="56" t="s">
+      <c r="O3" s="3"/>
+      <c r="P3" s="45" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="D4" s="56"/>
+      <c r="R3" s="45" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="D4" s="45"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="56"/>
+      <c r="F4" s="45"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="56"/>
+      <c r="H4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="L4" s="45"/>
       <c r="M4" s="3"/>
-      <c r="N4" s="56"/>
-    </row>
-    <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="N4" s="45"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="45"/>
+      <c r="R4" s="45"/>
+    </row>
+    <row r="5" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="D5" s="4"/>
       <c r="E5" s="3"/>
       <c r="F5" s="4"/>
       <c r="G5" s="3"/>
       <c r="H5" s="4"/>
       <c r="J5" s="4"/>
-      <c r="K5" s="3"/>
       <c r="L5" s="4"/>
       <c r="M5" s="3"/>
       <c r="N5" s="4"/>
-    </row>
-    <row r="6" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="O5" s="3"/>
+      <c r="P5" s="4"/>
+      <c r="R5" s="4"/>
+    </row>
+    <row r="6" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
@@ -2259,7 +2651,6 @@
       <c r="J6" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K6" s="3"/>
       <c r="L6" s="5" t="s">
         <v>79</v>
       </c>
@@ -2267,12 +2658,19 @@
       <c r="N6" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="O6" s="3"/>
+      <c r="P6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="54" t="s">
+    <row r="8" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="52" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -2289,21 +2687,23 @@
       <c r="H8" s="18">
         <v>1378</v>
       </c>
-      <c r="I8" s="20"/>
-      <c r="J8" s="18">
+      <c r="J8" s="21"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="18">
         <v>1146</v>
-      </c>
-      <c r="K8" s="19"/>
-      <c r="L8" s="21">
-        <v>6873</v>
       </c>
       <c r="M8" s="19"/>
       <c r="N8" s="21">
+        <v>6873</v>
+      </c>
+      <c r="O8" s="19"/>
+      <c r="P8" s="21">
         <v>1360</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="55"/>
+      <c r="R8" s="21"/>
+    </row>
+    <row r="9" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="53"/>
       <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
@@ -2318,21 +2718,23 @@
       <c r="H9" s="18">
         <v>721</v>
       </c>
-      <c r="I9" s="20"/>
-      <c r="J9" s="21">
+      <c r="J9" s="21"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="21">
         <v>5441</v>
-      </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="21">
-        <v>2148</v>
       </c>
       <c r="M9" s="19"/>
       <c r="N9" s="21">
+        <v>2148</v>
+      </c>
+      <c r="O9" s="19"/>
+      <c r="P9" s="21">
         <v>716</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="55"/>
+      <c r="R9" s="21"/>
+    </row>
+    <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="53"/>
       <c r="B10" s="2" t="s">
         <v>27</v>
       </c>
@@ -2347,36 +2749,40 @@
       <c r="H10" s="18">
         <v>739</v>
       </c>
-      <c r="I10" s="20"/>
-      <c r="J10" s="21">
+      <c r="J10" s="21"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="21">
         <v>7589</v>
-      </c>
-      <c r="K10" s="19"/>
-      <c r="L10" s="21">
-        <v>788</v>
       </c>
       <c r="M10" s="19"/>
       <c r="N10" s="21">
+        <v>788</v>
+      </c>
+      <c r="O10" s="19"/>
+      <c r="P10" s="21">
         <v>719</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="55"/>
+      <c r="R10" s="21"/>
+    </row>
+    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="53"/>
       <c r="B11" s="2"/>
       <c r="D11" s="19"/>
       <c r="E11" s="19"/>
       <c r="F11" s="19"/>
       <c r="G11" s="19"/>
       <c r="H11" s="19"/>
-      <c r="I11" s="20"/>
       <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
+      <c r="K11" s="20"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
       <c r="N11" s="19"/>
-    </row>
-    <row r="12" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="55"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="R11" s="19"/>
+    </row>
+    <row r="12" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="53"/>
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
@@ -2391,21 +2797,23 @@
       <c r="H12" s="18">
         <v>1699</v>
       </c>
-      <c r="I12" s="20"/>
-      <c r="J12" s="21">
+      <c r="J12" s="21"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="21">
         <v>6372</v>
-      </c>
-      <c r="K12" s="19"/>
-      <c r="L12" s="21">
-        <v>6157</v>
       </c>
       <c r="M12" s="19"/>
       <c r="N12" s="21">
+        <v>6157</v>
+      </c>
+      <c r="O12" s="19"/>
+      <c r="P12" s="21">
         <v>1145</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="55"/>
+      <c r="R12" s="21"/>
+    </row>
+    <row r="13" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="53"/>
       <c r="B13" s="2" t="s">
         <v>42</v>
       </c>
@@ -2420,21 +2828,23 @@
       <c r="H13" s="18">
         <v>650</v>
       </c>
-      <c r="I13" s="20"/>
-      <c r="J13" s="18">
+      <c r="J13" s="21"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="18">
         <v>10452</v>
-      </c>
-      <c r="K13" s="19"/>
-      <c r="L13" s="21">
-        <v>2148</v>
       </c>
       <c r="M13" s="19"/>
       <c r="N13" s="21">
+        <v>2148</v>
+      </c>
+      <c r="O13" s="19"/>
+      <c r="P13" s="21">
         <v>716</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="55"/>
+      <c r="R13" s="21"/>
+    </row>
+    <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="53"/>
       <c r="B14" s="2" t="s">
         <v>48</v>
       </c>
@@ -2449,35 +2859,39 @@
       <c r="H14" s="18">
         <v>653</v>
       </c>
-      <c r="I14" s="20"/>
-      <c r="J14" s="21">
+      <c r="J14" s="21"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="21">
         <v>4797</v>
-      </c>
-      <c r="K14" s="19"/>
-      <c r="L14" s="21">
-        <v>1575</v>
       </c>
       <c r="M14" s="19"/>
       <c r="N14" s="21">
+        <v>1575</v>
+      </c>
+      <c r="O14" s="19"/>
+      <c r="P14" s="21">
         <v>717</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="55"/>
+      <c r="R14" s="21"/>
+    </row>
+    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="53"/>
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
       <c r="H15" s="19"/>
-      <c r="I15" s="20"/>
       <c r="J15" s="24"/>
-      <c r="K15" s="19"/>
+      <c r="K15" s="20"/>
       <c r="L15" s="24"/>
       <c r="M15" s="19"/>
       <c r="N15" s="24"/>
-    </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="55"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="24"/>
+      <c r="R15" s="24"/>
+    </row>
+    <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="53"/>
       <c r="B16" s="12" t="s">
         <v>80</v>
       </c>
@@ -2487,7 +2901,7 @@
       </c>
       <c r="E16" s="26"/>
       <c r="F16" s="25">
-        <f t="shared" ref="F16:N16" si="0">AVERAGE(F8:F14)/86400</f>
+        <f t="shared" ref="F16:P16" si="0">AVERAGE(F8:F14)/86400</f>
         <v>3.0599922839506175E-2</v>
       </c>
       <c r="G16" s="26"/>
@@ -2495,24 +2909,32 @@
         <f t="shared" si="0"/>
         <v>1.1265432098765432E-2</v>
       </c>
-      <c r="I16" s="20"/>
-      <c r="J16" s="25">
+      <c r="J16" s="25" t="e">
+        <f t="shared" ref="J16" si="1">AVERAGE(J8:J14)/86400</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K16" s="20"/>
+      <c r="L16" s="25">
         <f t="shared" si="0"/>
         <v>6.905285493827161E-2</v>
-      </c>
-      <c r="K16" s="26"/>
-      <c r="L16" s="25">
-        <f t="shared" si="0"/>
-        <v>3.7980324074074076E-2</v>
       </c>
       <c r="M16" s="26"/>
       <c r="N16" s="25">
         <f t="shared" si="0"/>
+        <v>3.7980324074074076E-2</v>
+      </c>
+      <c r="O16" s="26"/>
+      <c r="P16" s="25">
+        <f t="shared" si="0"/>
         <v>1.0364583333333333E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="55"/>
+      <c r="R16" s="25" t="e">
+        <f t="shared" ref="R16" si="2">AVERAGE(R8:R14)/86400</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="53"/>
       <c r="B17" s="12" t="s">
         <v>81</v>
       </c>
@@ -2522,32 +2944,40 @@
       </c>
       <c r="E17" s="26"/>
       <c r="F17" s="25">
-        <f t="shared" ref="F17:N17" si="1">MIN(F8:F14)/86400</f>
+        <f t="shared" ref="F17:P17" si="3">MIN(F8:F14)/86400</f>
         <v>1.5011574074074075E-2</v>
       </c>
       <c r="G17" s="26"/>
       <c r="H17" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7.5231481481481477E-3</v>
       </c>
-      <c r="I17" s="20"/>
       <c r="J17" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J17" si="4">MIN(J8:J14)/86400</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="20"/>
+      <c r="L17" s="25">
+        <f t="shared" si="3"/>
         <v>1.3263888888888889E-2</v>
-      </c>
-      <c r="K17" s="26"/>
-      <c r="L17" s="25">
-        <f t="shared" si="1"/>
-        <v>9.1203703703703707E-3</v>
       </c>
       <c r="M17" s="26"/>
       <c r="N17" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
+        <v>9.1203703703703707E-3</v>
+      </c>
+      <c r="O17" s="26"/>
+      <c r="P17" s="25">
+        <f t="shared" si="3"/>
         <v>8.2870370370370372E-3</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="55"/>
+      <c r="R17" s="25">
+        <f t="shared" ref="R17" si="5">MIN(R8:R14)/86400</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="53"/>
       <c r="B18" s="12" t="s">
         <v>82</v>
       </c>
@@ -2557,33 +2987,42 @@
       </c>
       <c r="E18" s="26"/>
       <c r="F18" s="25">
-        <f t="shared" ref="F18:N18" si="2">MAX(F8:F14)/86400</f>
+        <f t="shared" ref="F18:P18" si="6">MAX(F8:F14)/86400</f>
         <v>6.3194444444444442E-2</v>
       </c>
       <c r="G18" s="26"/>
       <c r="H18" s="25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.9664351851851853E-2</v>
       </c>
-      <c r="I18" s="20"/>
+      <c r="I18" s="10"/>
       <c r="J18" s="25">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="J18" si="7">MAX(J8:J14)/86400</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="20"/>
+      <c r="L18" s="25">
+        <f t="shared" si="6"/>
         <v>0.12097222222222222</v>
-      </c>
-      <c r="K18" s="26"/>
-      <c r="L18" s="25">
-        <f t="shared" si="2"/>
-        <v>7.9548611111111112E-2</v>
       </c>
       <c r="M18" s="26"/>
       <c r="N18" s="25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
+        <v>7.9548611111111112E-2</v>
+      </c>
+      <c r="O18" s="26"/>
+      <c r="P18" s="25">
+        <f t="shared" si="6"/>
         <v>1.5740740740740739E-2</v>
       </c>
-      <c r="O18" s="10"/>
-    </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="55"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="25">
+        <f t="shared" ref="R18" si="8">MAX(R8:R14)/86400</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="53"/>
       <c r="B19" s="12" t="s">
         <v>83</v>
       </c>
@@ -2593,60 +3032,72 @@
       </c>
       <c r="E19" s="26"/>
       <c r="F19" s="25">
-        <f t="shared" ref="F19:N19" si="3">STDEV(F8:F14)/86400</f>
+        <f t="shared" ref="F19:P19" si="9">STDEV(F8:F14)/86400</f>
         <v>1.7594947479858736E-2</v>
       </c>
       <c r="G19" s="26"/>
       <c r="H19" s="25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>5.2175569904686506E-3</v>
       </c>
-      <c r="I19" s="20"/>
-      <c r="J19" s="25">
-        <f t="shared" si="3"/>
+      <c r="J19" s="25" t="e">
+        <f t="shared" ref="J19" si="10">STDEV(J8:J14)/86400</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K19" s="20"/>
+      <c r="L19" s="25">
+        <f t="shared" si="9"/>
         <v>3.5785325153604032E-2</v>
-      </c>
-      <c r="K19" s="26"/>
-      <c r="L19" s="25">
-        <f t="shared" si="3"/>
-        <v>2.9674220235764433E-2</v>
       </c>
       <c r="M19" s="26"/>
       <c r="N19" s="25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
+        <v>2.9674220235764433E-2</v>
+      </c>
+      <c r="O19" s="26"/>
+      <c r="P19" s="25">
+        <f t="shared" si="9"/>
         <v>3.2959317415711177E-3</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="R19" s="25" t="e">
+        <f t="shared" ref="R19" si="11">STDEV(R8:R14)/86400</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
       <c r="D20" s="19"/>
       <c r="E20" s="19"/>
       <c r="F20" s="19"/>
       <c r="G20" s="19"/>
       <c r="H20" s="19"/>
-      <c r="I20" s="20"/>
       <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
+      <c r="K20" s="20"/>
       <c r="L20" s="19"/>
       <c r="M20" s="19"/>
       <c r="N20" s="19"/>
-    </row>
-    <row r="21" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="R20" s="19"/>
+    </row>
+    <row r="21" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
       <c r="D21" s="19"/>
       <c r="E21" s="19"/>
       <c r="F21" s="19"/>
       <c r="G21" s="19"/>
       <c r="H21" s="19"/>
-      <c r="I21" s="20"/>
       <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
+      <c r="K21" s="20"/>
       <c r="L21" s="19"/>
       <c r="M21" s="19"/>
       <c r="N21" s="19"/>
-    </row>
-    <row r="22" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="54" t="s">
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="R21" s="19"/>
+    </row>
+    <row r="22" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="52" t="s">
         <v>54</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -2663,21 +3114,27 @@
       <c r="H22" s="18">
         <v>1986</v>
       </c>
-      <c r="I22" s="20"/>
-      <c r="J22" s="22" t="s">
+      <c r="J22" s="23">
+        <v>862</v>
+      </c>
+      <c r="K22" s="20"/>
+      <c r="L22" s="22" t="s">
         <v>84</v>
-      </c>
-      <c r="K22" s="19"/>
-      <c r="L22" s="23">
-        <v>29782</v>
       </c>
       <c r="M22" s="19"/>
       <c r="N22" s="23">
+        <v>29782</v>
+      </c>
+      <c r="O22" s="19"/>
+      <c r="P22" s="23">
         <v>5799</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="55"/>
+      <c r="R22" s="23">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="53"/>
       <c r="B23" s="2" t="s">
         <v>22</v>
       </c>
@@ -2692,21 +3149,27 @@
       <c r="H23" s="18">
         <v>2340</v>
       </c>
-      <c r="I23" s="20"/>
-      <c r="J23" s="22" t="s">
+      <c r="J23" s="21">
+        <v>510</v>
+      </c>
+      <c r="K23" s="20"/>
+      <c r="L23" s="22" t="s">
         <v>84</v>
-      </c>
-      <c r="K23" s="19"/>
-      <c r="L23" s="21">
-        <v>24197</v>
       </c>
       <c r="M23" s="19"/>
       <c r="N23" s="21">
+        <v>24197</v>
+      </c>
+      <c r="O23" s="19"/>
+      <c r="P23" s="21">
         <v>3078</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="55"/>
+      <c r="R23" s="21">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="53"/>
       <c r="B24" s="2" t="s">
         <v>27</v>
       </c>
@@ -2721,36 +3184,44 @@
       <c r="H24" s="18">
         <v>1517</v>
       </c>
-      <c r="I24" s="20"/>
-      <c r="J24" s="22" t="s">
+      <c r="J24" s="21">
+        <v>522</v>
+      </c>
+      <c r="K24" s="20"/>
+      <c r="L24" s="22" t="s">
         <v>84</v>
-      </c>
-      <c r="K24" s="19"/>
-      <c r="L24" s="21">
-        <v>1360</v>
       </c>
       <c r="M24" s="19"/>
       <c r="N24" s="21">
+        <v>1360</v>
+      </c>
+      <c r="O24" s="19"/>
+      <c r="P24" s="21">
         <v>1503</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="55"/>
+      <c r="R24" s="21">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="53"/>
       <c r="B25" s="2"/>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
-      <c r="I25" s="20"/>
       <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
+      <c r="K25" s="20"/>
       <c r="L25" s="19"/>
       <c r="M25" s="19"/>
       <c r="N25" s="19"/>
-    </row>
-    <row r="26" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="55"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="R25" s="19"/>
+    </row>
+    <row r="26" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="53"/>
       <c r="B26" s="2" t="s">
         <v>33</v>
       </c>
@@ -2765,21 +3236,27 @@
       <c r="H26" s="18">
         <v>4748</v>
       </c>
-      <c r="I26" s="20"/>
-      <c r="J26" s="22" t="s">
+      <c r="J26" s="18">
+        <v>713</v>
+      </c>
+      <c r="K26" s="20"/>
+      <c r="L26" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="K26" s="19"/>
-      <c r="L26" s="21">
+      <c r="M26" s="19"/>
+      <c r="N26" s="21">
         <v>2076</v>
       </c>
-      <c r="M26" s="19"/>
-      <c r="N26" s="18">
+      <c r="O26" s="19"/>
+      <c r="P26" s="18">
         <v>5226</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="55"/>
+      <c r="R26" s="18">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="53"/>
       <c r="B27" s="2" t="s">
         <v>42</v>
       </c>
@@ -2794,21 +3271,27 @@
       <c r="H27" s="18">
         <v>1372</v>
       </c>
-      <c r="I27" s="20"/>
-      <c r="J27" s="22" t="s">
+      <c r="J27" s="18">
+        <v>513</v>
+      </c>
+      <c r="K27" s="20"/>
+      <c r="L27" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="K27" s="19"/>
-      <c r="L27" s="21">
+      <c r="M27" s="19"/>
+      <c r="N27" s="21">
         <v>1718</v>
       </c>
-      <c r="M27" s="19"/>
-      <c r="N27" s="18">
+      <c r="O27" s="19"/>
+      <c r="P27" s="18">
         <v>1145</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="55"/>
+      <c r="R27" s="18">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="53"/>
       <c r="B28" s="2" t="s">
         <v>48</v>
       </c>
@@ -2823,24 +3306,30 @@
       <c r="H28" s="18">
         <v>815</v>
       </c>
-      <c r="I28" s="20"/>
-      <c r="J28" s="22" t="s">
+      <c r="J28" s="18">
+        <v>510</v>
+      </c>
+      <c r="K28" s="20"/>
+      <c r="L28" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="K28" s="19"/>
-      <c r="L28" s="21">
+      <c r="M28" s="19"/>
+      <c r="N28" s="21">
         <v>1933</v>
       </c>
-      <c r="M28" s="19"/>
-      <c r="N28" s="18">
+      <c r="O28" s="19"/>
+      <c r="P28" s="18">
         <v>716</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A29" s="55"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A30" s="55"/>
+      <c r="R28" s="18">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A29" s="53"/>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A30" s="53"/>
       <c r="B30" s="12" t="s">
         <v>80</v>
       </c>
@@ -2850,32 +3339,42 @@
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="25">
-        <f t="shared" ref="F30" si="4">AVERAGE(F22:F28)/86400</f>
+        <f t="shared" ref="F30" si="12">AVERAGE(F22:F28)/86400</f>
         <v>6.6024305555555551E-2</v>
       </c>
       <c r="G30" s="26"/>
       <c r="H30" s="25">
-        <f t="shared" ref="H30" si="5">AVERAGE(H22:H28)/86400</f>
+        <f t="shared" ref="H30" si="13">AVERAGE(H22:H28)/86400</f>
         <v>2.4648919753086418E-2</v>
       </c>
-      <c r="I30" s="20"/>
-      <c r="J30" s="25" t="e">
-        <f t="shared" ref="J30" si="6">AVERAGE(J22:J28)/86400</f>
+      <c r="I30" s="26"/>
+      <c r="J30" s="25">
+        <f t="shared" ref="J30" si="14">AVERAGE(J22:J28)/86400</f>
+        <v>7.0023148148148145E-3</v>
+      </c>
+      <c r="K30" s="20"/>
+      <c r="L30" s="25" t="e">
+        <f t="shared" ref="L30" si="15">AVERAGE(L22:L28)/86400</f>
         <v>#DIV/0!</v>
-      </c>
-      <c r="K30" s="26"/>
-      <c r="L30" s="25">
-        <f t="shared" ref="L30" si="7">AVERAGE(L22:L28)/86400</f>
-        <v>0.11779706790123456</v>
       </c>
       <c r="M30" s="26"/>
       <c r="N30" s="25">
-        <f t="shared" ref="N30" si="8">AVERAGE(N22:N28)/86400</f>
+        <f t="shared" ref="N30" si="16">AVERAGE(N22:N28)/86400</f>
+        <v>0.11779706790123456</v>
+      </c>
+      <c r="O30" s="26"/>
+      <c r="P30" s="25">
+        <f t="shared" ref="P30:R30" si="17">AVERAGE(P22:P28)/86400</f>
         <v>3.3694058641975305E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A31" s="55"/>
+      <c r="Q30" s="26"/>
+      <c r="R30" s="25">
+        <f t="shared" si="17"/>
+        <v>6.2905092592592596E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A31" s="53"/>
       <c r="B31" s="12" t="s">
         <v>81</v>
       </c>
@@ -2885,32 +3384,42 @@
       </c>
       <c r="E31" s="26"/>
       <c r="F31" s="25">
-        <f t="shared" ref="F31" si="9">MIN(F22:F28)/86400</f>
+        <f t="shared" ref="F31" si="18">MIN(F22:F28)/86400</f>
         <v>2.0162037037037037E-2</v>
       </c>
       <c r="G31" s="26"/>
       <c r="H31" s="25">
-        <f t="shared" ref="H31" si="10">MIN(H22:H28)/86400</f>
+        <f t="shared" ref="H31" si="19">MIN(H22:H28)/86400</f>
         <v>9.432870370370371E-3</v>
       </c>
-      <c r="I31" s="20"/>
+      <c r="I31" s="26"/>
       <c r="J31" s="25">
-        <f t="shared" ref="J31" si="11">MIN(J22:J28)/86400</f>
+        <f t="shared" ref="J31" si="20">MIN(J22:J28)/86400</f>
+        <v>5.9027777777777776E-3</v>
+      </c>
+      <c r="K31" s="20"/>
+      <c r="L31" s="25">
+        <f t="shared" ref="L31" si="21">MIN(L22:L28)/86400</f>
         <v>0</v>
-      </c>
-      <c r="K31" s="26"/>
-      <c r="L31" s="25">
-        <f t="shared" ref="L31" si="12">MIN(L22:L28)/86400</f>
-        <v>1.5740740740740739E-2</v>
       </c>
       <c r="M31" s="26"/>
       <c r="N31" s="25">
-        <f t="shared" ref="N31" si="13">MIN(N22:N28)/86400</f>
+        <f t="shared" ref="N31" si="22">MIN(N22:N28)/86400</f>
+        <v>1.5740740740740739E-2</v>
+      </c>
+      <c r="O31" s="26"/>
+      <c r="P31" s="25">
+        <f t="shared" ref="P31:R31" si="23">MIN(P22:P28)/86400</f>
         <v>8.2870370370370372E-3</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A32" s="55"/>
+      <c r="Q31" s="26"/>
+      <c r="R31" s="25">
+        <f t="shared" si="23"/>
+        <v>5.8796296296296296E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A32" s="53"/>
       <c r="B32" s="12" t="s">
         <v>82</v>
       </c>
@@ -2920,32 +3429,42 @@
       </c>
       <c r="E32" s="26"/>
       <c r="F32" s="25">
-        <f t="shared" ref="F32" si="14">MAX(F22:F28)/86400</f>
+        <f t="shared" ref="F32" si="24">MAX(F22:F28)/86400</f>
         <v>0.15104166666666666</v>
       </c>
       <c r="G32" s="26"/>
       <c r="H32" s="25">
-        <f t="shared" ref="H32" si="15">MAX(H22:H28)/86400</f>
+        <f t="shared" ref="H32" si="25">MAX(H22:H28)/86400</f>
         <v>5.4953703703703706E-2</v>
       </c>
-      <c r="I32" s="20"/>
+      <c r="I32" s="26"/>
       <c r="J32" s="25">
-        <f t="shared" ref="J32" si="16">MAX(J22:J28)/86400</f>
+        <f t="shared" ref="J32" si="26">MAX(J22:J28)/86400</f>
+        <v>9.9768518518518513E-3</v>
+      </c>
+      <c r="K32" s="20"/>
+      <c r="L32" s="25">
+        <f t="shared" ref="L32" si="27">MAX(L22:L28)/86400</f>
         <v>0</v>
-      </c>
-      <c r="K32" s="26"/>
-      <c r="L32" s="25">
-        <f t="shared" ref="L32" si="17">MAX(L22:L28)/86400</f>
-        <v>0.34469907407407407</v>
       </c>
       <c r="M32" s="26"/>
       <c r="N32" s="25">
-        <f t="shared" ref="N32" si="18">MAX(N22:N28)/86400</f>
+        <f t="shared" ref="N32" si="28">MAX(N22:N28)/86400</f>
+        <v>0.34469907407407407</v>
+      </c>
+      <c r="O32" s="26"/>
+      <c r="P32" s="25">
+        <f t="shared" ref="P32:R32" si="29">MAX(P22:P28)/86400</f>
         <v>6.7118055555555556E-2</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33" s="55"/>
+      <c r="Q32" s="26"/>
+      <c r="R32" s="25">
+        <f t="shared" si="29"/>
+        <v>7.6504629629629631E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A33" s="53"/>
       <c r="B33" s="12" t="s">
         <v>83</v>
       </c>
@@ -2955,42 +3474,54 @@
       </c>
       <c r="E33" s="26"/>
       <c r="F33" s="25">
-        <f t="shared" ref="F33" si="19">STDEV(F22:F28)/86400</f>
+        <f t="shared" ref="F33" si="30">STDEV(F22:F28)/86400</f>
         <v>5.4060922696568502E-2</v>
       </c>
       <c r="G33" s="26"/>
       <c r="H33" s="25">
-        <f t="shared" ref="H33" si="20">STDEV(H22:H28)/86400</f>
+        <f t="shared" ref="H33" si="31">STDEV(H22:H28)/86400</f>
         <v>1.6036101906559692E-2</v>
       </c>
-      <c r="I33" s="20"/>
-      <c r="J33" s="25" t="e">
-        <f t="shared" ref="J33" si="21">STDEV(J22:J28)/86400</f>
+      <c r="I33" s="26"/>
+      <c r="J33" s="25">
+        <f t="shared" ref="J33" si="32">STDEV(J22:J28)/86400</f>
+        <v>1.7253990512763721E-3</v>
+      </c>
+      <c r="K33" s="20"/>
+      <c r="L33" s="25" t="e">
+        <f t="shared" ref="L33" si="33">STDEV(L22:L28)/86400</f>
         <v>#DIV/0!</v>
-      </c>
-      <c r="K33" s="26"/>
-      <c r="L33" s="25">
-        <f t="shared" ref="L33" si="22">STDEV(L22:L28)/86400</f>
-        <v>0.15212757345059646</v>
       </c>
       <c r="M33" s="26"/>
       <c r="N33" s="25">
-        <f t="shared" ref="N33" si="23">STDEV(N22:N28)/86400</f>
+        <f t="shared" ref="N33" si="34">STDEV(N22:N28)/86400</f>
+        <v>0.15212757345059646</v>
+      </c>
+      <c r="O33" s="26"/>
+      <c r="P33" s="25">
+        <f t="shared" ref="P33:R33" si="35">STDEV(P22:P28)/86400</f>
         <v>2.5170299821243251E-2</v>
       </c>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="25">
+        <f t="shared" si="35"/>
+        <v>6.9655351028867355E-4</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="L1:R2"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="D1:J2"/>
     <mergeCell ref="A8:A19"/>
     <mergeCell ref="A22:A33"/>
-    <mergeCell ref="D1:H2"/>
-    <mergeCell ref="J1:N2"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="J3:J4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N3:N4"/>
+    <mergeCell ref="P3:P4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2998,7 +3529,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35BC7457-1CE9-274B-9C5C-A6A35A70BB57}">
-  <dimension ref="A1:AF141"/>
+  <dimension ref="A1:AO141"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
@@ -3009,91 +3540,117 @@
     <col min="6" max="6" width="8.83203125"/>
     <col min="7" max="7" width="1" customWidth="1"/>
     <col min="8" max="8" width="8.83203125"/>
-    <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="1.1640625" customWidth="1"/>
+    <col min="9" max="9" width="1.1640625" customWidth="1"/>
+    <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="1.1640625" customWidth="1"/>
-    <col min="19" max="19" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="10.83203125" style="10"/>
+    <col min="15" max="15" width="1.1640625" customWidth="1"/>
+    <col min="17" max="17" width="1.1640625" customWidth="1"/>
+    <col min="23" max="23" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="10.83203125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="27"/>
-      <c r="D1" s="53" t="s">
+      <c r="D1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="J1" s="53" t="s">
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="L1" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-    </row>
-    <row r="3" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="D3" s="62" t="s">
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+    </row>
+    <row r="2" spans="1:26" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+    </row>
+    <row r="3" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+      <c r="D3" s="49" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="45" t="s">
         <v>3</v>
       </c>
       <c r="G3" s="3"/>
-      <c r="H3" s="56" t="s">
+      <c r="H3" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="56" t="s">
+      <c r="I3" s="63"/>
+      <c r="J3" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="L3" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="56" t="s">
+      <c r="M3" s="3"/>
+      <c r="N3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="3"/>
-      <c r="N3" s="56" t="s">
+      <c r="O3" s="3"/>
+      <c r="P3" s="45" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="D4" s="62"/>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="45" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+      <c r="D4" s="49"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="56"/>
+      <c r="F4" s="45"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="56"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="45"/>
+      <c r="L4" s="45"/>
       <c r="M4" s="3"/>
-      <c r="N4" s="56"/>
-    </row>
-    <row r="5" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="N4" s="45"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="45"/>
+      <c r="Q4" s="63"/>
+      <c r="R4" s="45"/>
+    </row>
+    <row r="5" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="D5" s="30"/>
       <c r="E5" s="3"/>
       <c r="F5" s="4"/>
       <c r="G5" s="3"/>
       <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
       <c r="J5" s="4"/>
-      <c r="K5" s="3"/>
       <c r="L5" s="4"/>
       <c r="M5" s="3"/>
       <c r="N5" s="4"/>
-    </row>
-    <row r="6" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="O5" s="3"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+    </row>
+    <row r="6" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
@@ -3114,10 +3671,10 @@
       <c r="H6" s="5" t="s">
         <v>79</v>
       </c>
+      <c r="I6" s="63"/>
       <c r="J6" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K6" s="3"/>
       <c r="L6" s="5" t="s">
         <v>79</v>
       </c>
@@ -3125,12 +3682,20 @@
       <c r="N6" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="54" t="s">
+      <c r="O6" s="3"/>
+      <c r="P6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q6" s="63"/>
+      <c r="R6" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="46" t="s">
         <v>11</v>
       </c>
       <c r="C7">
@@ -3147,19 +3712,23 @@
       <c r="H7" s="33">
         <v>86.371557100000004</v>
       </c>
-      <c r="J7">
+      <c r="I7" s="33"/>
+      <c r="J7" s="33"/>
+      <c r="L7">
         <v>77.830788299999995</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>601.26380110000002</v>
       </c>
-      <c r="N7" s="36">
+      <c r="P7" s="36">
         <v>81.728998700000005</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="55"/>
-      <c r="B8" s="60"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="33"/>
+    </row>
+    <row r="8" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="53"/>
+      <c r="B8" s="47"/>
       <c r="C8">
         <v>2</v>
       </c>
@@ -3174,19 +3743,21 @@
       <c r="H8" s="33">
         <v>80.167861900000005</v>
       </c>
-      <c r="J8">
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="L8">
         <v>69.680095600000001</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>158.07883570000001</v>
       </c>
-      <c r="N8">
+      <c r="P8">
         <v>84.766424000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="55"/>
-      <c r="B9" s="60"/>
+    <row r="9" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="53"/>
+      <c r="B9" s="47"/>
       <c r="C9">
         <v>3</v>
       </c>
@@ -3201,25 +3772,27 @@
       <c r="H9" s="33">
         <v>77.724527300000005</v>
       </c>
-      <c r="J9">
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
+      <c r="L9">
         <v>72.386975800000002</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>247.77741470000001</v>
       </c>
-      <c r="N9">
+      <c r="P9">
         <v>157.49419499999999</v>
       </c>
-      <c r="S9" s="57" t="s">
+      <c r="W9" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="T9" s="57"/>
-      <c r="U9" s="57"/>
-      <c r="V9" s="57"/>
-    </row>
-    <row r="10" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="55"/>
-      <c r="B10" s="60"/>
+      <c r="X9" s="51"/>
+      <c r="Y9" s="51"/>
+      <c r="Z9" s="51"/>
+    </row>
+    <row r="10" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="53"/>
+      <c r="B10" s="47"/>
       <c r="C10">
         <v>4</v>
       </c>
@@ -3234,24 +3807,26 @@
       <c r="H10" s="33">
         <v>230.29127550000001</v>
       </c>
-      <c r="J10">
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
+      <c r="L10">
         <v>216.59442749999999</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>86.154680900000002</v>
       </c>
-      <c r="N10">
+      <c r="P10">
         <v>78.742313800000005</v>
       </c>
-      <c r="T10" s="38"/>
-      <c r="U10" s="38"/>
-      <c r="V10" s="38" t="s">
+      <c r="X10" s="38"/>
+      <c r="Y10" s="38"/>
+      <c r="Z10" s="38" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="55"/>
-      <c r="B11" s="60"/>
+    <row r="11" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="53"/>
+      <c r="B11" s="47"/>
       <c r="C11">
         <v>5</v>
       </c>
@@ -3266,30 +3841,32 @@
       <c r="H11" s="33">
         <v>299.50239399999998</v>
       </c>
-      <c r="J11">
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="L11">
         <v>291.95927260000002</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>86.823207999999994</v>
       </c>
-      <c r="N11">
+      <c r="P11">
         <v>153.21892299999999</v>
       </c>
-      <c r="S11" s="37" t="s">
+      <c r="W11" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="T11" s="10">
-        <f>AVERAGE(D38:N67,D7:N36,F74:N103,F105:H134,L105:N134)</f>
-        <v>351.26274900967718</v>
-      </c>
-      <c r="V11" s="26">
-        <f>TIME(,,T11)</f>
-        <v>4.0625000000000001E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="55"/>
-      <c r="B12" s="60"/>
+      <c r="X11" s="10">
+        <f>AVERAGE(D38:P67,D7:P36,F74:P103,F105:H134,N105:P134)</f>
+        <v>337.29835891227754</v>
+      </c>
+      <c r="Z11" s="26">
+        <f>TIME(,,X11)</f>
+        <v>3.9004629629629628E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="53"/>
+      <c r="B12" s="47"/>
       <c r="C12">
         <v>6</v>
       </c>
@@ -3304,30 +3881,32 @@
       <c r="H12" s="33">
         <v>73.355889099999999</v>
       </c>
-      <c r="J12">
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="L12">
         <v>77.210132999999999</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>2313.245696</v>
       </c>
-      <c r="N12">
+      <c r="P12">
         <v>155.06151919999999</v>
       </c>
-      <c r="S12" s="37" t="s">
+      <c r="W12" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="T12" s="10">
-        <f>MIN(D38:N67,D7:N36,F74:N103,F105:H134,L105:N134)</f>
-        <v>59.023810400000002</v>
-      </c>
-      <c r="V12" s="26">
-        <f t="shared" ref="V12:V14" si="0">TIME(,,T12)</f>
-        <v>6.8287037037037036E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="55"/>
-      <c r="B13" s="60"/>
+      <c r="X12" s="10">
+        <f>MIN(D38:P67,D7:P36,F74:P103,F105:H134,N105:P134)</f>
+        <v>50.330599999999997</v>
+      </c>
+      <c r="Z12" s="26">
+        <f t="shared" ref="Z12:Z14" si="0">TIME(,,X12)</f>
+        <v>5.7870370370370367E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="53"/>
+      <c r="B13" s="47"/>
       <c r="C13">
         <v>7</v>
       </c>
@@ -3342,30 +3921,32 @@
       <c r="H13" s="33">
         <v>151.47417250000001</v>
       </c>
-      <c r="J13">
+      <c r="I13" s="33"/>
+      <c r="J13" s="33"/>
+      <c r="L13">
         <v>73.184496300000006</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>661.98075889999996</v>
       </c>
-      <c r="N13">
+      <c r="P13">
         <v>456.90458919999998</v>
       </c>
-      <c r="S13" s="37" t="s">
+      <c r="W13" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="T13" s="10">
-        <f>MAX(D38:N67,D7:N36,F74:N103,F105:H134,L105:N134)</f>
+      <c r="X13" s="10">
+        <f>MAX(D38:P67,D7:P36,F74:P103,F105:H134,N105:P134)</f>
         <v>7218.0189136999998</v>
       </c>
-      <c r="V13" s="26">
+      <c r="Z13" s="26">
         <f t="shared" si="0"/>
         <v>8.3541666666666667E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="55"/>
-      <c r="B14" s="60"/>
+    <row r="14" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="53"/>
+      <c r="B14" s="47"/>
       <c r="C14">
         <v>8</v>
       </c>
@@ -3380,30 +3961,32 @@
       <c r="H14" s="33">
         <v>76.544575100000003</v>
       </c>
-      <c r="J14">
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="L14">
         <v>146.44123880000001</v>
       </c>
-      <c r="L14">
+      <c r="N14">
         <v>3011.4654556999999</v>
       </c>
-      <c r="N14">
+      <c r="P14">
         <v>81.961152400000003</v>
       </c>
-      <c r="S14" s="37" t="s">
+      <c r="W14" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="T14" s="10">
-        <f>STDEV(D38:N67,D7:N36,F74:N103,F105:H134,L105:N134)</f>
-        <v>534.84662778775873</v>
-      </c>
-      <c r="V14" s="26">
+      <c r="X14" s="10">
+        <f>STDEV(D38:P67,D7:P36,F74:P103,F105:H134,N105:P134)</f>
+        <v>525.50420106598369</v>
+      </c>
+      <c r="Z14" s="26">
         <f t="shared" si="0"/>
-        <v>6.1805555555555555E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="55"/>
-      <c r="B15" s="60"/>
+        <v>6.076388888888889E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="53"/>
+      <c r="B15" s="47"/>
       <c r="C15">
         <v>9</v>
       </c>
@@ -3418,19 +4001,21 @@
       <c r="H15" s="33">
         <v>78.093684600000003</v>
       </c>
-      <c r="J15">
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="L15">
         <v>78.716759600000003</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>355.65836380000002</v>
       </c>
-      <c r="N15">
+      <c r="P15">
         <v>159.94233370000001</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="55"/>
-      <c r="B16" s="61"/>
+    <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="53"/>
+      <c r="B16" s="48"/>
       <c r="C16">
         <v>10</v>
       </c>
@@ -3444,19 +4029,21 @@
       <c r="H16" s="31">
         <v>224.6588481</v>
       </c>
-      <c r="J16">
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="L16">
         <v>78.939935899999995</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>141.9226768</v>
       </c>
-      <c r="N16">
+      <c r="P16">
         <v>77.275726899999995</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="55"/>
-      <c r="B17" s="59" t="s">
+    <row r="17" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="53"/>
+      <c r="B17" s="46" t="s">
         <v>86</v>
       </c>
       <c r="C17">
@@ -3473,19 +4060,21 @@
       <c r="H17" s="33">
         <v>73.114328499999999</v>
       </c>
-      <c r="J17">
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="L17">
         <v>207.18083060000001</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>75.325193799999994</v>
       </c>
-      <c r="N17">
+      <c r="P17">
         <v>72.4576469</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="55"/>
-      <c r="B18" s="60"/>
+    <row r="18" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="53"/>
+      <c r="B18" s="47"/>
       <c r="C18">
         <v>2</v>
       </c>
@@ -3500,19 +4089,21 @@
       <c r="H18" s="33">
         <v>71.188278800000006</v>
       </c>
-      <c r="J18">
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="L18">
         <v>65.375731599999995</v>
       </c>
-      <c r="L18">
+      <c r="N18">
         <v>297.85747670000001</v>
       </c>
-      <c r="N18">
+      <c r="P18">
         <v>73.037465600000004</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="55"/>
-      <c r="B19" s="60"/>
+    <row r="19" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="53"/>
+      <c r="B19" s="47"/>
       <c r="C19">
         <v>3</v>
       </c>
@@ -3527,19 +4118,21 @@
       <c r="H19" s="33">
         <v>70.401290500000002</v>
       </c>
-      <c r="J19">
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="L19">
         <v>586.4684383</v>
       </c>
-      <c r="L19">
+      <c r="N19">
         <v>234.6544241</v>
       </c>
-      <c r="N19">
+      <c r="P19">
         <v>75.679750100000007</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="55"/>
-      <c r="B20" s="60"/>
+    <row r="20" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="53"/>
+      <c r="B20" s="47"/>
       <c r="C20">
         <v>4</v>
       </c>
@@ -3554,19 +4147,21 @@
       <c r="H20" s="33">
         <v>80.338869299999999</v>
       </c>
-      <c r="J20">
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="L20">
         <v>323.32953090000001</v>
       </c>
-      <c r="L20">
+      <c r="N20">
         <v>207.73227080000001</v>
       </c>
-      <c r="N20">
+      <c r="P20">
         <v>69.004712999999995</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="55"/>
-      <c r="B21" s="60"/>
+    <row r="21" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="53"/>
+      <c r="B21" s="47"/>
       <c r="C21">
         <v>5</v>
       </c>
@@ -3581,19 +4176,21 @@
       <c r="H21" s="33">
         <v>74.254665099999997</v>
       </c>
-      <c r="J21">
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="L21">
         <v>129.41876830000001</v>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>218.40097359999999</v>
       </c>
-      <c r="N21">
+      <c r="P21">
         <v>64.653414799999993</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="55"/>
-      <c r="B22" s="60"/>
+    <row r="22" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="53"/>
+      <c r="B22" s="47"/>
       <c r="C22">
         <v>6</v>
       </c>
@@ -3608,19 +4205,21 @@
       <c r="H22" s="33">
         <v>70.6183075</v>
       </c>
-      <c r="J22">
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="L22">
         <v>196.73654540000001</v>
       </c>
-      <c r="L22">
+      <c r="N22">
         <v>238.8835492</v>
       </c>
-      <c r="N22">
+      <c r="P22">
         <v>64.707670100000001</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="55"/>
-      <c r="B23" s="60"/>
+    <row r="23" spans="1:16" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="53"/>
+      <c r="B23" s="47"/>
       <c r="C23">
         <v>7</v>
       </c>
@@ -3635,19 +4234,21 @@
       <c r="H23" s="33">
         <v>69.177133299999994</v>
       </c>
-      <c r="J23">
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="L23">
         <v>129.47770080000001</v>
       </c>
-      <c r="L23">
+      <c r="N23">
         <v>220.64875190000001</v>
       </c>
-      <c r="N23">
+      <c r="P23">
         <v>66.928739100000001</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="55"/>
-      <c r="B24" s="60"/>
+    <row r="24" spans="1:16" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="53"/>
+      <c r="B24" s="47"/>
       <c r="C24">
         <v>8</v>
       </c>
@@ -3662,19 +4263,21 @@
       <c r="H24" s="33">
         <v>70.352484700000005</v>
       </c>
-      <c r="J24">
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="L24">
         <v>583.81888790000005</v>
       </c>
-      <c r="L24">
+      <c r="N24">
         <v>156.702572</v>
       </c>
-      <c r="N24">
+      <c r="P24">
         <v>85.198224800000006</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="55"/>
-      <c r="B25" s="60"/>
+    <row r="25" spans="1:16" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="53"/>
+      <c r="B25" s="47"/>
       <c r="C25">
         <v>9</v>
       </c>
@@ -3689,19 +4292,21 @@
       <c r="H25" s="33">
         <v>70.135643900000005</v>
       </c>
-      <c r="J25">
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="L25">
         <v>1580.9047197</v>
       </c>
-      <c r="L25">
+      <c r="N25">
         <v>461.69033109999998</v>
       </c>
-      <c r="N25">
+      <c r="P25">
         <v>86.575239600000003</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="55"/>
-      <c r="B26" s="61"/>
+    <row r="26" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="53"/>
+      <c r="B26" s="48"/>
       <c r="C26">
         <v>10</v>
       </c>
@@ -3715,19 +4320,21 @@
       <c r="H26" s="31">
         <v>70.832701700000001</v>
       </c>
-      <c r="J26">
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="L26">
         <v>1218.9549171000001</v>
       </c>
-      <c r="L26">
+      <c r="N26">
         <v>131.76363090000001</v>
       </c>
-      <c r="N26">
+      <c r="P26">
         <v>75.496478600000003</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" s="55"/>
-      <c r="B27" s="59" t="s">
+    <row r="27" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="53"/>
+      <c r="B27" s="46" t="s">
         <v>27</v>
       </c>
       <c r="C27">
@@ -3744,19 +4351,21 @@
       <c r="H27" s="33">
         <v>81.723654499999995</v>
       </c>
-      <c r="J27">
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="L27">
         <v>916.28107279999995</v>
       </c>
-      <c r="L27">
+      <c r="N27">
         <v>135.59849030000001</v>
       </c>
-      <c r="N27">
+      <c r="P27">
         <v>75.413589000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="55"/>
-      <c r="B28" s="60"/>
+    <row r="28" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="53"/>
+      <c r="B28" s="47"/>
       <c r="C28">
         <v>2</v>
       </c>
@@ -3771,19 +4380,21 @@
       <c r="H28" s="33">
         <v>73.767661000000004</v>
       </c>
-      <c r="J28">
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="L28">
         <v>867.80258600000002</v>
       </c>
-      <c r="L28">
+      <c r="N28">
         <v>66.316842500000007</v>
       </c>
-      <c r="N28">
+      <c r="P28">
         <v>77.701590100000004</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="55"/>
-      <c r="B29" s="60"/>
+    <row r="29" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="53"/>
+      <c r="B29" s="47"/>
       <c r="C29">
         <v>3</v>
       </c>
@@ -3798,19 +4409,21 @@
       <c r="H29" s="33">
         <v>76.209941599999993</v>
       </c>
-      <c r="J29">
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="L29">
         <v>325.8396424</v>
       </c>
-      <c r="L29">
+      <c r="N29">
         <v>66.043703899999997</v>
       </c>
-      <c r="N29">
+      <c r="P29">
         <v>78.494008300000004</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="55"/>
-      <c r="B30" s="60"/>
+    <row r="30" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="53"/>
+      <c r="B30" s="47"/>
       <c r="C30">
         <v>4</v>
       </c>
@@ -3825,19 +4438,21 @@
       <c r="H30" s="33">
         <v>72.462500500000004</v>
       </c>
-      <c r="J30">
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="L30">
         <v>192.90137920000001</v>
       </c>
-      <c r="L30">
+      <c r="N30">
         <v>66.748610299999996</v>
       </c>
-      <c r="N30">
+      <c r="P30">
         <v>73.773346900000007</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A31" s="55"/>
-      <c r="B31" s="60"/>
+    <row r="31" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="53"/>
+      <c r="B31" s="47"/>
       <c r="C31">
         <v>5</v>
       </c>
@@ -3852,19 +4467,21 @@
       <c r="H31" s="33">
         <v>72.456881800000005</v>
       </c>
-      <c r="J31">
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
+      <c r="L31">
         <v>704.56541179999999</v>
       </c>
-      <c r="L31">
+      <c r="N31">
         <v>66.651984799999994</v>
       </c>
-      <c r="N31">
+      <c r="P31">
         <v>86.556363700000006</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="55"/>
-      <c r="B32" s="60"/>
+    <row r="32" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="53"/>
+      <c r="B32" s="47"/>
       <c r="C32">
         <v>6</v>
       </c>
@@ -3879,19 +4496,21 @@
       <c r="H32" s="33">
         <v>72.692214000000007</v>
       </c>
-      <c r="J32">
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+      <c r="L32">
         <v>1577.8932976000001</v>
       </c>
-      <c r="L32">
+      <c r="N32">
         <v>66.842946999999995</v>
       </c>
-      <c r="N32">
+      <c r="P32">
         <v>81.386483100000007</v>
       </c>
     </row>
-    <row r="33" spans="1:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="55"/>
-      <c r="B33" s="60"/>
+    <row r="33" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="53"/>
+      <c r="B33" s="47"/>
       <c r="C33">
         <v>7</v>
       </c>
@@ -3906,19 +4525,21 @@
       <c r="H33" s="33">
         <v>72.928730299999998</v>
       </c>
-      <c r="J33">
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="L33">
         <v>249.1666912</v>
       </c>
-      <c r="L33">
+      <c r="N33">
         <v>68.512321200000002</v>
       </c>
-      <c r="N33">
+      <c r="P33">
         <v>88.930410199999997</v>
       </c>
     </row>
-    <row r="34" spans="1:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="55"/>
-      <c r="B34" s="60"/>
+    <row r="34" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="53"/>
+      <c r="B34" s="47"/>
       <c r="C34">
         <v>8</v>
       </c>
@@ -3933,19 +4554,21 @@
       <c r="H34" s="33">
         <v>70.194977100000003</v>
       </c>
-      <c r="J34">
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="L34">
         <v>485.6161606</v>
       </c>
-      <c r="L34">
+      <c r="N34">
         <v>70.594743300000005</v>
       </c>
-      <c r="N34">
+      <c r="P34">
         <v>81.324767699999995</v>
       </c>
     </row>
-    <row r="35" spans="1:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="55"/>
-      <c r="B35" s="60"/>
+    <row r="35" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="53"/>
+      <c r="B35" s="47"/>
       <c r="C35">
         <v>9</v>
       </c>
@@ -3960,19 +4583,21 @@
       <c r="H35" s="33">
         <v>72.091733000000005</v>
       </c>
-      <c r="J35">
+      <c r="I35" s="33"/>
+      <c r="J35" s="33"/>
+      <c r="L35">
         <v>1728.0716404</v>
       </c>
-      <c r="L35">
+      <c r="N35">
         <v>69.713253100000003</v>
       </c>
-      <c r="N35">
+      <c r="P35">
         <v>84.404220199999997</v>
       </c>
     </row>
-    <row r="36" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="55"/>
-      <c r="B36" s="61"/>
+    <row r="36" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="53"/>
+      <c r="B36" s="48"/>
       <c r="C36">
         <v>10</v>
       </c>
@@ -3986,59 +4611,75 @@
       <c r="H36" s="31">
         <v>74.820149400000005</v>
       </c>
-      <c r="J36">
+      <c r="I36" s="31"/>
+      <c r="J36" s="31"/>
+      <c r="L36">
         <v>399.93897140000001</v>
       </c>
-      <c r="L36">
+      <c r="N36">
         <v>71.220160899999996</v>
       </c>
-      <c r="N36">
+      <c r="P36">
         <v>78.9069042</v>
       </c>
-      <c r="S36" s="57" t="s">
+      <c r="W36" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="T36" s="57"/>
-      <c r="U36" s="57"/>
-      <c r="V36" s="57"/>
-      <c r="X36" s="57" t="s">
+      <c r="X36" s="51"/>
+      <c r="Y36" s="51"/>
+      <c r="Z36" s="51"/>
+      <c r="AB36" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="Y36" s="57"/>
-      <c r="Z36" s="57"/>
-      <c r="AA36" s="57"/>
-      <c r="AC36" s="58" t="s">
+      <c r="AC36" s="51"/>
+      <c r="AD36" s="51"/>
+      <c r="AE36" s="51"/>
+      <c r="AG36" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="AD36" s="58"/>
-      <c r="AE36" s="58"/>
-      <c r="AF36" s="58"/>
-    </row>
-    <row r="37" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="55"/>
+      <c r="AH36" s="50"/>
+      <c r="AI36" s="50"/>
+      <c r="AJ36" s="50"/>
+      <c r="AL36" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="AM36" s="50"/>
+      <c r="AN36" s="50"/>
+      <c r="AO36" s="50"/>
+    </row>
+    <row r="37" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="53"/>
       <c r="F37" s="31"/>
       <c r="G37" s="31"/>
       <c r="H37" s="31"/>
-      <c r="T37" s="38"/>
-      <c r="U37" s="38"/>
-      <c r="V37" s="38" t="s">
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="X37" s="38"/>
+      <c r="Y37" s="38"/>
+      <c r="Z37" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="Y37" s="38"/>
-      <c r="Z37" s="38"/>
-      <c r="AA37" s="38" t="s">
+      <c r="AC37" s="38"/>
+      <c r="AD37" s="38"/>
+      <c r="AE37" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="AC37" s="39"/>
-      <c r="AD37" s="41"/>
-      <c r="AE37" s="41"/>
-      <c r="AF37" s="41" t="s">
+      <c r="AG37" s="39"/>
+      <c r="AH37" s="41"/>
+      <c r="AI37" s="41"/>
+      <c r="AJ37" s="41" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="38" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="55"/>
-      <c r="B38" s="59" t="s">
+      <c r="AL37" s="39"/>
+      <c r="AM37" s="41"/>
+      <c r="AN37" s="41"/>
+      <c r="AO37" s="41" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="1:41" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" s="53"/>
+      <c r="B38" s="46" t="s">
         <v>33</v>
       </c>
       <c r="C38">
@@ -4055,54 +4696,68 @@
       <c r="H38" s="33">
         <v>66.098048399999996</v>
       </c>
-      <c r="J38">
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
+      <c r="L38">
         <v>272.02645749999999</v>
       </c>
-      <c r="L38">
+      <c r="N38">
         <v>724.32734670000002</v>
       </c>
-      <c r="N38">
+      <c r="P38">
         <v>66.911195300000003</v>
       </c>
-      <c r="S38" s="37" t="s">
+      <c r="W38" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="T38" s="10">
-        <f>AVERAGE(D7:D67,J7:J67)</f>
+      <c r="X38" s="10">
+        <f>AVERAGE(D7:D67,L7:L67)</f>
         <v>546.31773920583328</v>
       </c>
-      <c r="V38" s="26">
-        <f>TIME(,,T38)</f>
+      <c r="Z38" s="26">
+        <f>TIME(,,X38)</f>
         <v>6.3194444444444444E-3</v>
       </c>
-      <c r="X38" s="37" t="s">
+      <c r="AB38" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="Y38" s="10">
-        <f>AVERAGE(F7:F67,L7:L67)</f>
+      <c r="AC38" s="10">
+        <f>AVERAGE(F7:F67,N7:N67)</f>
         <v>374.52974976499985</v>
       </c>
-      <c r="Z38" s="10"/>
-      <c r="AA38" s="26">
-        <f>TIME(,,Y38)</f>
+      <c r="AD38" s="10"/>
+      <c r="AE38" s="26">
+        <f>TIME(,,AC38)</f>
         <v>4.3287037037037035E-3</v>
       </c>
-      <c r="AC38" s="40" t="s">
+      <c r="AG38" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="AD38" s="42">
-        <f>AVERAGE(H7:H67,N7:N67)</f>
+      <c r="AH38" s="42">
+        <f>AVERAGE(H7:H67,P7:P67)</f>
         <v>96.597025105833339</v>
       </c>
-      <c r="AE38" s="42"/>
-      <c r="AF38" s="43">
-        <f>TIME(,,AD38)</f>
+      <c r="AI38" s="42"/>
+      <c r="AJ38" s="43">
+        <f>TIME(,,AH38)</f>
         <v>1.1111111111111111E-3</v>
       </c>
-    </row>
-    <row r="39" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="55"/>
-      <c r="B39" s="60"/>
+      <c r="AL38" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM38" s="42" t="e">
+        <f>AVERAGE(J7:J67,R7:R67)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AN38" s="42"/>
+      <c r="AO38" s="43" t="e">
+        <f>TIME(,,AM38)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="39" spans="1:41" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="53"/>
+      <c r="B39" s="47"/>
       <c r="C39">
         <v>2</v>
       </c>
@@ -4117,54 +4772,68 @@
       <c r="H39" s="33">
         <v>61.709756200000001</v>
       </c>
-      <c r="J39">
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="L39">
         <v>271.00988949999999</v>
       </c>
-      <c r="L39">
+      <c r="N39">
         <v>516.50285350000001</v>
       </c>
-      <c r="N39">
+      <c r="P39">
         <v>64.378168500000001</v>
       </c>
-      <c r="S39" s="37" t="s">
+      <c r="W39" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="T39" s="10">
-        <f>MIN(D7:D67,J7:J67)</f>
+      <c r="X39" s="10">
+        <f>MIN(D7:D67,L7:L67)</f>
         <v>62.1611634</v>
       </c>
-      <c r="V39" s="26">
-        <f t="shared" ref="V39:V41" si="1">TIME(,,T39)</f>
+      <c r="Z39" s="26">
+        <f t="shared" ref="Z39:Z41" si="1">TIME(,,X39)</f>
         <v>7.1759259259259259E-4</v>
       </c>
-      <c r="X39" s="37" t="s">
+      <c r="AB39" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="Y39" s="10">
-        <f>MIN(F7:F67,L7:L67)</f>
+      <c r="AC39" s="10">
+        <f>MIN(F7:F67,N7:N67)</f>
         <v>59.023810400000002</v>
       </c>
-      <c r="Z39" s="10"/>
-      <c r="AA39" s="26">
-        <f t="shared" ref="AA39:AA41" si="2">TIME(,,Y39)</f>
+      <c r="AD39" s="10"/>
+      <c r="AE39" s="26">
+        <f t="shared" ref="AE39:AE41" si="2">TIME(,,AC39)</f>
         <v>6.8287037037037036E-4</v>
       </c>
-      <c r="AC39" s="40" t="s">
+      <c r="AG39" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="AD39" s="42">
-        <f>MIN(H7:H67,N7:N67)</f>
+      <c r="AH39" s="42">
+        <f>MIN(H7:H67,P7:P67)</f>
         <v>61.305089099999996</v>
       </c>
-      <c r="AE39" s="42"/>
-      <c r="AF39" s="43">
-        <f t="shared" ref="AF39:AF41" si="3">TIME(,,AD39)</f>
+      <c r="AI39" s="42"/>
+      <c r="AJ39" s="43">
+        <f t="shared" ref="AJ39:AJ41" si="3">TIME(,,AH39)</f>
         <v>7.0601851851851847E-4</v>
       </c>
-    </row>
-    <row r="40" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="55"/>
-      <c r="B40" s="60"/>
+      <c r="AL39" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM39" s="42">
+        <f>MIN(J7:J67,R7:R67)</f>
+        <v>0</v>
+      </c>
+      <c r="AN39" s="42"/>
+      <c r="AO39" s="43">
+        <f t="shared" ref="AO39:AO41" si="4">TIME(,,AM39)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:41" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" s="53"/>
+      <c r="B40" s="47"/>
       <c r="C40">
         <v>3</v>
       </c>
@@ -4179,54 +4848,68 @@
       <c r="H40" s="33">
         <v>188.01339630000001</v>
       </c>
-      <c r="J40">
+      <c r="I40" s="33"/>
+      <c r="J40" s="33"/>
+      <c r="L40">
         <v>726.76372800000001</v>
       </c>
-      <c r="L40">
+      <c r="N40">
         <v>627.01927850000004</v>
       </c>
-      <c r="N40">
+      <c r="P40">
         <v>66.806464399999996</v>
       </c>
-      <c r="S40" s="37" t="s">
+      <c r="W40" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="T40" s="10">
-        <f>MAX(D7:D67,J7:J67)</f>
+      <c r="X40" s="10">
+        <f>MAX(D7:D67,L7:L67)</f>
         <v>2702.1846860999999</v>
       </c>
-      <c r="V40" s="26">
+      <c r="Z40" s="26">
         <f t="shared" si="1"/>
         <v>3.1273148148148147E-2</v>
       </c>
-      <c r="X40" s="37" t="s">
+      <c r="AB40" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="Y40" s="10">
-        <f>MAX(F7:F67,L7:L67)</f>
+      <c r="AC40" s="10">
+        <f>MAX(F7:F67,N7:N67)</f>
         <v>7218.0189136999998</v>
       </c>
-      <c r="Z40" s="10"/>
-      <c r="AA40" s="26">
+      <c r="AD40" s="10"/>
+      <c r="AE40" s="26">
         <f t="shared" si="2"/>
         <v>8.3541666666666667E-2</v>
       </c>
-      <c r="AC40" s="40" t="s">
+      <c r="AG40" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="AD40" s="42">
-        <f>MAX(H7:H67,N7:N67)</f>
+      <c r="AH40" s="42">
+        <f>MAX(H7:H67,P7:P67)</f>
         <v>456.90458919999998</v>
       </c>
-      <c r="AE40" s="42"/>
-      <c r="AF40" s="43">
+      <c r="AI40" s="42"/>
+      <c r="AJ40" s="43">
         <f t="shared" si="3"/>
         <v>5.2777777777777779E-3</v>
       </c>
-    </row>
-    <row r="41" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="55"/>
-      <c r="B41" s="60"/>
+      <c r="AL40" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM40" s="42">
+        <f>MAX(J7:J67,R7:R67)</f>
+        <v>0</v>
+      </c>
+      <c r="AN40" s="42"/>
+      <c r="AO40" s="43">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:41" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="53"/>
+      <c r="B41" s="47"/>
       <c r="C41">
         <v>4</v>
       </c>
@@ -4241,54 +4924,68 @@
       <c r="H41" s="33">
         <v>248.90476090000001</v>
       </c>
-      <c r="J41">
+      <c r="I41" s="33"/>
+      <c r="J41" s="33"/>
+      <c r="L41">
         <v>540.2707183</v>
       </c>
-      <c r="L41">
+      <c r="N41">
         <v>203.78538520000001</v>
       </c>
-      <c r="N41">
+      <c r="P41">
         <v>383.47915019999999</v>
       </c>
-      <c r="S41" s="37" t="s">
+      <c r="W41" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="T41" s="10">
-        <f>STDEV(D7:D67,J7:J67)</f>
+      <c r="X41" s="10">
+        <f>STDEV(D7:D67,L7:L67)</f>
         <v>503.77851799898792</v>
       </c>
-      <c r="V41" s="26">
+      <c r="Z41" s="26">
         <f t="shared" si="1"/>
         <v>5.8217592592592592E-3</v>
       </c>
-      <c r="X41" s="37" t="s">
+      <c r="AB41" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="Y41" s="10">
-        <f>STDEV(F7:F67,L7:L67)</f>
+      <c r="AC41" s="10">
+        <f>STDEV(F7:F67,N7:N67)</f>
         <v>777.67428783235016</v>
       </c>
-      <c r="Z41" s="10"/>
-      <c r="AA41" s="26">
+      <c r="AD41" s="10"/>
+      <c r="AE41" s="26">
         <f t="shared" si="2"/>
         <v>8.9930555555555562E-3</v>
       </c>
-      <c r="AC41" s="40" t="s">
+      <c r="AG41" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="AD41" s="42">
-        <f>STDEV(H7:H67,N7:N67)</f>
+      <c r="AH41" s="42">
+        <f>STDEV(H7:H67,P7:P67)</f>
         <v>70.136006265364259</v>
       </c>
-      <c r="AE41" s="42"/>
-      <c r="AF41" s="43">
+      <c r="AI41" s="42"/>
+      <c r="AJ41" s="43">
         <f t="shared" si="3"/>
         <v>8.1018518518518516E-4</v>
       </c>
-    </row>
-    <row r="42" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="55"/>
-      <c r="B42" s="60"/>
+      <c r="AL41" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM41" s="42" t="e">
+        <f>STDEV(J7:J67,R7:R67)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AN41" s="42"/>
+      <c r="AO41" s="43" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:41" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" s="53"/>
+      <c r="B42" s="47"/>
       <c r="C42">
         <v>5</v>
       </c>
@@ -4303,19 +5000,21 @@
       <c r="H42" s="33">
         <v>61.305089099999996</v>
       </c>
-      <c r="J42">
+      <c r="I42" s="33"/>
+      <c r="J42" s="33"/>
+      <c r="L42">
         <v>64.362414000000001</v>
       </c>
-      <c r="L42">
+      <c r="N42">
         <v>2114.0303715999999</v>
       </c>
-      <c r="N42">
+      <c r="P42">
         <v>62.552345799999998</v>
       </c>
     </row>
-    <row r="43" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A43" s="55"/>
-      <c r="B43" s="60"/>
+    <row r="43" spans="1:41" ht="16" x14ac:dyDescent="0.2">
+      <c r="A43" s="53"/>
+      <c r="B43" s="47"/>
       <c r="C43">
         <v>6</v>
       </c>
@@ -4330,19 +5029,21 @@
       <c r="H43" s="33">
         <v>310.8813571</v>
       </c>
-      <c r="J43">
+      <c r="I43" s="33"/>
+      <c r="J43" s="33"/>
+      <c r="L43">
         <v>64.178668500000001</v>
       </c>
-      <c r="L43">
+      <c r="N43">
         <v>363.88059229999999</v>
       </c>
-      <c r="N43">
+      <c r="P43">
         <v>66.208508899999998</v>
       </c>
     </row>
-    <row r="44" spans="1:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="55"/>
-      <c r="B44" s="60"/>
+    <row r="44" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="53"/>
+      <c r="B44" s="47"/>
       <c r="C44">
         <v>7</v>
       </c>
@@ -4357,35 +5058,43 @@
       <c r="H44" s="33">
         <v>185.79902559999999</v>
       </c>
-      <c r="J44">
+      <c r="I44" s="33"/>
+      <c r="J44" s="33"/>
+      <c r="L44">
         <v>128.72593209999999</v>
       </c>
-      <c r="L44">
+      <c r="N44">
         <v>2376.7919195999998</v>
       </c>
-      <c r="N44">
+      <c r="P44">
         <v>132.51080440000001</v>
       </c>
-      <c r="S44" s="37"/>
-      <c r="T44" s="37"/>
-      <c r="U44" s="37"/>
-      <c r="V44" s="37"/>
-      <c r="X44" s="57" t="s">
+      <c r="W44" s="37"/>
+      <c r="X44" s="37"/>
+      <c r="Y44" s="37"/>
+      <c r="Z44" s="37"/>
+      <c r="AB44" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="Y44" s="57"/>
-      <c r="Z44" s="57"/>
-      <c r="AA44" s="57"/>
-      <c r="AC44" s="58" t="s">
+      <c r="AC44" s="51"/>
+      <c r="AD44" s="51"/>
+      <c r="AE44" s="51"/>
+      <c r="AG44" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="AD44" s="58"/>
-      <c r="AE44" s="58"/>
-      <c r="AF44" s="58"/>
-    </row>
-    <row r="45" spans="1:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="55"/>
-      <c r="B45" s="60"/>
+      <c r="AH44" s="50"/>
+      <c r="AI44" s="50"/>
+      <c r="AJ44" s="50"/>
+      <c r="AL44" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="AM44" s="50"/>
+      <c r="AN44" s="50"/>
+      <c r="AO44" s="50"/>
+    </row>
+    <row r="45" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="53"/>
+      <c r="B45" s="47"/>
       <c r="C45">
         <v>8</v>
       </c>
@@ -4400,33 +5109,41 @@
       <c r="H45" s="33">
         <v>61.944671700000001</v>
       </c>
-      <c r="J45">
+      <c r="I45" s="33"/>
+      <c r="J45" s="33"/>
+      <c r="L45">
         <v>1315.3337303000001</v>
       </c>
-      <c r="L45">
+      <c r="N45">
         <v>7218.0189136999998</v>
       </c>
-      <c r="N45">
+      <c r="P45">
         <v>67.6577901</v>
       </c>
-      <c r="T45" s="38"/>
-      <c r="U45" s="38"/>
-      <c r="V45" s="38"/>
+      <c r="X45" s="38"/>
       <c r="Y45" s="38"/>
       <c r="Z45" s="38"/>
-      <c r="AA45" s="38" t="s">
+      <c r="AC45" s="38"/>
+      <c r="AD45" s="38"/>
+      <c r="AE45" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="AC45" s="39"/>
-      <c r="AD45" s="41"/>
-      <c r="AE45" s="41"/>
-      <c r="AF45" s="41" t="s">
+      <c r="AG45" s="39"/>
+      <c r="AH45" s="41"/>
+      <c r="AI45" s="41"/>
+      <c r="AJ45" s="41" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="46" spans="1:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="55"/>
-      <c r="B46" s="60"/>
+      <c r="AL45" s="39"/>
+      <c r="AM45" s="41"/>
+      <c r="AN45" s="41"/>
+      <c r="AO45" s="41" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="53"/>
+      <c r="B46" s="47"/>
       <c r="C46">
         <v>9</v>
       </c>
@@ -4441,45 +5158,59 @@
       <c r="H46" s="33">
         <v>62.026653699999997</v>
       </c>
-      <c r="J46">
+      <c r="I46" s="33"/>
+      <c r="J46" s="33"/>
+      <c r="L46">
         <v>1165.9940234000001</v>
       </c>
-      <c r="L46">
+      <c r="N46">
         <v>776.33947339999997</v>
       </c>
-      <c r="N46">
+      <c r="P46">
         <v>65.501620900000006</v>
       </c>
-      <c r="S46" s="37"/>
-      <c r="V46" s="26"/>
-      <c r="X46" s="37" t="s">
+      <c r="W46" s="37"/>
+      <c r="Z46" s="26"/>
+      <c r="AB46" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="Y46" s="10">
-        <f>AVERAGE(F74:F134,L74:L134)</f>
+      <c r="AC46" s="10">
+        <f>AVERAGE(F74:F134,N74:N134)</f>
         <v>504.82828081192645</v>
       </c>
-      <c r="Z46" s="10"/>
-      <c r="AA46" s="26">
-        <f>TIME(,,Y46)</f>
+      <c r="AD46" s="10"/>
+      <c r="AE46" s="26">
+        <f>TIME(,,AC46)</f>
         <v>5.8333333333333336E-3</v>
       </c>
-      <c r="AC46" s="40" t="s">
+      <c r="AG46" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="AD46" s="42">
-        <f>AVERAGE(H74:H134,N74:N134)</f>
+      <c r="AH46" s="42">
+        <f>AVERAGE(H74:H134,P74:P134)</f>
         <v>248.11779057499996</v>
       </c>
-      <c r="AE46" s="42"/>
-      <c r="AF46" s="43">
-        <f>TIME(,,AD46)</f>
+      <c r="AI46" s="42"/>
+      <c r="AJ46" s="43">
+        <f>TIME(,,AH46)</f>
         <v>2.8703703703703703E-3</v>
       </c>
-    </row>
-    <row r="47" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="55"/>
-      <c r="B47" s="61"/>
+      <c r="AL46" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM46" s="42">
+        <f>AVERAGE(H74:H134,R74:R134)</f>
+        <v>133.6580019466667</v>
+      </c>
+      <c r="AN46" s="42"/>
+      <c r="AO46" s="43">
+        <f>TIME(,,AM46)</f>
+        <v>1.5393518518518519E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="53"/>
+      <c r="B47" s="48"/>
       <c r="C47">
         <v>10</v>
       </c>
@@ -4493,45 +5224,59 @@
       <c r="H47" s="31">
         <v>452.67738200000002</v>
       </c>
-      <c r="J47">
+      <c r="I47" s="31"/>
+      <c r="J47" s="31"/>
+      <c r="L47">
         <v>1281.4269638999999</v>
       </c>
-      <c r="L47">
+      <c r="N47">
         <v>258.84629430000001</v>
       </c>
-      <c r="N47">
+      <c r="P47">
         <v>65.377549599999995</v>
       </c>
-      <c r="S47" s="37"/>
-      <c r="V47" s="26"/>
-      <c r="X47" s="37" t="s">
+      <c r="W47" s="37"/>
+      <c r="Z47" s="26"/>
+      <c r="AB47" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="Y47" s="10">
-        <f>MIN(F74:F134,L74:L134)</f>
+      <c r="AC47" s="10">
+        <f>MIN(F74:F134,N74:N134)</f>
         <v>64.483929500000002</v>
       </c>
-      <c r="Z47" s="10"/>
-      <c r="AA47" s="26">
-        <f t="shared" ref="AA47:AA49" si="4">TIME(,,Y47)</f>
+      <c r="AD47" s="10"/>
+      <c r="AE47" s="26">
+        <f t="shared" ref="AE47:AE49" si="5">TIME(,,AC47)</f>
         <v>7.407407407407407E-4</v>
       </c>
-      <c r="AC47" s="40" t="s">
+      <c r="AG47" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="AD47" s="42">
-        <f>MIN(H74:H134,N74:N134)</f>
+      <c r="AH47" s="42">
+        <f>MIN(H74:H134,P74:P134)</f>
         <v>64.796429700000004</v>
       </c>
-      <c r="AE47" s="42"/>
-      <c r="AF47" s="43">
-        <f t="shared" ref="AF47:AF49" si="5">TIME(,,AD47)</f>
+      <c r="AI47" s="42"/>
+      <c r="AJ47" s="43">
+        <f t="shared" ref="AJ47:AJ49" si="6">TIME(,,AH47)</f>
         <v>7.407407407407407E-4</v>
       </c>
-    </row>
-    <row r="48" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="55"/>
-      <c r="B48" s="59" t="s">
+      <c r="AL47" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM47" s="42">
+        <f>MIN(J74:J134,R74:R134)</f>
+        <v>49.9163</v>
+      </c>
+      <c r="AN47" s="42"/>
+      <c r="AO47" s="43">
+        <f t="shared" ref="AO47:AO49" si="7">TIME(,,AM47)</f>
+        <v>5.6712962962962967E-4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:41" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" s="53"/>
+      <c r="B48" s="46" t="s">
         <v>42</v>
       </c>
       <c r="C48">
@@ -4548,45 +5293,59 @@
       <c r="H48" s="33">
         <v>66.010996500000005</v>
       </c>
-      <c r="J48">
+      <c r="I48" s="33"/>
+      <c r="J48" s="33"/>
+      <c r="L48">
         <v>1067.6859191999999</v>
       </c>
-      <c r="L48">
+      <c r="N48">
         <v>441.2645364</v>
       </c>
-      <c r="N48">
+      <c r="P48">
         <v>75.916192300000006</v>
       </c>
-      <c r="S48" s="37"/>
-      <c r="V48" s="26"/>
-      <c r="X48" s="37" t="s">
+      <c r="W48" s="37"/>
+      <c r="Z48" s="26"/>
+      <c r="AB48" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="Y48" s="10">
-        <f>MAX(F74:F134,L74:L134)</f>
+      <c r="AC48" s="10">
+        <f>MAX(F74:F134,N74:N134)</f>
         <v>3419.3379930999999</v>
       </c>
-      <c r="Z48" s="10"/>
-      <c r="AA48" s="26">
-        <f t="shared" si="4"/>
+      <c r="AD48" s="10"/>
+      <c r="AE48" s="26">
+        <f t="shared" si="5"/>
         <v>3.9571759259259258E-2</v>
       </c>
-      <c r="AC48" s="40" t="s">
+      <c r="AG48" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="AD48" s="42">
-        <f>MAX(H74:H134,N74:N134)</f>
+      <c r="AH48" s="42">
+        <f>MAX(H74:H134,P74:P134)</f>
         <v>2129.4957175999998</v>
       </c>
-      <c r="AE48" s="42"/>
-      <c r="AF48" s="43">
-        <f t="shared" si="5"/>
+      <c r="AI48" s="42"/>
+      <c r="AJ48" s="43">
+        <f t="shared" si="6"/>
         <v>2.4641203703703703E-2</v>
       </c>
-    </row>
-    <row r="49" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A49" s="55"/>
-      <c r="B49" s="60"/>
+      <c r="AL48" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM48" s="42">
+        <f>MAX(J74:J134,R74:R134)</f>
+        <v>353.98700000000002</v>
+      </c>
+      <c r="AN48" s="42"/>
+      <c r="AO48" s="43">
+        <f t="shared" si="7"/>
+        <v>4.0856481481481481E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:41" ht="16" x14ac:dyDescent="0.2">
+      <c r="A49" s="53"/>
+      <c r="B49" s="47"/>
       <c r="C49">
         <v>2</v>
       </c>
@@ -4601,45 +5360,59 @@
       <c r="H49" s="33">
         <v>61.7772839</v>
       </c>
-      <c r="J49">
+      <c r="I49" s="33"/>
+      <c r="J49" s="33"/>
+      <c r="L49">
         <v>496.0932545</v>
       </c>
-      <c r="L49">
+      <c r="N49">
         <v>245.3121313</v>
       </c>
-      <c r="N49">
+      <c r="P49">
         <v>68.917741399999997</v>
       </c>
-      <c r="S49" s="37"/>
-      <c r="V49" s="26"/>
-      <c r="X49" s="37" t="s">
+      <c r="W49" s="37"/>
+      <c r="Z49" s="26"/>
+      <c r="AB49" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="Y49" s="10">
-        <f>STDEV(F74:F134,L74:L134)</f>
+      <c r="AC49" s="10">
+        <f>STDEV(F74:F134,N74:N134)</f>
         <v>597.31219328536656</v>
       </c>
-      <c r="Z49" s="10"/>
-      <c r="AA49" s="26">
-        <f t="shared" si="4"/>
+      <c r="AD49" s="10"/>
+      <c r="AE49" s="26">
+        <f t="shared" si="5"/>
         <v>6.9097222222222225E-3</v>
       </c>
-      <c r="AC49" s="40" t="s">
+      <c r="AG49" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="AD49" s="42">
-        <f>STDEV(H74:H134,N74:N134)</f>
+      <c r="AH49" s="42">
+        <f>STDEV(H74:H134,P74:P134)</f>
         <v>299.24178733784595</v>
       </c>
-      <c r="AE49" s="42"/>
-      <c r="AF49" s="43">
-        <f t="shared" si="5"/>
+      <c r="AI49" s="42"/>
+      <c r="AJ49" s="43">
+        <f t="shared" si="6"/>
         <v>3.460648148148148E-3</v>
       </c>
-    </row>
-    <row r="50" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="55"/>
-      <c r="B50" s="60"/>
+      <c r="AL49" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM49" s="42">
+        <f>STDEV(J74:J134,R74:R134)</f>
+        <v>34.253767070059197</v>
+      </c>
+      <c r="AN49" s="42"/>
+      <c r="AO49" s="43">
+        <f t="shared" si="7"/>
+        <v>3.9351851851851852E-4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:41" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="53"/>
+      <c r="B50" s="47"/>
       <c r="C50">
         <v>3</v>
       </c>
@@ -4654,19 +5427,21 @@
       <c r="H50" s="33">
         <v>62.869197700000001</v>
       </c>
-      <c r="J50">
+      <c r="I50" s="33"/>
+      <c r="J50" s="33"/>
+      <c r="L50">
         <v>2702.1846860999999</v>
       </c>
-      <c r="L50">
+      <c r="N50">
         <v>306.33084680000002</v>
       </c>
-      <c r="N50">
+      <c r="P50">
         <v>66.262496600000006</v>
       </c>
     </row>
-    <row r="51" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A51" s="55"/>
-      <c r="B51" s="60"/>
+    <row r="51" spans="1:41" ht="16" x14ac:dyDescent="0.2">
+      <c r="A51" s="53"/>
+      <c r="B51" s="47"/>
       <c r="C51">
         <v>4</v>
       </c>
@@ -4681,19 +5456,21 @@
       <c r="H51" s="33">
         <v>74.841529699999995</v>
       </c>
-      <c r="J51">
+      <c r="I51" s="33"/>
+      <c r="J51" s="33"/>
+      <c r="L51">
         <v>1368.3347223999999</v>
       </c>
-      <c r="L51">
+      <c r="N51">
         <v>185.0211382</v>
       </c>
-      <c r="N51">
+      <c r="P51">
         <v>65.344129800000005</v>
       </c>
     </row>
-    <row r="52" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A52" s="55"/>
-      <c r="B52" s="60"/>
+    <row r="52" spans="1:41" ht="16" x14ac:dyDescent="0.2">
+      <c r="A52" s="53"/>
+      <c r="B52" s="47"/>
       <c r="C52">
         <v>5</v>
       </c>
@@ -4708,19 +5485,21 @@
       <c r="H52" s="33">
         <v>65.391042400000003</v>
       </c>
-      <c r="J52">
+      <c r="I52" s="33"/>
+      <c r="J52" s="33"/>
+      <c r="L52">
         <v>122.9923916</v>
       </c>
-      <c r="L52">
+      <c r="N52">
         <v>121.817357</v>
       </c>
-      <c r="N52">
+      <c r="P52">
         <v>73.091260399999996</v>
       </c>
     </row>
-    <row r="53" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A53" s="55"/>
-      <c r="B53" s="60"/>
+    <row r="53" spans="1:41" ht="16" x14ac:dyDescent="0.2">
+      <c r="A53" s="53"/>
+      <c r="B53" s="47"/>
       <c r="C53">
         <v>6</v>
       </c>
@@ -4735,19 +5514,21 @@
       <c r="H53" s="33">
         <v>65.577701300000001</v>
       </c>
-      <c r="J53">
+      <c r="I53" s="33"/>
+      <c r="J53" s="33"/>
+      <c r="L53">
         <v>122.7202302</v>
       </c>
-      <c r="L53">
+      <c r="N53">
         <v>61.669807200000001</v>
       </c>
-      <c r="N53">
+      <c r="P53">
         <v>69.363162599999995</v>
       </c>
     </row>
-    <row r="54" spans="1:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="55"/>
-      <c r="B54" s="60"/>
+    <row r="54" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="53"/>
+      <c r="B54" s="47"/>
       <c r="C54">
         <v>7</v>
       </c>
@@ -4762,31 +5543,33 @@
       <c r="H54" s="33">
         <v>63.4976409</v>
       </c>
-      <c r="J54">
+      <c r="I54" s="33"/>
+      <c r="J54" s="33"/>
+      <c r="L54">
         <v>1246.0557417</v>
       </c>
-      <c r="L54">
+      <c r="N54">
         <v>244.8656919</v>
       </c>
-      <c r="N54">
+      <c r="P54">
         <v>66.126271200000005</v>
       </c>
-      <c r="S54" s="57" t="s">
+      <c r="W54" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="T54" s="57"/>
-      <c r="U54" s="57"/>
-      <c r="V54" s="57"/>
-      <c r="X54" s="57" t="s">
+      <c r="X54" s="51"/>
+      <c r="Y54" s="51"/>
+      <c r="Z54" s="51"/>
+      <c r="AB54" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="Y54" s="57"/>
-      <c r="Z54" s="57"/>
-      <c r="AA54" s="57"/>
-    </row>
-    <row r="55" spans="1:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="55"/>
-      <c r="B55" s="60"/>
+      <c r="AC54" s="51"/>
+      <c r="AD54" s="51"/>
+      <c r="AE54" s="51"/>
+    </row>
+    <row r="55" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="53"/>
+      <c r="B55" s="47"/>
       <c r="C55">
         <v>8</v>
       </c>
@@ -4801,29 +5584,31 @@
       <c r="H55" s="33">
         <v>64.229546999999997</v>
       </c>
-      <c r="J55">
+      <c r="I55" s="33"/>
+      <c r="J55" s="33"/>
+      <c r="L55">
         <v>123.4047491</v>
       </c>
-      <c r="L55">
+      <c r="N55">
         <v>61.419639699999998</v>
       </c>
-      <c r="N55">
+      <c r="P55">
         <v>64.695870499999998</v>
       </c>
-      <c r="T55" s="38"/>
-      <c r="U55" s="38"/>
-      <c r="V55" s="38" t="s">
+      <c r="X55" s="38"/>
+      <c r="Y55" s="38"/>
+      <c r="Z55" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="Y55" s="38"/>
-      <c r="Z55" s="38"/>
-      <c r="AA55" s="38" t="s">
+      <c r="AC55" s="38"/>
+      <c r="AD55" s="38"/>
+      <c r="AE55" s="38" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="56" spans="1:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="55"/>
-      <c r="B56" s="60"/>
+    <row r="56" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="53"/>
+      <c r="B56" s="47"/>
       <c r="C56">
         <v>9</v>
       </c>
@@ -4838,42 +5623,44 @@
       <c r="H56" s="33">
         <v>63.266840199999997</v>
       </c>
-      <c r="J56">
+      <c r="I56" s="33"/>
+      <c r="J56" s="33"/>
+      <c r="L56">
         <v>434.81144430000001</v>
       </c>
-      <c r="L56">
+      <c r="N56">
         <v>61.638997500000002</v>
       </c>
-      <c r="N56">
+      <c r="P56">
         <v>66.252286600000005</v>
       </c>
-      <c r="S56" s="37" t="s">
+      <c r="W56" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="T56" s="10">
-        <f>AVERAGE(D7:H67,F74:H134)</f>
-        <v>338.24720364499984</v>
-      </c>
-      <c r="V56" s="26">
-        <f>TIME(,,T56)</f>
-        <v>3.9120370370370368E-3</v>
-      </c>
-      <c r="X56" s="37" t="s">
+      <c r="X56" s="10">
+        <f>AVERAGE(D7:J67,F74:J134)</f>
+        <v>291.95593470416668</v>
+      </c>
+      <c r="Z56" s="26">
+        <f>TIME(,,X56)</f>
+        <v>3.3680555555555556E-3</v>
+      </c>
+      <c r="AB56" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="Y56" s="10">
-        <f>AVERAGE(J7:N67,J74:N103,L105:N134)</f>
-        <v>364.77369575501712</v>
-      </c>
-      <c r="Z56" s="10"/>
-      <c r="AA56" s="26">
-        <f>TIME(,,Y56)</f>
-        <v>4.2129629629629626E-3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="55"/>
-      <c r="B57" s="61"/>
+      <c r="AC56" s="10">
+        <f>AVERAGE(L7:R67,N74:R103,N105:R134)</f>
+        <v>311.41033659942678</v>
+      </c>
+      <c r="AD56" s="10"/>
+      <c r="AE56" s="26">
+        <f>TIME(,,AC56)</f>
+        <v>3.5995370370370369E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="53"/>
+      <c r="B57" s="48"/>
       <c r="C57">
         <v>10</v>
       </c>
@@ -4887,42 +5674,44 @@
       <c r="H57" s="31">
         <v>62.7056605</v>
       </c>
-      <c r="J57">
+      <c r="I57" s="31"/>
+      <c r="J57" s="31"/>
+      <c r="L57">
         <v>1426.1018938</v>
       </c>
-      <c r="L57">
+      <c r="N57">
         <v>122.74415930000001</v>
       </c>
-      <c r="N57">
+      <c r="P57">
         <v>65.3028932</v>
       </c>
-      <c r="S57" s="37" t="s">
+      <c r="W57" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="T57" s="10">
-        <f>MIN(D7:H67,F74:H134)</f>
-        <v>59.023810400000002</v>
-      </c>
-      <c r="V57" s="26">
-        <f t="shared" ref="V57:V59" si="6">TIME(,,T57)</f>
-        <v>6.8287037037037036E-4</v>
-      </c>
-      <c r="X57" s="37" t="s">
+      <c r="X57" s="10">
+        <f>MIN(D7:J67,F74:J134)</f>
+        <v>50.256300000000003</v>
+      </c>
+      <c r="Z57" s="26">
+        <f t="shared" ref="Z57:Z59" si="8">TIME(,,X57)</f>
+        <v>5.7870370370370367E-4</v>
+      </c>
+      <c r="AB57" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="Y57" s="10">
-        <f>MIN(J7:N67,J74:N103,L105:N134)</f>
-        <v>61.419639699999998</v>
-      </c>
-      <c r="Z57" s="10"/>
-      <c r="AA57" s="26">
-        <f t="shared" ref="AA57:AA59" si="7">TIME(,,Y57)</f>
-        <v>7.0601851851851847E-4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A58" s="55"/>
-      <c r="B58" s="59" t="s">
+      <c r="AC57" s="10">
+        <f>MIN(L7:R67,N74:R103,N105:R134)</f>
+        <v>49.9163</v>
+      </c>
+      <c r="AD57" s="10"/>
+      <c r="AE57" s="26">
+        <f t="shared" ref="AE57:AE59" si="9">TIME(,,AC57)</f>
+        <v>5.6712962962962967E-4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:41" ht="16" x14ac:dyDescent="0.2">
+      <c r="A58" s="53"/>
+      <c r="B58" s="46" t="s">
         <v>48</v>
       </c>
       <c r="C58">
@@ -4939,42 +5728,43 @@
       <c r="H58" s="33">
         <v>77.070805199999995</v>
       </c>
-      <c r="J58">
+      <c r="I58" s="33"/>
+      <c r="L58">
         <v>66.247412199999999</v>
       </c>
-      <c r="L58">
+      <c r="N58">
         <v>206.059055</v>
       </c>
-      <c r="N58">
+      <c r="P58">
         <v>95.839778699999997</v>
       </c>
-      <c r="S58" s="37" t="s">
+      <c r="W58" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="T58" s="10">
-        <f>MAX(D7:H67,F74:H134)</f>
+      <c r="X58" s="10">
+        <f>MAX(D7:J67,F74:J134)</f>
         <v>2543.6004963999999</v>
       </c>
-      <c r="V58" s="26">
-        <f t="shared" si="6"/>
+      <c r="Z58" s="26">
+        <f t="shared" si="8"/>
         <v>2.943287037037037E-2</v>
       </c>
-      <c r="X58" s="37" t="s">
+      <c r="AB58" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="Y58" s="10">
-        <f>MAX(J7:N67,J74:N103,L105:N134)</f>
+      <c r="AC58" s="10">
+        <f>MAX(L7:R67,N74:R103,N105:R134)</f>
         <v>7218.0189136999998</v>
       </c>
-      <c r="Z58" s="10"/>
-      <c r="AA58" s="26">
-        <f t="shared" si="7"/>
+      <c r="AD58" s="10"/>
+      <c r="AE58" s="26">
+        <f t="shared" si="9"/>
         <v>8.3541666666666667E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A59" s="55"/>
-      <c r="B59" s="60"/>
+    <row r="59" spans="1:41" ht="16" x14ac:dyDescent="0.2">
+      <c r="A59" s="53"/>
+      <c r="B59" s="47"/>
       <c r="C59">
         <v>2</v>
       </c>
@@ -4989,42 +5779,43 @@
       <c r="H59" s="33">
         <v>67.473517299999997</v>
       </c>
-      <c r="J59">
+      <c r="I59" s="33"/>
+      <c r="L59">
         <v>386.56979080000002</v>
       </c>
-      <c r="L59">
+      <c r="N59">
         <v>61.946001899999999</v>
       </c>
-      <c r="N59">
+      <c r="P59">
         <v>110.28815590000001</v>
       </c>
-      <c r="S59" s="37" t="s">
+      <c r="W59" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="T59" s="10">
-        <f>STDEV(D7:H67,F74:H134)</f>
-        <v>394.80492299000736</v>
-      </c>
-      <c r="V59" s="26">
-        <f t="shared" si="6"/>
-        <v>4.5601851851851853E-3</v>
-      </c>
-      <c r="X59" s="37" t="s">
+      <c r="X59" s="10">
+        <f>STDEV(D7:J67,F74:J134)</f>
+        <v>375.39820027214569</v>
+      </c>
+      <c r="Z59" s="26">
+        <f t="shared" si="8"/>
+        <v>4.340277777777778E-3</v>
+      </c>
+      <c r="AB59" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="Y59" s="10">
-        <f>STDEV(J7:N67,J74:N103,L105:N134)</f>
-        <v>649.50524414137317</v>
-      </c>
-      <c r="Z59" s="10"/>
-      <c r="AA59" s="26">
-        <f t="shared" si="7"/>
-        <v>7.5115740740740742E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A60" s="55"/>
-      <c r="B60" s="60"/>
+      <c r="AC59" s="10">
+        <f>STDEV(L7:R67,N74:R103,N105:R134)</f>
+        <v>602.41664910795362</v>
+      </c>
+      <c r="AD59" s="10"/>
+      <c r="AE59" s="26">
+        <f t="shared" si="9"/>
+        <v>6.9675925925925929E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:41" ht="16" x14ac:dyDescent="0.2">
+      <c r="A60" s="53"/>
+      <c r="B60" s="47"/>
       <c r="C60">
         <v>3</v>
       </c>
@@ -5039,19 +5830,20 @@
       <c r="H60" s="33">
         <v>63.312723699999999</v>
       </c>
-      <c r="J60">
+      <c r="I60" s="33"/>
+      <c r="L60">
         <v>686.01692530000003</v>
       </c>
-      <c r="L60">
+      <c r="N60">
         <v>64.429386699999995</v>
       </c>
-      <c r="N60">
+      <c r="P60">
         <v>116.1841663</v>
       </c>
     </row>
-    <row r="61" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A61" s="55"/>
-      <c r="B61" s="60"/>
+    <row r="61" spans="1:41" ht="16" x14ac:dyDescent="0.2">
+      <c r="A61" s="53"/>
+      <c r="B61" s="47"/>
       <c r="C61">
         <v>4</v>
       </c>
@@ -5066,19 +5858,20 @@
       <c r="H61" s="33">
         <v>66.620741300000006</v>
       </c>
-      <c r="J61">
+      <c r="I61" s="33"/>
+      <c r="L61">
         <v>63.7846884</v>
       </c>
-      <c r="L61">
+      <c r="N61">
         <v>183.68048870000001</v>
       </c>
-      <c r="N61">
+      <c r="P61">
         <v>110.5701389</v>
       </c>
     </row>
-    <row r="62" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A62" s="55"/>
-      <c r="B62" s="60"/>
+    <row r="62" spans="1:41" ht="16" x14ac:dyDescent="0.2">
+      <c r="A62" s="53"/>
+      <c r="B62" s="47"/>
       <c r="C62">
         <v>5</v>
       </c>
@@ -5093,19 +5886,20 @@
       <c r="H62" s="33">
         <v>63.612826599999998</v>
       </c>
-      <c r="J62">
+      <c r="I62" s="33"/>
+      <c r="L62">
         <v>560.03005040000005</v>
       </c>
-      <c r="L62">
+      <c r="N62">
         <v>63.199841900000003</v>
       </c>
-      <c r="N62">
+      <c r="P62">
         <v>112.1447738</v>
       </c>
     </row>
-    <row r="63" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A63" s="55"/>
-      <c r="B63" s="60"/>
+    <row r="63" spans="1:41" ht="16" x14ac:dyDescent="0.2">
+      <c r="A63" s="53"/>
+      <c r="B63" s="47"/>
       <c r="C63">
         <v>6</v>
       </c>
@@ -5120,19 +5914,20 @@
       <c r="H63" s="33">
         <v>62.2764235</v>
       </c>
-      <c r="J63">
+      <c r="I63" s="33"/>
+      <c r="L63">
         <v>685.14225999999996</v>
       </c>
-      <c r="L63">
+      <c r="N63">
         <v>122.9248932</v>
       </c>
-      <c r="N63">
+      <c r="P63">
         <v>105.71322069999999</v>
       </c>
     </row>
-    <row r="64" spans="1:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="55"/>
-      <c r="B64" s="60"/>
+    <row r="64" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="53"/>
+      <c r="B64" s="47"/>
       <c r="C64">
         <v>7</v>
       </c>
@@ -5147,19 +5942,20 @@
       <c r="H64" s="33">
         <v>62.672274899999998</v>
       </c>
-      <c r="J64">
+      <c r="I64" s="33"/>
+      <c r="L64">
         <v>124.58991930000001</v>
       </c>
-      <c r="L64">
+      <c r="N64">
         <v>62.615116499999999</v>
       </c>
-      <c r="N64">
+      <c r="P64">
         <v>103.50280239999999</v>
       </c>
     </row>
-    <row r="65" spans="1:24" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="55"/>
-      <c r="B65" s="60"/>
+    <row r="65" spans="1:30" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="53"/>
+      <c r="B65" s="47"/>
       <c r="C65">
         <v>8</v>
       </c>
@@ -5174,27 +5970,30 @@
       <c r="H65" s="33">
         <v>62.066623900000003</v>
       </c>
-      <c r="J65">
+      <c r="I65" s="33"/>
+      <c r="L65">
         <v>1430.3951505</v>
       </c>
-      <c r="L65">
+      <c r="N65">
         <v>311.06919740000001</v>
       </c>
-      <c r="N65">
+      <c r="P65">
         <v>89.825549699999996</v>
       </c>
-      <c r="S65" s="57" t="s">
+      <c r="W65" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="T65" s="57"/>
-      <c r="U65" s="57"/>
-      <c r="V65" s="57"/>
-      <c r="W65" s="57"/>
-      <c r="X65" s="57"/>
-    </row>
-    <row r="66" spans="1:24" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="55"/>
-      <c r="B66" s="60"/>
+      <c r="X65" s="51"/>
+      <c r="Y65" s="51"/>
+      <c r="Z65" s="51"/>
+      <c r="AA65" s="51"/>
+      <c r="AB65" s="51"/>
+      <c r="AC65" s="51"/>
+      <c r="AD65" s="51"/>
+    </row>
+    <row r="66" spans="1:30" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="53"/>
+      <c r="B66" s="47"/>
       <c r="C66">
         <v>9</v>
       </c>
@@ -5209,34 +6008,41 @@
       <c r="H66" s="33">
         <v>62.867806299999998</v>
       </c>
-      <c r="J66">
+      <c r="I66" s="33"/>
+      <c r="L66">
         <v>124.3385308</v>
       </c>
-      <c r="L66">
+      <c r="N66">
         <v>62.329187400000002</v>
       </c>
-      <c r="N66">
+      <c r="P66">
         <v>77.588893900000002</v>
       </c>
-      <c r="T66" s="38" t="s">
+      <c r="X66" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="U66" s="38" t="s">
+      <c r="Y66" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="V66" s="38" t="s">
+      <c r="Z66" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="W66" s="38" t="s">
+      <c r="AA66" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB66" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="X66" s="38" t="s">
+      <c r="AC66" s="38" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="67" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="55"/>
-      <c r="B67" s="61"/>
+      <c r="AD66" s="38" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="67" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="53"/>
+      <c r="B67" s="48"/>
       <c r="C67">
         <v>10</v>
       </c>
@@ -5250,78 +6056,95 @@
       <c r="H67" s="31">
         <v>64.716894199999999</v>
       </c>
-      <c r="J67">
+      <c r="I67" s="31"/>
+      <c r="L67">
         <v>62.1611634</v>
       </c>
-      <c r="L67">
+      <c r="N67">
         <v>254.94474790000001</v>
       </c>
-      <c r="N67">
+      <c r="P67">
         <v>79.4372781</v>
       </c>
-      <c r="S67" s="37" t="s">
+      <c r="W67" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="T67" s="10">
-        <f>MEDIAN(D7:D67,J7:J67)</f>
+      <c r="X67" s="10">
+        <f>MEDIAN(D7:D67,L7:L67)</f>
         <v>393.25438110000005</v>
       </c>
-      <c r="U67" s="10">
-        <f>MEDIAN(F7:F67,L7:L67)</f>
+      <c r="Y67" s="10">
+        <f>MEDIAN(F7:F67,N7:N67)</f>
         <v>194.58409510000001</v>
       </c>
-      <c r="V67" s="10">
-        <f>MEDIAN(H7:H67,N7:N67)</f>
+      <c r="Z67" s="10">
+        <f>MEDIAN(H7:H67,P7:P67)</f>
         <v>73.235108800000006</v>
       </c>
-      <c r="W67">
-        <f>MEDIAN(F74:F134,L74:L134)</f>
+      <c r="AA67" s="10" t="e">
+        <f>MEDIAN(J7:J67,R7:R67)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB67">
+        <f>MEDIAN(F74:F134,N74:N134)</f>
         <v>262.68448710000001</v>
       </c>
-      <c r="X67">
-        <f>MEDIAN(H74:H134,N74:N134)</f>
+      <c r="AC67">
+        <f>MEDIAN(H74:H134,P74:P134)</f>
         <v>132.92846044999999</v>
       </c>
-    </row>
-    <row r="68" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD67">
+        <f>MEDIAN(J74:J134,R74:R134)</f>
+        <v>50.875100000000003</v>
+      </c>
+    </row>
+    <row r="68" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="28"/>
       <c r="B68" s="1"/>
-      <c r="S68" s="37" t="s">
+      <c r="W68" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="T68" s="10">
-        <f>AVERAGE(D7:D67,J7:J67)</f>
+      <c r="X68" s="10">
+        <f>AVERAGE(D7:D67,L7:L67)</f>
         <v>546.31773920583328</v>
       </c>
-      <c r="U68" s="10">
-        <f>AVERAGE(F7:F67,L7:L67)</f>
+      <c r="Y68" s="10">
+        <f>AVERAGE(F7:F67,N7:N67)</f>
         <v>374.52974976499985</v>
       </c>
-      <c r="V68" s="10">
-        <f>AVERAGE(H7:H67,N7:N67)</f>
+      <c r="Z68" s="10">
+        <f>AVERAGE(H7:H67,P7:P67)</f>
         <v>96.597025105833339</v>
       </c>
-      <c r="W68">
-        <f>AVERAGE(F74:F134,L74:L134)</f>
+      <c r="AA68" s="10" t="e">
+        <f>AVERAGE(J7:J67,R7:R67)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB68">
+        <f>AVERAGE(F74:F134,N74:N134)</f>
         <v>504.82828081192645</v>
       </c>
-      <c r="X68">
-        <f>AVERAGE(H74:H134,N74:N134)</f>
+      <c r="AC68">
+        <f>AVERAGE(H74:H134,P74:P134)</f>
         <v>248.11779057499996</v>
       </c>
-    </row>
-    <row r="69" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD68">
+        <f>AVERAGE(J74:J134,R74:R134)</f>
+        <v>57.438206666666666</v>
+      </c>
+    </row>
+    <row r="69" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="28"/>
       <c r="B69" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D69" s="31">
-        <f t="shared" ref="D69:F69" si="8">AVERAGE(D7:D67)</f>
+        <f t="shared" ref="D69:F69" si="10">AVERAGE(D7:D67)</f>
         <v>546.26147013000013</v>
       </c>
       <c r="E69" s="31"/>
       <c r="F69" s="31">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>264.37453663499997</v>
       </c>
       <c r="G69" s="31"/>
@@ -5330,56 +6153,68 @@
         <v>97.33608582833331</v>
       </c>
       <c r="I69" s="31"/>
-      <c r="J69" s="31">
-        <f t="shared" ref="J69:N69" si="9">AVERAGE(J7:J67)</f>
-        <v>546.37400828166676</v>
-      </c>
+      <c r="J69" s="31"/>
       <c r="K69" s="31"/>
       <c r="L69" s="31">
-        <f t="shared" si="9"/>
-        <v>484.68496289500018</v>
+        <f t="shared" ref="L69:P69" si="11">AVERAGE(L7:L67)</f>
+        <v>546.37400828166676</v>
       </c>
       <c r="M69" s="31"/>
       <c r="N69" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
+        <v>484.68496289500018</v>
+      </c>
+      <c r="O69" s="31"/>
+      <c r="P69" s="31">
+        <f t="shared" si="11"/>
         <v>95.857964383333311</v>
       </c>
-      <c r="S69" s="37" t="s">
+      <c r="Q69" s="31"/>
+      <c r="R69" s="31"/>
+      <c r="W69" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="T69" s="10">
-        <f>_xlfn.QUARTILE.EXC((D7:D67,J7:J67),1)</f>
+      <c r="X69" s="10">
+        <f>_xlfn.QUARTILE.EXC((D7:D67,L7:L67),1)</f>
         <v>128.04324550000001</v>
       </c>
-      <c r="U69" s="10">
-        <f>_xlfn.QUARTILE.EXC((F7:F67,L7:L67),1)</f>
+      <c r="Y69" s="10">
+        <f>_xlfn.QUARTILE.EXC((F7:F67,N7:N67),1)</f>
         <v>70.607067600000008</v>
       </c>
-      <c r="V69" s="10">
-        <f>_xlfn.QUARTILE.EXC((H7:H67,N7:N67),1)</f>
+      <c r="Z69" s="10">
+        <f>_xlfn.QUARTILE.EXC((H7:H67,P7:P67),1)</f>
         <v>66.105104100000005</v>
       </c>
-      <c r="W69">
-        <f>_xlfn.QUARTILE.EXC((F74:F134,L74:L134),1)</f>
+      <c r="AA69" s="10" t="e">
+        <f>_xlfn.QUARTILE.EXC((J7:J67,R7:R67),1)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB69">
+        <f>_xlfn.QUARTILE.EXC((F74:F134,N74:N134),1)</f>
         <v>133.60371085</v>
       </c>
-      <c r="X69">
-        <f>_xlfn.QUARTILE.EXC((H74:H134,N74:N134),1)</f>
+      <c r="AC69">
+        <f>_xlfn.QUARTILE.EXC((H74:H134,P74:P134),1)</f>
         <v>78.655683824999997</v>
       </c>
-    </row>
-    <row r="70" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD69">
+        <f>_xlfn.QUARTILE.EXC((J74:J134,R74:R134),1)</f>
+        <v>50.533649999999994</v>
+      </c>
+    </row>
+    <row r="70" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="28"/>
       <c r="B70" s="1" t="s">
         <v>81</v>
       </c>
       <c r="D70" s="31">
-        <f t="shared" ref="D70:F70" si="10">MIN(D7:D67)</f>
+        <f t="shared" ref="D70:F70" si="12">MIN(D7:D67)</f>
         <v>64.404756800000001</v>
       </c>
       <c r="E70" s="31"/>
       <c r="F70" s="31">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>59.023810400000002</v>
       </c>
       <c r="G70" s="31"/>
@@ -5388,56 +6223,68 @@
         <v>61.305089099999996</v>
       </c>
       <c r="I70" s="31"/>
-      <c r="J70" s="31">
-        <f t="shared" ref="J70:N70" si="11">MIN(J7:J67)</f>
-        <v>62.1611634</v>
-      </c>
+      <c r="J70" s="31"/>
       <c r="K70" s="31"/>
       <c r="L70" s="31">
-        <f t="shared" si="11"/>
-        <v>61.419639699999998</v>
+        <f t="shared" ref="L70:P70" si="13">MIN(L7:L67)</f>
+        <v>62.1611634</v>
       </c>
       <c r="M70" s="31"/>
       <c r="N70" s="31">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
+        <v>61.419639699999998</v>
+      </c>
+      <c r="O70" s="31"/>
+      <c r="P70" s="31">
+        <f t="shared" si="13"/>
         <v>62.552345799999998</v>
       </c>
-      <c r="S70" s="37" t="s">
+      <c r="Q70" s="31"/>
+      <c r="R70" s="31"/>
+      <c r="W70" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="T70" s="10">
-        <f>_xlfn.QUARTILE.EXC((D7:D67,J7:J67),3)</f>
+      <c r="X70" s="10">
+        <f>_xlfn.QUARTILE.EXC((D7:D67,L7:L67),3)</f>
         <v>847.7565196999999</v>
       </c>
-      <c r="U70" s="10">
-        <f>_xlfn.QUARTILE.EXC((F7:F67,L7:L67),3)</f>
+      <c r="Y70" s="10">
+        <f>_xlfn.QUARTILE.EXC((F7:F67,N7:N67),3)</f>
         <v>368.582647775</v>
       </c>
-      <c r="V70" s="10">
-        <f>_xlfn.QUARTILE.EXC((H7:H67,N7:N67),3)</f>
+      <c r="Z70" s="10">
+        <f>_xlfn.QUARTILE.EXC((H7:H67,P7:P67),3)</f>
         <v>84.675873050000007</v>
       </c>
-      <c r="W70">
-        <f>_xlfn.QUARTILE.EXC((F74:F134,L74:L134),3)</f>
+      <c r="AA70" s="10" t="e">
+        <f>_xlfn.QUARTILE.EXC((J7:J67,R7:R67),3)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB70">
+        <f>_xlfn.QUARTILE.EXC((F74:F134,N74:N134),3)</f>
         <v>667.83910349999996</v>
       </c>
-      <c r="X70">
-        <f>_xlfn.QUARTILE.EXC((H74:H134,N74:N134),3)</f>
+      <c r="AC70">
+        <f>_xlfn.QUARTILE.EXC((H74:H134,P74:P134),3)</f>
         <v>284.64135290000002</v>
       </c>
-    </row>
-    <row r="71" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD70">
+        <f>_xlfn.QUARTILE.EXC((J74:J134,R74:R134),3)</f>
+        <v>51.852874999999997</v>
+      </c>
+    </row>
+    <row r="71" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="28"/>
       <c r="B71" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D71" s="31">
-        <f t="shared" ref="D71:F71" si="12">MAX(D7:D67)</f>
+        <f t="shared" ref="D71:F71" si="14">MAX(D7:D67)</f>
         <v>2074.6347596000001</v>
       </c>
       <c r="E71" s="31"/>
       <c r="F71" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>932.88624049999999</v>
       </c>
       <c r="G71" s="31"/>
@@ -5446,56 +6293,68 @@
         <v>452.67738200000002</v>
       </c>
       <c r="I71" s="31"/>
-      <c r="J71" s="31">
-        <f t="shared" ref="J71:N71" si="13">MAX(J7:J67)</f>
-        <v>2702.1846860999999</v>
-      </c>
+      <c r="J71" s="31"/>
       <c r="K71" s="31"/>
       <c r="L71" s="31">
-        <f t="shared" si="13"/>
-        <v>7218.0189136999998</v>
+        <f t="shared" ref="L71:P71" si="15">MAX(L7:L67)</f>
+        <v>2702.1846860999999</v>
       </c>
       <c r="M71" s="31"/>
       <c r="N71" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
+        <v>7218.0189136999998</v>
+      </c>
+      <c r="O71" s="31"/>
+      <c r="P71" s="31">
+        <f t="shared" si="15"/>
         <v>456.90458919999998</v>
       </c>
-      <c r="S71" s="37" t="s">
+      <c r="Q71" s="31"/>
+      <c r="R71" s="31"/>
+      <c r="W71" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="T71" s="10">
-        <f>T70+1.5*(T70-T69)</f>
+      <c r="X71" s="10">
+        <f>X70+1.5*(X70-X69)</f>
         <v>1927.3264309999997</v>
       </c>
-      <c r="U71" s="10">
-        <f t="shared" ref="U71:X71" si="14">U70+1.5*(U70-U69)</f>
+      <c r="Y71" s="10">
+        <f t="shared" ref="Y71:AB71" si="16">Y70+1.5*(Y70-Y69)</f>
         <v>815.54601803750006</v>
       </c>
-      <c r="V71" s="10">
-        <f t="shared" si="14"/>
+      <c r="Z71" s="10">
+        <f t="shared" si="16"/>
         <v>112.53202647500001</v>
       </c>
-      <c r="W71" s="10">
-        <f t="shared" si="14"/>
+      <c r="AA71" s="10" t="e">
+        <f>AA70+1.5*(AA70-AA69)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB71" s="10">
+        <f>AB70+1.5*(AB70-AB69)</f>
         <v>1469.192192475</v>
       </c>
-      <c r="X71" s="10">
-        <f t="shared" si="14"/>
+      <c r="AC71" s="10">
+        <f>AC70+1.5*(AC70-AC69)</f>
         <v>593.61985651250006</v>
       </c>
-    </row>
-    <row r="72" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD71" s="10">
+        <f>AD70+1.5*(AD70-AD69)</f>
+        <v>53.831712500000002</v>
+      </c>
+    </row>
+    <row r="72" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="28"/>
       <c r="B72" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D72" s="31">
-        <f t="shared" ref="D72:F72" si="15">STDEV(D7:D67)</f>
+        <f t="shared" ref="D72:F72" si="17">STDEV(D7:D67)</f>
         <v>436.89147549757564</v>
       </c>
       <c r="E72" s="31"/>
       <c r="F72" s="31">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>242.69754810017969</v>
       </c>
       <c r="G72" s="31"/>
@@ -5504,52 +6363,64 @@
         <v>74.776434817048084</v>
       </c>
       <c r="I72" s="31"/>
-      <c r="J72" s="31">
-        <f t="shared" ref="J72:N72" si="16">STDEV(J7:J67)</f>
-        <v>566.58008735947578</v>
-      </c>
+      <c r="J72" s="31"/>
       <c r="K72" s="31"/>
       <c r="L72" s="31">
-        <f t="shared" si="16"/>
-        <v>1065.9377509710532</v>
+        <f t="shared" ref="L72:P72" si="18">STDEV(L7:L67)</f>
+        <v>566.58008735947578</v>
       </c>
       <c r="M72" s="31"/>
       <c r="N72" s="31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
+        <v>1065.9377509710532</v>
+      </c>
+      <c r="O72" s="31"/>
+      <c r="P72" s="31">
+        <f t="shared" si="18"/>
         <v>65.794122050148587</v>
       </c>
-      <c r="S72" s="37" t="s">
+      <c r="Q72" s="31"/>
+      <c r="R72" s="31"/>
+      <c r="W72" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="T72" s="10">
-        <f>IF(T69-1.5*(T70-T69)&lt;0,0,T69-1.5*(T70-T69))</f>
+      <c r="X72" s="10">
+        <f>IF(X69-1.5*(X70-X69)&lt;0,0,X69-1.5*(X70-X69))</f>
         <v>0</v>
       </c>
-      <c r="U72" s="10">
-        <f t="shared" ref="U72:X72" si="17">IF(U69-1.5*(U70-U69)&lt;0,0,U69-1.5*(U70-U69))</f>
+      <c r="Y72" s="10">
+        <f t="shared" ref="Y72:AB72" si="19">IF(Y69-1.5*(Y70-Y69)&lt;0,0,Y69-1.5*(Y70-Y69))</f>
         <v>0</v>
       </c>
-      <c r="V72" s="10">
-        <f>IF(V69-1.5*(V70-V69)&lt;0,0,V69-1.5*(V70-V69))</f>
+      <c r="Z72" s="10">
+        <f>IF(Z69-1.5*(Z70-Z69)&lt;0,0,Z69-1.5*(Z70-Z69))</f>
         <v>38.248950675000003</v>
       </c>
-      <c r="W72" s="10">
-        <f t="shared" si="17"/>
+      <c r="AA72" s="10" t="e">
+        <f>IF(AA69-1.5*(AA70-AA69)&lt;0,0,AA69-1.5*(AA70-AA69))</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB72" s="10">
+        <f>IF(AB69-1.5*(AB70-AB69)&lt;0,0,AB69-1.5*(AB70-AB69))</f>
         <v>0</v>
       </c>
-      <c r="X72" s="10">
-        <f t="shared" si="17"/>
+      <c r="AC72" s="10">
+        <f>IF(AC69-1.5*(AC70-AC69)&lt;0,0,AC69-1.5*(AC70-AC69))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:24" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD72" s="10">
+        <f>IF(AD69-1.5*(AD70-AD69)&lt;0,0,AD69-1.5*(AD70-AD69))</f>
+        <v>48.55481249999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4"/>
     </row>
-    <row r="74" spans="1:24" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="54" t="s">
+    <row r="74" spans="1:30" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="B74" s="59" t="s">
+      <c r="B74" s="46" t="s">
         <v>11</v>
       </c>
       <c r="C74">
@@ -5566,19 +6437,26 @@
       <c r="H74" s="33">
         <v>66.763275300000004</v>
       </c>
-      <c r="J74" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L74" s="63">
+      <c r="I74" s="33"/>
+      <c r="J74" s="33">
+        <v>53.061100000000003</v>
+      </c>
+      <c r="L74" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N74">
         <v>3419.3379930999999</v>
       </c>
-      <c r="N74">
+      <c r="P74">
         <v>284.21020099999998</v>
       </c>
-    </row>
-    <row r="75" spans="1:24" ht="16" x14ac:dyDescent="0.2">
-      <c r="A75" s="55"/>
-      <c r="B75" s="60"/>
+      <c r="R74">
+        <v>53.6995</v>
+      </c>
+    </row>
+    <row r="75" spans="1:30" ht="16" x14ac:dyDescent="0.2">
+      <c r="A75" s="53"/>
+      <c r="B75" s="47"/>
       <c r="C75">
         <v>2</v>
       </c>
@@ -5593,19 +6471,26 @@
       <c r="H75" s="33">
         <v>64.796429700000004</v>
       </c>
-      <c r="J75" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L75" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="N75">
+      <c r="I75" s="33"/>
+      <c r="J75" s="33">
+        <v>50.7117</v>
+      </c>
+      <c r="L75" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N75" t="s">
+        <v>88</v>
+      </c>
+      <c r="P75">
         <v>269.4879608</v>
       </c>
-    </row>
-    <row r="76" spans="1:24" ht="16" x14ac:dyDescent="0.2">
-      <c r="A76" s="55"/>
-      <c r="B76" s="60"/>
+      <c r="R75">
+        <v>50.559399999999997</v>
+      </c>
+    </row>
+    <row r="76" spans="1:30" ht="16" x14ac:dyDescent="0.2">
+      <c r="A76" s="53"/>
+      <c r="B76" s="47"/>
       <c r="C76">
         <v>3</v>
       </c>
@@ -5620,19 +6505,26 @@
       <c r="H76" s="33">
         <v>143.70110059999999</v>
       </c>
-      <c r="J76" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L76" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="N76">
+      <c r="I76" s="33"/>
+      <c r="J76" s="33">
+        <v>51.131300000000003</v>
+      </c>
+      <c r="L76" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N76" t="s">
+        <v>88</v>
+      </c>
+      <c r="P76">
         <v>734.02437339999994</v>
       </c>
-    </row>
-    <row r="77" spans="1:24" ht="16" x14ac:dyDescent="0.2">
-      <c r="A77" s="55"/>
-      <c r="B77" s="60"/>
+      <c r="R76">
+        <v>102.2818</v>
+      </c>
+    </row>
+    <row r="77" spans="1:30" ht="16" x14ac:dyDescent="0.2">
+      <c r="A77" s="53"/>
+      <c r="B77" s="47"/>
       <c r="C77">
         <v>4</v>
       </c>
@@ -5647,19 +6539,26 @@
       <c r="H77" s="33">
         <v>275.11039959999999</v>
       </c>
-      <c r="J77" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L77" s="63">
+      <c r="I77" s="33"/>
+      <c r="J77" s="90">
+        <v>353.98700000000002</v>
+      </c>
+      <c r="L77" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N77">
         <v>1116.3597103</v>
       </c>
-      <c r="N77">
+      <c r="P77">
         <v>1531.9837926</v>
       </c>
-    </row>
-    <row r="78" spans="1:24" ht="16" x14ac:dyDescent="0.2">
-      <c r="A78" s="55"/>
-      <c r="B78" s="60"/>
+      <c r="R77">
+        <v>50.771599999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:30" ht="16" x14ac:dyDescent="0.2">
+      <c r="A78" s="53"/>
+      <c r="B78" s="47"/>
       <c r="C78">
         <v>5</v>
       </c>
@@ -5674,19 +6573,26 @@
       <c r="H78" s="33">
         <v>135.82408670000001</v>
       </c>
-      <c r="J78" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L78" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="N78">
+      <c r="I78" s="33"/>
+      <c r="J78" s="33">
+        <v>50.622300000000003</v>
+      </c>
+      <c r="L78" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N78" t="s">
+        <v>88</v>
+      </c>
+      <c r="P78">
         <v>66.381577199999995</v>
       </c>
-    </row>
-    <row r="79" spans="1:24" ht="16" x14ac:dyDescent="0.2">
-      <c r="A79" s="55"/>
-      <c r="B79" s="60"/>
+      <c r="R78" s="83">
+        <v>50.402000000000001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:30" ht="16" x14ac:dyDescent="0.2">
+      <c r="A79" s="53"/>
+      <c r="B79" s="47"/>
       <c r="C79">
         <v>6</v>
       </c>
@@ -5701,19 +6607,26 @@
       <c r="H79" s="33">
         <v>478.77884940000001</v>
       </c>
-      <c r="J79" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L79" s="63">
+      <c r="I79" s="33"/>
+      <c r="J79" s="33">
+        <v>50.330599999999997</v>
+      </c>
+      <c r="L79" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N79">
         <v>2291.4962295999999</v>
       </c>
-      <c r="N79">
+      <c r="P79">
         <v>132.72599790000001</v>
       </c>
-    </row>
-    <row r="80" spans="1:24" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="55"/>
-      <c r="B80" s="60"/>
+      <c r="R79">
+        <v>50.2241</v>
+      </c>
+    </row>
+    <row r="80" spans="1:30" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="53"/>
+      <c r="B80" s="47"/>
       <c r="C80">
         <v>7</v>
       </c>
@@ -5728,19 +6641,26 @@
       <c r="H80" s="33">
         <v>411.42527480000001</v>
       </c>
-      <c r="J80" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L80" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="N80">
+      <c r="I80" s="33"/>
+      <c r="J80" s="33">
+        <v>50.485700000000001</v>
+      </c>
+      <c r="L80" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N80" t="s">
+        <v>88</v>
+      </c>
+      <c r="P80">
         <v>2129.4957175999998</v>
       </c>
-    </row>
-    <row r="81" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="55"/>
-      <c r="B81" s="60"/>
+      <c r="R80">
+        <v>100.97629999999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="53"/>
+      <c r="B81" s="47"/>
       <c r="C81">
         <v>8</v>
       </c>
@@ -5755,19 +6675,26 @@
       <c r="H81" s="33">
         <v>136.67672809999999</v>
       </c>
-      <c r="J81" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L81" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="N81">
+      <c r="I81" s="33"/>
+      <c r="J81" s="33">
+        <v>100.5929</v>
+      </c>
+      <c r="L81" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N81" t="s">
+        <v>88</v>
+      </c>
+      <c r="P81">
         <v>132.93145910000001</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="55"/>
-      <c r="B82" s="60"/>
+      <c r="R81">
+        <v>100.8334</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="53"/>
+      <c r="B82" s="47"/>
       <c r="C82">
         <v>9</v>
       </c>
@@ -5782,19 +6709,26 @@
       <c r="H82" s="33">
         <v>68.646983199999994</v>
       </c>
-      <c r="J82" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L82" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="N82">
+      <c r="I82" s="33"/>
+      <c r="J82" s="33">
+        <v>50.373600000000003</v>
+      </c>
+      <c r="L82" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N82" t="s">
+        <v>88</v>
+      </c>
+      <c r="P82">
         <v>66.191384099999993</v>
       </c>
-    </row>
-    <row r="83" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="55"/>
-      <c r="B83" s="61"/>
+      <c r="R82">
+        <v>50.533499999999997</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="53"/>
+      <c r="B83" s="48"/>
       <c r="C83">
         <v>10</v>
       </c>
@@ -5808,19 +6742,26 @@
       <c r="H83" s="31">
         <v>204.3538739</v>
       </c>
-      <c r="J83" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L83" s="63">
+      <c r="I83" s="31"/>
+      <c r="J83" s="31">
+        <v>50.584400000000002</v>
+      </c>
+      <c r="L83" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N83">
         <v>866.2734921</v>
       </c>
-      <c r="N83">
+      <c r="P83">
         <v>65.962567100000001</v>
       </c>
-    </row>
-    <row r="84" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A84" s="55"/>
-      <c r="B84" s="59" t="s">
+      <c r="R83">
+        <v>50.620800000000003</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A84" s="53"/>
+      <c r="B84" s="46" t="s">
         <v>86</v>
       </c>
       <c r="C84">
@@ -5837,19 +6778,26 @@
       <c r="H84" s="33">
         <v>233.3466028</v>
       </c>
-      <c r="J84" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L84" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="N84">
+      <c r="I84" s="33"/>
+      <c r="J84" s="33">
+        <v>52.639200000000002</v>
+      </c>
+      <c r="L84" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N84" t="s">
+        <v>88</v>
+      </c>
+      <c r="P84">
         <v>277.75115970000002</v>
       </c>
-    </row>
-    <row r="85" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A85" s="55"/>
-      <c r="B85" s="60"/>
+      <c r="R84">
+        <v>53.482700000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A85" s="53"/>
+      <c r="B85" s="47"/>
       <c r="C85">
         <v>2</v>
       </c>
@@ -5864,19 +6812,26 @@
       <c r="H85" s="33">
         <v>293.3295832</v>
       </c>
-      <c r="J85" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L85" s="63">
+      <c r="I85" s="33"/>
+      <c r="J85" s="33">
+        <v>51.4953</v>
+      </c>
+      <c r="L85" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N85">
         <v>1537.7299883000001</v>
       </c>
-      <c r="N85">
+      <c r="P85">
         <v>134.52035739999999</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A86" s="55"/>
-      <c r="B86" s="60"/>
+      <c r="R85">
+        <v>50.421500000000002</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A86" s="53"/>
+      <c r="B86" s="47"/>
       <c r="C86">
         <v>3</v>
       </c>
@@ -5891,19 +6846,26 @@
       <c r="H86" s="33">
         <v>221.75517379999999</v>
       </c>
-      <c r="J86" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L86" s="63">
+      <c r="I86" s="33"/>
+      <c r="J86" s="33">
+        <v>50.7624</v>
+      </c>
+      <c r="L86" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N86">
         <v>480.55343540000001</v>
       </c>
-      <c r="N86">
+      <c r="P86">
         <v>340.43719440000001</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A87" s="55"/>
-      <c r="B87" s="60"/>
+      <c r="R86">
+        <v>50.620399999999997</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A87" s="53"/>
+      <c r="B87" s="47"/>
       <c r="C87">
         <v>4</v>
       </c>
@@ -5918,19 +6880,26 @@
       <c r="H87" s="33">
         <v>78.798304700000003</v>
       </c>
-      <c r="J87" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L87" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="N87">
+      <c r="I87" s="33"/>
+      <c r="J87" s="33">
+        <v>50.907299999999999</v>
+      </c>
+      <c r="L87" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N87" t="s">
+        <v>88</v>
+      </c>
+      <c r="P87">
         <v>350.21360909999999</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A88" s="55"/>
-      <c r="B88" s="60"/>
+      <c r="R87">
+        <v>50.913800000000002</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A88" s="53"/>
+      <c r="B88" s="47"/>
       <c r="C88">
         <v>5</v>
       </c>
@@ -5945,19 +6914,26 @@
       <c r="H88" s="33">
         <v>767.51336170000002</v>
       </c>
-      <c r="J88" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L88" s="63">
+      <c r="I88" s="33"/>
+      <c r="J88" s="33">
+        <v>50.641100000000002</v>
+      </c>
+      <c r="L88" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N88">
         <v>1113.2449271999999</v>
       </c>
-      <c r="N88">
+      <c r="P88">
         <v>275.05557240000002</v>
       </c>
-    </row>
-    <row r="89" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A89" s="55"/>
-      <c r="B89" s="60"/>
+      <c r="R88">
+        <v>51.726799999999997</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A89" s="53"/>
+      <c r="B89" s="47"/>
       <c r="C89">
         <v>6</v>
       </c>
@@ -5972,19 +6948,26 @@
       <c r="H89" s="33">
         <v>73.746508800000001</v>
       </c>
-      <c r="J89" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L89" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="N89">
+      <c r="I89" s="33"/>
+      <c r="J89" s="90">
+        <v>50.674999999999997</v>
+      </c>
+      <c r="L89" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N89" t="s">
+        <v>88</v>
+      </c>
+      <c r="P89">
         <v>204.8521217</v>
       </c>
-    </row>
-    <row r="90" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="55"/>
-      <c r="B90" s="60"/>
+      <c r="R89">
+        <v>51.264200000000002</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="53"/>
+      <c r="B90" s="47"/>
       <c r="C90">
         <v>7</v>
       </c>
@@ -5999,19 +6982,26 @@
       <c r="H90" s="33">
         <v>148.5537539</v>
       </c>
-      <c r="J90" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L90" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="N90">
+      <c r="I90" s="33"/>
+      <c r="J90" s="33">
+        <v>50.398600000000002</v>
+      </c>
+      <c r="L90" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N90" t="s">
+        <v>88</v>
+      </c>
+      <c r="P90">
         <v>481.83748580000002</v>
       </c>
-    </row>
-    <row r="91" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="55"/>
-      <c r="B91" s="60"/>
+      <c r="R90">
+        <v>50.277099999999997</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="53"/>
+      <c r="B91" s="47"/>
       <c r="C91">
         <v>8</v>
       </c>
@@ -6026,19 +7016,26 @@
       <c r="H91" s="33">
         <v>153.4032641</v>
       </c>
-      <c r="J91" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L91" s="63">
+      <c r="I91" s="33"/>
+      <c r="J91" s="33">
+        <v>50.822200000000002</v>
+      </c>
+      <c r="L91" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N91">
         <v>1434.7723593999999</v>
       </c>
-      <c r="N91">
+      <c r="P91">
         <v>560.53439649999996</v>
       </c>
-    </row>
-    <row r="92" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="55"/>
-      <c r="B92" s="60"/>
+      <c r="R91">
+        <v>50.418300000000002</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="53"/>
+      <c r="B92" s="47"/>
       <c r="C92">
         <v>9</v>
       </c>
@@ -6053,19 +7050,26 @@
       <c r="H92" s="33">
         <v>83.474116499999994</v>
       </c>
-      <c r="J92" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L92" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="N92">
+      <c r="I92" s="33"/>
+      <c r="J92" s="33">
+        <v>50.892499999999998</v>
+      </c>
+      <c r="L92" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N92" t="s">
+        <v>88</v>
+      </c>
+      <c r="P92">
         <v>284.78507020000001</v>
       </c>
-    </row>
-    <row r="93" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="55"/>
-      <c r="B93" s="61"/>
+      <c r="R92">
+        <v>50.322800000000001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="53"/>
+      <c r="B93" s="48"/>
       <c r="C93">
         <v>10</v>
       </c>
@@ -6079,19 +7083,26 @@
       <c r="H93" s="31">
         <v>286.33039719999999</v>
       </c>
-      <c r="J93" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L93" s="63">
+      <c r="I93" s="31"/>
+      <c r="J93" s="31">
+        <v>50.554600000000001</v>
+      </c>
+      <c r="L93" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N93">
         <v>1500.9513285</v>
       </c>
-      <c r="N93">
+      <c r="P93">
         <v>82.148705500000005</v>
       </c>
-    </row>
-    <row r="94" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A94" s="55"/>
-      <c r="B94" s="59" t="s">
+      <c r="R93">
+        <v>50.313200000000002</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A94" s="53"/>
+      <c r="B94" s="46" t="s">
         <v>27</v>
       </c>
       <c r="C94">
@@ -6108,19 +7119,26 @@
       <c r="H94" s="33">
         <v>792.71955839999998</v>
       </c>
-      <c r="J94" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L94">
+      <c r="I94" s="33"/>
+      <c r="J94" s="33">
+        <v>53.315600000000003</v>
+      </c>
+      <c r="L94" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N94">
         <v>142.45123580000001</v>
       </c>
-      <c r="N94">
+      <c r="P94">
         <v>72.897619000000006</v>
       </c>
-    </row>
-    <row r="95" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A95" s="55"/>
-      <c r="B95" s="60"/>
+      <c r="R94">
+        <v>52.554699999999997</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A95" s="53"/>
+      <c r="B95" s="47"/>
       <c r="C95">
         <v>2</v>
       </c>
@@ -6135,19 +7153,26 @@
       <c r="H95" s="33">
         <v>66.452325099999996</v>
       </c>
-      <c r="J95" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L95">
+      <c r="I95" s="33"/>
+      <c r="J95" s="33">
+        <v>51.974699999999999</v>
+      </c>
+      <c r="L95" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N95">
         <v>71.119555300000002</v>
       </c>
-      <c r="N95">
+      <c r="P95">
         <v>282.90778799999998</v>
       </c>
-    </row>
-    <row r="96" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A96" s="55"/>
-      <c r="B96" s="60"/>
+      <c r="R95">
+        <v>50.7592</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A96" s="53"/>
+      <c r="B96" s="47"/>
       <c r="C96">
         <v>3</v>
       </c>
@@ -6162,19 +7187,26 @@
       <c r="H96" s="33">
         <v>66.909788599999999</v>
       </c>
-      <c r="J96" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L96">
+      <c r="I96" s="33"/>
+      <c r="J96" s="33">
+        <v>51.908200000000001</v>
+      </c>
+      <c r="L96" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N96">
         <v>70.831908999999996</v>
       </c>
-      <c r="N96">
+      <c r="P96">
         <v>142.34365790000001</v>
       </c>
-    </row>
-    <row r="97" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A97" s="55"/>
-      <c r="B97" s="60"/>
+      <c r="R96">
+        <v>51.112900000000003</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A97" s="53"/>
+      <c r="B97" s="47"/>
       <c r="C97">
         <v>4</v>
       </c>
@@ -6189,19 +7221,26 @@
       <c r="H97" s="33">
         <v>67.079431900000003</v>
       </c>
-      <c r="J97" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L97">
+      <c r="I97" s="33"/>
+      <c r="J97" s="33">
+        <v>51.871200000000002</v>
+      </c>
+      <c r="L97" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N97">
         <v>71.067789500000003</v>
       </c>
-      <c r="N97">
+      <c r="P97">
         <v>141.33162870000001</v>
       </c>
-    </row>
-    <row r="98" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A98" s="55"/>
-      <c r="B98" s="60"/>
+      <c r="R97">
+        <v>50.479100000000003</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A98" s="53"/>
+      <c r="B98" s="47"/>
       <c r="C98">
         <v>5</v>
       </c>
@@ -6216,19 +7255,26 @@
       <c r="H98" s="33">
         <v>66.137360299999997</v>
       </c>
-      <c r="J98" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L98">
+      <c r="I98" s="33"/>
+      <c r="J98" s="33">
+        <v>51.906199999999998</v>
+      </c>
+      <c r="L98" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N98">
         <v>140.45656829999999</v>
       </c>
-      <c r="N98">
+      <c r="P98">
         <v>282.32531840000001</v>
       </c>
-    </row>
-    <row r="99" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A99" s="55"/>
-      <c r="B99" s="60"/>
+      <c r="R98">
+        <v>51.470300000000002</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A99" s="53"/>
+      <c r="B99" s="47"/>
       <c r="C99">
         <v>6</v>
       </c>
@@ -6243,19 +7289,26 @@
       <c r="H99" s="33">
         <v>65.576798600000004</v>
       </c>
-      <c r="J99" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L99">
+      <c r="I99" s="33"/>
+      <c r="J99" s="33">
+        <v>51.8705</v>
+      </c>
+      <c r="L99" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N99">
         <v>71.386210399999996</v>
       </c>
-      <c r="N99">
+      <c r="P99">
         <v>70.631985299999997</v>
       </c>
-    </row>
-    <row r="100" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="55"/>
-      <c r="B100" s="60"/>
+      <c r="R99">
+        <v>50.5839</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="53"/>
+      <c r="B100" s="47"/>
       <c r="C100">
         <v>7</v>
       </c>
@@ -6270,19 +7323,26 @@
       <c r="H100" s="33">
         <v>65.720580600000005</v>
       </c>
-      <c r="J100" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L100">
+      <c r="I100" s="33"/>
+      <c r="J100" s="33">
+        <v>52.648800000000001</v>
+      </c>
+      <c r="L100" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N100">
         <v>70.090210400000004</v>
       </c>
-      <c r="N100">
+      <c r="P100">
         <v>70.4665933</v>
       </c>
-    </row>
-    <row r="101" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="55"/>
-      <c r="B101" s="60"/>
+      <c r="R100">
+        <v>50.473300000000002</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="53"/>
+      <c r="B101" s="47"/>
       <c r="C101">
         <v>8</v>
       </c>
@@ -6297,19 +7357,26 @@
       <c r="H101" s="33">
         <v>130.2536542</v>
       </c>
-      <c r="J101" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L101">
+      <c r="I101" s="33"/>
+      <c r="J101" s="33">
+        <v>52.612299999999998</v>
+      </c>
+      <c r="L101" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N101">
         <v>69.581791999999993</v>
       </c>
-      <c r="N101">
+      <c r="P101">
         <v>284.09153300000003</v>
       </c>
-    </row>
-    <row r="102" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="55"/>
-      <c r="B102" s="60"/>
+      <c r="R101" s="83">
+        <v>50.481000000000002</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="53"/>
+      <c r="B102" s="47"/>
       <c r="C102">
         <v>9</v>
       </c>
@@ -6324,19 +7391,26 @@
       <c r="H102" s="33">
         <v>65.525855399999998</v>
       </c>
-      <c r="J102" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L102">
+      <c r="I102" s="33"/>
+      <c r="J102" s="33">
+        <v>52.011200000000002</v>
+      </c>
+      <c r="L102" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N102">
         <v>142.3687774</v>
       </c>
-      <c r="N102">
+      <c r="P102">
         <v>68.542201000000006</v>
       </c>
-    </row>
-    <row r="103" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="55"/>
-      <c r="B103" s="61"/>
+      <c r="R102">
+        <v>50.660200000000003</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="53"/>
+      <c r="B103" s="48"/>
       <c r="C103">
         <v>10</v>
       </c>
@@ -6350,25 +7424,34 @@
       <c r="H103" s="31">
         <v>130.14358279999999</v>
       </c>
-      <c r="J103" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L103">
+      <c r="I103" s="31"/>
+      <c r="J103" s="31">
+        <v>52.137500000000003</v>
+      </c>
+      <c r="L103" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N103">
         <v>493.20489029999999</v>
       </c>
-      <c r="N103">
+      <c r="P103">
         <v>69.565183899999994</v>
       </c>
-    </row>
-    <row r="104" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="55"/>
+      <c r="R103">
+        <v>50.861699999999999</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="53"/>
       <c r="F104" s="31"/>
       <c r="G104" s="31"/>
       <c r="H104" s="31"/>
-    </row>
-    <row r="105" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A105" s="55"/>
-      <c r="B105" s="59" t="s">
+      <c r="I104" s="31"/>
+      <c r="J104" s="31"/>
+    </row>
+    <row r="105" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A105" s="53"/>
+      <c r="B105" s="46" t="s">
         <v>33</v>
       </c>
       <c r="C105">
@@ -6385,19 +7468,26 @@
       <c r="H105" s="33">
         <v>802.76437429999999</v>
       </c>
-      <c r="J105" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L105">
+      <c r="I105" s="33"/>
+      <c r="J105" s="33">
+        <v>52.943399999999997</v>
+      </c>
+      <c r="L105" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N105">
         <v>431.44677050000001</v>
       </c>
-      <c r="N105">
+      <c r="P105">
         <v>491.76410010000001</v>
       </c>
-    </row>
-    <row r="106" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A106" s="55"/>
-      <c r="B106" s="60"/>
+      <c r="R105" s="83">
+        <v>51.8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A106" s="53"/>
+      <c r="B106" s="47"/>
       <c r="C106">
         <v>2</v>
       </c>
@@ -6412,19 +7502,26 @@
       <c r="H106" s="33">
         <v>326.89859630000001</v>
       </c>
-      <c r="J106" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L106">
+      <c r="I106" s="33"/>
+      <c r="J106" s="33">
+        <v>52.3489</v>
+      </c>
+      <c r="L106" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N106">
         <v>80.275543099999993</v>
       </c>
-      <c r="N106">
+      <c r="P106">
         <v>232.53405960000001</v>
       </c>
-    </row>
-    <row r="107" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A107" s="55"/>
-      <c r="B107" s="60"/>
+      <c r="R106" s="83">
+        <v>50.033000000000001</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A107" s="53"/>
+      <c r="B107" s="47"/>
       <c r="C107">
         <v>3</v>
       </c>
@@ -6439,19 +7536,26 @@
       <c r="H107" s="33">
         <v>64.922921500000001</v>
       </c>
-      <c r="J107" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L107">
+      <c r="I107" s="33"/>
+      <c r="J107" s="33">
+        <v>51.193800000000003</v>
+      </c>
+      <c r="L107" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N107">
         <v>162.89621389999999</v>
       </c>
-      <c r="N107">
+      <c r="P107">
         <v>605.2249865</v>
       </c>
-    </row>
-    <row r="108" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A108" s="55"/>
-      <c r="B108" s="60"/>
+      <c r="R107">
+        <v>50.224200000000003</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A108" s="53"/>
+      <c r="B108" s="47"/>
       <c r="C108">
         <v>4</v>
       </c>
@@ -6466,19 +7570,26 @@
       <c r="H108" s="33">
         <v>971.69256729999995</v>
       </c>
-      <c r="J108" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L108">
+      <c r="I108" s="33"/>
+      <c r="J108" s="90">
+        <v>51.485999999999997</v>
+      </c>
+      <c r="L108" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N108">
         <v>490.99147099999999</v>
       </c>
-      <c r="N108">
+      <c r="P108">
         <v>199.2026663</v>
       </c>
-    </row>
-    <row r="109" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A109" s="55"/>
-      <c r="B109" s="60"/>
+      <c r="R108">
+        <v>50.607199999999999</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A109" s="53"/>
+      <c r="B109" s="47"/>
       <c r="C109">
         <v>5</v>
       </c>
@@ -6493,19 +7604,26 @@
       <c r="H109" s="33">
         <v>529.6448001</v>
       </c>
-      <c r="J109" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L109">
+      <c r="I109" s="33"/>
+      <c r="J109" s="33">
+        <v>50.762099999999997</v>
+      </c>
+      <c r="L109" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N109">
         <v>211.0026641</v>
       </c>
-      <c r="N109">
+      <c r="P109">
         <v>930.15459169999997</v>
       </c>
-    </row>
-    <row r="110" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A110" s="55"/>
-      <c r="B110" s="60"/>
+      <c r="R109">
+        <v>50.477699999999999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A110" s="53"/>
+      <c r="B110" s="47"/>
       <c r="C110">
         <v>6</v>
       </c>
@@ -6520,19 +7638,26 @@
       <c r="H110" s="33">
         <v>145.6007726</v>
       </c>
-      <c r="J110" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L110">
+      <c r="I110" s="33"/>
+      <c r="J110" s="90">
+        <v>51.104999999999997</v>
+      </c>
+      <c r="L110" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N110">
         <v>139.85866469999999</v>
       </c>
-      <c r="N110">
+      <c r="P110">
         <v>532.86005709999995</v>
       </c>
-    </row>
-    <row r="111" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="55"/>
-      <c r="B111" s="60"/>
+      <c r="R110">
+        <v>50.447800000000001</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="53"/>
+      <c r="B111" s="47"/>
       <c r="C111">
         <v>7</v>
       </c>
@@ -6547,19 +7672,26 @@
       <c r="H111" s="33">
         <v>535.69973249999998</v>
       </c>
-      <c r="J111" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L111">
+      <c r="I111" s="33"/>
+      <c r="J111" s="33">
+        <v>50.825499999999998</v>
+      </c>
+      <c r="L111" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N111">
         <v>69.583251700000005</v>
       </c>
-      <c r="N111">
+      <c r="P111">
         <v>464.14077909999997</v>
       </c>
-    </row>
-    <row r="112" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="55"/>
-      <c r="B112" s="60"/>
+      <c r="R111">
+        <v>100.14409999999999</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="53"/>
+      <c r="B112" s="47"/>
       <c r="C112">
         <v>8</v>
       </c>
@@ -6574,19 +7706,26 @@
       <c r="H112" s="33">
         <v>524.29981559999999</v>
       </c>
-      <c r="J112" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L112">
+      <c r="I112" s="33"/>
+      <c r="J112" s="33">
+        <v>50.878300000000003</v>
+      </c>
+      <c r="L112" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N112">
         <v>275.00340569999997</v>
       </c>
-      <c r="N112">
+      <c r="P112">
         <v>530.75148639999998</v>
       </c>
-    </row>
-    <row r="113" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="55"/>
-      <c r="B113" s="60"/>
+      <c r="R112">
+        <v>50.356200000000001</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="53"/>
+      <c r="B113" s="47"/>
       <c r="C113">
         <v>9</v>
       </c>
@@ -6601,19 +7740,26 @@
       <c r="H113" s="33">
         <v>780.2396066</v>
       </c>
-      <c r="J113" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L113">
+      <c r="I113" s="33"/>
+      <c r="J113" s="91">
+        <v>251.42080000000001</v>
+      </c>
+      <c r="L113" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N113">
         <v>137.27711629999999</v>
       </c>
-      <c r="N113">
+      <c r="P113">
         <v>794.70245620000003</v>
       </c>
-    </row>
-    <row r="114" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="55"/>
-      <c r="B114" s="61"/>
+      <c r="R113">
+        <v>49.9163</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="53"/>
+      <c r="B114" s="48"/>
       <c r="C114">
         <v>10</v>
       </c>
@@ -6627,19 +7773,26 @@
       <c r="H114" s="31">
         <v>65.373191199999994</v>
       </c>
-      <c r="J114" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L114">
+      <c r="I114" s="31"/>
+      <c r="J114" s="31">
+        <v>50.256300000000003</v>
+      </c>
+      <c r="L114" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N114">
         <v>69.129179500000006</v>
       </c>
-      <c r="N114">
+      <c r="P114">
         <v>132.92546179999999</v>
       </c>
-    </row>
-    <row r="115" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A115" s="55"/>
-      <c r="B115" s="59" t="s">
+      <c r="R114">
+        <v>50.026600000000002</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A115" s="53"/>
+      <c r="B115" s="46" t="s">
         <v>42</v>
       </c>
       <c r="C115">
@@ -6656,19 +7809,26 @@
       <c r="H115" s="33">
         <v>86.674660399999993</v>
       </c>
-      <c r="J115" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L115">
+      <c r="I115" s="33"/>
+      <c r="J115" s="90">
+        <v>52.41</v>
+      </c>
+      <c r="L115" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N115">
         <v>75.366843200000005</v>
       </c>
-      <c r="N115">
+      <c r="P115">
         <v>174.2282764</v>
       </c>
-    </row>
-    <row r="116" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A116" s="55"/>
-      <c r="B116" s="60"/>
+      <c r="R115" s="82">
+        <v>52.584600000000002</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A116" s="53"/>
+      <c r="B116" s="47"/>
       <c r="C116">
         <v>2</v>
       </c>
@@ -6683,19 +7843,26 @@
       <c r="H116" s="33">
         <v>166.6076999</v>
       </c>
-      <c r="J116" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L116">
+      <c r="I116" s="33"/>
+      <c r="J116" s="90">
+        <v>51.065199999999997</v>
+      </c>
+      <c r="L116" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N116">
         <v>75.052509999999998</v>
       </c>
-      <c r="N116">
+      <c r="P116">
         <v>285.83021500000001</v>
       </c>
-    </row>
-    <row r="117" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A117" s="55"/>
-      <c r="B117" s="60"/>
+      <c r="R116">
+        <v>50.979900000000001</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A117" s="53"/>
+      <c r="B117" s="47"/>
       <c r="C117">
         <v>3</v>
       </c>
@@ -6710,19 +7877,26 @@
       <c r="H117" s="33">
         <v>83.641438399999998</v>
       </c>
-      <c r="J117" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L117">
+      <c r="I117" s="33"/>
+      <c r="J117" s="90">
+        <v>51.0871</v>
+      </c>
+      <c r="L117" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N117">
         <v>290.48057679999999</v>
       </c>
-      <c r="N117">
+      <c r="P117">
         <v>95.346653200000006</v>
       </c>
-    </row>
-    <row r="118" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A118" s="55"/>
-      <c r="B118" s="60"/>
+      <c r="R117">
+        <v>51.025700000000001</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A118" s="53"/>
+      <c r="B118" s="47"/>
       <c r="C118">
         <v>4</v>
       </c>
@@ -6737,19 +7911,26 @@
       <c r="H118" s="33">
         <v>78.636828100000002</v>
       </c>
-      <c r="J118" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L118">
+      <c r="I118" s="33"/>
+      <c r="J118" s="90">
+        <v>50.910699999999999</v>
+      </c>
+      <c r="L118" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N118">
         <v>144.97095210000001</v>
       </c>
-      <c r="N118">
+      <c r="P118">
         <v>191.66834940000001</v>
       </c>
-    </row>
-    <row r="119" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A119" s="55"/>
-      <c r="B119" s="60"/>
+      <c r="R118">
+        <v>50.896900000000002</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A119" s="53"/>
+      <c r="B119" s="47"/>
       <c r="C119">
         <v>5</v>
       </c>
@@ -6764,19 +7945,26 @@
       <c r="H119" s="33">
         <v>78.712250999999995</v>
       </c>
-      <c r="J119" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L119">
+      <c r="I119" s="33"/>
+      <c r="J119" s="90">
+        <v>50.9011</v>
+      </c>
+      <c r="L119" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N119">
         <v>72.438531600000005</v>
       </c>
-      <c r="N119">
+      <c r="P119">
         <v>95.527129200000005</v>
       </c>
-    </row>
-    <row r="120" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A120" s="55"/>
-      <c r="B120" s="60"/>
+      <c r="R119">
+        <v>50.631399999999999</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A120" s="53"/>
+      <c r="B120" s="47"/>
       <c r="C120">
         <v>6</v>
       </c>
@@ -6791,19 +7979,26 @@
       <c r="H120" s="33">
         <v>396.00587339999998</v>
       </c>
-      <c r="J120" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L120">
+      <c r="I120" s="33"/>
+      <c r="J120" s="90">
+        <v>50.796599999999998</v>
+      </c>
+      <c r="L120" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N120">
         <v>282.17546399999998</v>
       </c>
-      <c r="N120">
+      <c r="P120">
         <v>97.068762699999994</v>
       </c>
-    </row>
-    <row r="121" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="55"/>
-      <c r="B121" s="60"/>
+      <c r="R120" s="83">
+        <v>50.25</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="53"/>
+      <c r="B121" s="47"/>
       <c r="C121">
         <v>7</v>
       </c>
@@ -6818,19 +8013,26 @@
       <c r="H121" s="33">
         <v>242.74594289999999</v>
       </c>
-      <c r="J121" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L121">
+      <c r="I121" s="33"/>
+      <c r="J121" s="90">
+        <v>51.620199999999997</v>
+      </c>
+      <c r="L121" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N121">
         <v>290.40525339999999</v>
       </c>
-      <c r="N121">
+      <c r="P121">
         <v>95.341222599999995</v>
       </c>
-    </row>
-    <row r="122" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="55"/>
-      <c r="B122" s="60"/>
+      <c r="R121">
+        <v>50.871899999999997</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="53"/>
+      <c r="B122" s="47"/>
       <c r="C122">
         <v>8</v>
       </c>
@@ -6845,19 +8047,26 @@
       <c r="H122" s="33">
         <v>78.237251799999996</v>
       </c>
-      <c r="J122" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L122">
+      <c r="I122" s="33"/>
+      <c r="J122" s="90">
+        <v>51.393599999999999</v>
+      </c>
+      <c r="L122" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N122">
         <v>215.324352</v>
       </c>
-      <c r="N122">
+      <c r="P122">
         <v>142.11990599999999</v>
       </c>
-    </row>
-    <row r="123" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="55"/>
-      <c r="B123" s="60"/>
+      <c r="R122">
+        <v>50.534100000000002</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="53"/>
+      <c r="B123" s="47"/>
       <c r="C123">
         <v>9</v>
       </c>
@@ -6872,19 +8081,26 @@
       <c r="H123" s="33">
         <v>81.641992000000002</v>
       </c>
-      <c r="J123" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L123">
+      <c r="I123" s="33"/>
+      <c r="J123" s="90">
+        <v>51.420200000000001</v>
+      </c>
+      <c r="L123" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N123">
         <v>140.54426609999999</v>
       </c>
-      <c r="N123">
+      <c r="P123">
         <v>69.517111099999994</v>
       </c>
-    </row>
-    <row r="124" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="55"/>
-      <c r="B124" s="61"/>
+      <c r="R123">
+        <v>50.344099999999997</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="53"/>
+      <c r="B124" s="48"/>
       <c r="C124">
         <v>10</v>
       </c>
@@ -6898,19 +8114,26 @@
       <c r="H124" s="31">
         <v>78.717697200000003</v>
       </c>
-      <c r="J124" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L124">
+      <c r="I124" s="31"/>
+      <c r="J124" s="92">
+        <v>51.58</v>
+      </c>
+      <c r="L124" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N124">
         <v>140.9688342</v>
       </c>
-      <c r="N124">
+      <c r="P124">
         <v>139.7056632</v>
       </c>
-    </row>
-    <row r="125" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A125" s="55"/>
-      <c r="B125" s="59" t="s">
+      <c r="R124">
+        <v>50.293900000000001</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A125" s="53"/>
+      <c r="B125" s="46" t="s">
         <v>48</v>
       </c>
       <c r="C125">
@@ -6927,19 +8150,26 @@
       <c r="H125" s="33">
         <v>80.974393000000006</v>
       </c>
-      <c r="J125" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L125">
+      <c r="I125" s="33"/>
+      <c r="J125" s="93">
+        <v>52.299199999999999</v>
+      </c>
+      <c r="L125" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N125">
         <v>212.90962529999999</v>
       </c>
-      <c r="N125">
+      <c r="P125">
         <v>77.481720800000005</v>
       </c>
-    </row>
-    <row r="126" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A126" s="55"/>
-      <c r="B126" s="60"/>
+      <c r="R125" s="33">
+        <v>59.0197</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A126" s="53"/>
+      <c r="B126" s="47"/>
       <c r="C126">
         <v>2</v>
       </c>
@@ -6954,19 +8184,26 @@
       <c r="H126" s="33">
         <v>87.044013899999996</v>
       </c>
-      <c r="J126" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L126">
+      <c r="I126" s="33"/>
+      <c r="J126" s="93">
+        <v>50.614699999999999</v>
+      </c>
+      <c r="L126" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N126">
         <v>217.74866639999999</v>
       </c>
-      <c r="N126">
+      <c r="P126">
         <v>77.597401199999993</v>
       </c>
-    </row>
-    <row r="127" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A127" s="55"/>
-      <c r="B127" s="60"/>
+      <c r="R126" s="33">
+        <v>53.289200000000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A127" s="53"/>
+      <c r="B127" s="47"/>
       <c r="C127">
         <v>3</v>
       </c>
@@ -6981,19 +8218,26 @@
       <c r="H127" s="33">
         <v>88.587937499999995</v>
       </c>
-      <c r="J127" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L127">
+      <c r="I127" s="33"/>
+      <c r="J127" s="93">
+        <v>50.531399999999998</v>
+      </c>
+      <c r="L127" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N127">
         <v>212.84175049999999</v>
       </c>
-      <c r="N127">
+      <c r="P127">
         <v>89.024965499999993</v>
       </c>
-    </row>
-    <row r="128" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A128" s="55"/>
-      <c r="B128" s="60"/>
+      <c r="R127" s="33">
+        <v>52.644300000000001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A128" s="53"/>
+      <c r="B128" s="47"/>
       <c r="C128">
         <v>4</v>
       </c>
@@ -7008,19 +8252,26 @@
       <c r="H128" s="33">
         <v>83.735353000000003</v>
       </c>
-      <c r="J128" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L128">
+      <c r="I128" s="33"/>
+      <c r="J128" s="93">
+        <v>50.688400000000001</v>
+      </c>
+      <c r="L128" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N128">
         <v>71.781501199999994</v>
       </c>
-      <c r="N128">
+      <c r="P128">
         <v>84.717883599999993</v>
       </c>
-    </row>
-    <row r="129" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A129" s="55"/>
-      <c r="B129" s="60"/>
+      <c r="R128" s="33">
+        <v>51.373899999999999</v>
+      </c>
+    </row>
+    <row r="129" spans="1:20" ht="16" x14ac:dyDescent="0.2">
+      <c r="A129" s="53"/>
+      <c r="B129" s="47"/>
       <c r="C129">
         <v>5</v>
       </c>
@@ -7035,19 +8286,26 @@
       <c r="H129" s="33">
         <v>78.882186200000007</v>
       </c>
-      <c r="J129" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L129">
+      <c r="I129" s="33"/>
+      <c r="J129" s="93">
+        <v>51.0458</v>
+      </c>
+      <c r="L129" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N129">
         <v>213.31621939999999</v>
       </c>
-      <c r="N129">
+      <c r="P129">
         <v>79.496501199999997</v>
       </c>
-    </row>
-    <row r="130" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A130" s="55"/>
-      <c r="B130" s="60"/>
+      <c r="R129" s="33">
+        <v>50.450200000000002</v>
+      </c>
+    </row>
+    <row r="130" spans="1:20" ht="16" x14ac:dyDescent="0.2">
+      <c r="A130" s="53"/>
+      <c r="B130" s="47"/>
       <c r="C130">
         <v>6</v>
       </c>
@@ -7062,19 +8320,26 @@
       <c r="H130" s="33">
         <v>77.985264799999996</v>
       </c>
-      <c r="J130" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L130">
+      <c r="I130" s="33"/>
+      <c r="J130" s="93">
+        <v>51.209400000000002</v>
+      </c>
+      <c r="L130" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N130">
         <v>348.75418839999998</v>
       </c>
-      <c r="N130">
+      <c r="P130">
         <v>80.706606300000004</v>
       </c>
-    </row>
-    <row r="131" spans="1:16" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="55"/>
-      <c r="B131" s="60"/>
+      <c r="R130" s="33">
+        <v>50.359699999999997</v>
+      </c>
+    </row>
+    <row r="131" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="53"/>
+      <c r="B131" s="47"/>
       <c r="C131">
         <v>7</v>
       </c>
@@ -7089,19 +8354,26 @@
       <c r="H131" s="33">
         <v>81.148442500000002</v>
       </c>
-      <c r="J131" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L131">
+      <c r="I131" s="33"/>
+      <c r="J131" s="93">
+        <v>50.741500000000002</v>
+      </c>
+      <c r="L131" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N131">
         <v>70.685447999999994</v>
       </c>
-      <c r="N131">
+      <c r="P131">
         <v>83.2099209</v>
       </c>
-    </row>
-    <row r="132" spans="1:16" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="55"/>
-      <c r="B132" s="60"/>
+      <c r="R131" s="33">
+        <v>50.342700000000001</v>
+      </c>
+    </row>
+    <row r="132" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="53"/>
+      <c r="B132" s="47"/>
       <c r="C132">
         <v>8</v>
       </c>
@@ -7116,19 +8388,26 @@
       <c r="H132" s="33">
         <v>77.694044700000006</v>
       </c>
-      <c r="J132" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L132">
+      <c r="I132" s="33"/>
+      <c r="J132" s="93">
+        <v>50.7605</v>
+      </c>
+      <c r="L132" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N132">
         <v>280.10586769999998</v>
       </c>
-      <c r="N132">
+      <c r="P132">
         <v>85.678925399999997</v>
       </c>
-    </row>
-    <row r="133" spans="1:16" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="55"/>
-      <c r="B133" s="60"/>
+      <c r="R132" s="33">
+        <v>50.582500000000003</v>
+      </c>
+    </row>
+    <row r="133" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="53"/>
+      <c r="B133" s="47"/>
       <c r="C133">
         <v>9</v>
       </c>
@@ -7143,19 +8422,26 @@
       <c r="H133" s="33">
         <v>79.305596800000004</v>
       </c>
-      <c r="J133" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L133">
+      <c r="I133" s="33"/>
+      <c r="J133" s="93">
+        <v>50.810699999999997</v>
+      </c>
+      <c r="L133" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N133">
         <v>140.0890728</v>
       </c>
-      <c r="N133">
+      <c r="P133">
         <v>77.875469800000005</v>
       </c>
-    </row>
-    <row r="134" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="55"/>
-      <c r="B134" s="61"/>
+      <c r="R133" s="33">
+        <v>50.709800000000001</v>
+      </c>
+    </row>
+    <row r="134" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="53"/>
+      <c r="B134" s="48"/>
       <c r="C134">
         <v>10</v>
       </c>
@@ -7169,32 +8455,39 @@
       <c r="H134" s="31">
         <v>79.388584199999997</v>
       </c>
-      <c r="J134" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L134">
+      <c r="I134" s="31"/>
+      <c r="J134" s="93">
+        <v>50.944000000000003</v>
+      </c>
+      <c r="L134" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="N134">
         <v>140.0952983</v>
       </c>
-      <c r="N134">
+      <c r="P134">
         <v>70.746495100000004</v>
       </c>
-    </row>
-    <row r="135" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R134" s="31">
+        <v>51.292299999999997</v>
+      </c>
+    </row>
+    <row r="135" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="28"/>
       <c r="B135" s="1"/>
     </row>
-    <row r="136" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="28"/>
       <c r="B136" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D136" s="31" t="e">
-        <f t="shared" ref="D136" si="18">AVERAGE(D74:D134)</f>
+        <f t="shared" ref="D136" si="20">AVERAGE(D74:D134)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E136" s="31"/>
       <c r="F136" s="31">
-        <f t="shared" ref="F136" si="19">AVERAGE(F74:F134)</f>
+        <f t="shared" ref="F136" si="21">AVERAGE(F74:F134)</f>
         <v>570.32474507166648</v>
       </c>
       <c r="G136" s="31"/>
@@ -7203,35 +8496,45 @@
         <v>212.93918055999998</v>
       </c>
       <c r="I136" s="31"/>
-      <c r="J136" s="31" t="e">
-        <f t="shared" ref="J136:N136" si="20">AVERAGE(J74:J134)</f>
+      <c r="J136" s="31">
+        <f>AVERAGE(J74:J134)</f>
+        <v>60.499589999999984</v>
+      </c>
+      <c r="K136" s="31"/>
+      <c r="L136" s="31" t="e">
+        <f t="shared" ref="L136:P136" si="22">AVERAGE(L74:L134)</f>
         <v>#DIV/0!</v>
-      </c>
-      <c r="K136" s="31"/>
-      <c r="L136" s="31">
-        <f t="shared" si="20"/>
-        <v>424.62852865714297</v>
       </c>
       <c r="M136" s="31"/>
       <c r="N136" s="31">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
+        <v>424.62852865714297</v>
+      </c>
+      <c r="O136" s="31"/>
+      <c r="P136" s="31">
+        <f t="shared" si="22"/>
         <v>283.29640059000008</v>
       </c>
-      <c r="O136" s="31"/>
-      <c r="P136" s="31"/>
-    </row>
-    <row r="137" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q136" s="31"/>
+      <c r="R136" s="31">
+        <f t="shared" ref="Q136:R136" si="23">AVERAGE(R74:R134)</f>
+        <v>54.376823333333355</v>
+      </c>
+      <c r="S136" s="31"/>
+      <c r="T136" s="31"/>
+    </row>
+    <row r="137" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="28"/>
       <c r="B137" s="1" t="s">
         <v>81</v>
       </c>
       <c r="D137" s="31">
-        <f t="shared" ref="D137" si="21">MIN(D74:D134)</f>
+        <f t="shared" ref="D137" si="24">MIN(D74:D134)</f>
         <v>0</v>
       </c>
       <c r="E137" s="31"/>
       <c r="F137" s="31">
-        <f t="shared" ref="F137" si="22">MIN(F74:F134)</f>
+        <f t="shared" ref="F137" si="25">MIN(F74:F134)</f>
         <v>64.483929500000002</v>
       </c>
       <c r="G137" s="31"/>
@@ -7241,34 +8544,44 @@
       </c>
       <c r="I137" s="31"/>
       <c r="J137" s="31">
-        <f t="shared" ref="J137:N137" si="23">MIN(J74:J134)</f>
-        <v>0</v>
+        <f>MIN(J74:J134)</f>
+        <v>50.256300000000003</v>
       </c>
       <c r="K137" s="31"/>
       <c r="L137" s="31">
-        <f t="shared" si="23"/>
-        <v>69.129179500000006</v>
+        <f t="shared" ref="L137:P137" si="26">MIN(L74:L134)</f>
+        <v>0</v>
       </c>
       <c r="M137" s="31"/>
       <c r="N137" s="31">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
+        <v>69.129179500000006</v>
+      </c>
+      <c r="O137" s="31"/>
+      <c r="P137" s="31">
+        <f t="shared" si="26"/>
         <v>65.962567100000001</v>
       </c>
-      <c r="O137" s="31"/>
-      <c r="P137" s="31"/>
-    </row>
-    <row r="138" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q137" s="31"/>
+      <c r="R137" s="31">
+        <f t="shared" ref="Q137:R137" si="27">MIN(R74:R134)</f>
+        <v>49.9163</v>
+      </c>
+      <c r="S137" s="31"/>
+      <c r="T137" s="31"/>
+    </row>
+    <row r="138" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="28"/>
       <c r="B138" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D138" s="31">
-        <f t="shared" ref="D138" si="24">MAX(D74:D134)</f>
+        <f t="shared" ref="D138" si="28">MAX(D74:D134)</f>
         <v>0</v>
       </c>
       <c r="E138" s="31"/>
       <c r="F138" s="31">
-        <f t="shared" ref="F138" si="25">MAX(F74:F134)</f>
+        <f t="shared" ref="F138" si="29">MAX(F74:F134)</f>
         <v>2543.6004963999999</v>
       </c>
       <c r="G138" s="31"/>
@@ -7278,34 +8591,44 @@
       </c>
       <c r="I138" s="31"/>
       <c r="J138" s="31">
-        <f t="shared" ref="J138:N138" si="26">MAX(J74:J134)</f>
-        <v>0</v>
+        <f>MAX(J74:J134)</f>
+        <v>353.98700000000002</v>
       </c>
       <c r="K138" s="31"/>
       <c r="L138" s="31">
-        <f t="shared" si="26"/>
-        <v>3419.3379930999999</v>
+        <f t="shared" ref="L138:P138" si="30">MAX(L74:L134)</f>
+        <v>0</v>
       </c>
       <c r="M138" s="31"/>
       <c r="N138" s="31">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
+        <v>3419.3379930999999</v>
+      </c>
+      <c r="O138" s="31"/>
+      <c r="P138" s="31">
+        <f t="shared" si="30"/>
         <v>2129.4957175999998</v>
       </c>
-      <c r="O138" s="31"/>
-      <c r="P138" s="31"/>
-    </row>
-    <row r="139" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q138" s="31"/>
+      <c r="R138" s="31">
+        <f t="shared" ref="Q138:R138" si="31">MAX(R74:R134)</f>
+        <v>102.2818</v>
+      </c>
+      <c r="S138" s="31"/>
+      <c r="T138" s="31"/>
+    </row>
+    <row r="139" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="28"/>
       <c r="B139" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D139" s="31" t="e">
-        <f t="shared" ref="D139" si="27">STDEV(D74:D134)</f>
+        <f t="shared" ref="D139" si="32">STDEV(D74:D134)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E139" s="31"/>
       <c r="F139" s="31">
-        <f t="shared" ref="F139" si="28">STDEV(F74:F134)</f>
+        <f t="shared" ref="F139" si="33">STDEV(F74:F134)</f>
         <v>551.46046394672555</v>
       </c>
       <c r="G139" s="31"/>
@@ -7314,55 +8637,68 @@
         <v>226.1189487780623</v>
       </c>
       <c r="I139" s="31"/>
-      <c r="J139" s="31" t="e">
-        <f t="shared" ref="J139:N139" si="29">STDEV(J74:J134)</f>
+      <c r="J139" s="31">
+        <f>STDEV(J74:J134)</f>
+        <v>46.769044041917475</v>
+      </c>
+      <c r="K139" s="31"/>
+      <c r="L139" s="31" t="e">
+        <f t="shared" ref="L139:P139" si="34">STDEV(L74:L134)</f>
         <v>#DIV/0!</v>
-      </c>
-      <c r="K139" s="31"/>
-      <c r="L139" s="31">
-        <f t="shared" si="29"/>
-        <v>645.77916920766768</v>
       </c>
       <c r="M139" s="31"/>
       <c r="N139" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
+        <v>645.77916920766768</v>
+      </c>
+      <c r="O139" s="31"/>
+      <c r="P139" s="31">
+        <f t="shared" si="34"/>
         <v>356.31758150072289</v>
       </c>
-      <c r="O139" s="31"/>
-      <c r="P139" s="31"/>
-    </row>
-    <row r="140" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="Q139" s="31"/>
+      <c r="R139" s="31">
+        <f t="shared" ref="Q139:R139" si="35">STDEV(R74:R134)</f>
+        <v>12.653955605550385</v>
+      </c>
+      <c r="S139" s="31"/>
+      <c r="T139" s="31"/>
+    </row>
+    <row r="140" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A140" s="4"/>
       <c r="D140" s="34"/>
       <c r="E140" s="19"/>
       <c r="F140" s="19"/>
       <c r="G140" s="19"/>
       <c r="H140" s="19"/>
-    </row>
-    <row r="141" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="I140" s="19"/>
+      <c r="J140" s="19"/>
+    </row>
+    <row r="141" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A141" s="4"/>
       <c r="D141" s="34"/>
       <c r="E141" s="19"/>
       <c r="F141" s="19"/>
       <c r="G141" s="19"/>
       <c r="H141" s="19"/>
+      <c r="I141" s="19"/>
+      <c r="J141" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="J1:N2"/>
+  <mergeCells count="35">
+    <mergeCell ref="AL44:AO44"/>
+    <mergeCell ref="AL36:AO36"/>
+    <mergeCell ref="W65:AD65"/>
+    <mergeCell ref="W9:Z9"/>
+    <mergeCell ref="W36:Z36"/>
+    <mergeCell ref="AB36:AE36"/>
+    <mergeCell ref="D1:J2"/>
+    <mergeCell ref="L1:R2"/>
     <mergeCell ref="J3:J4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="B27:B36"/>
-    <mergeCell ref="D1:H2"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="B7:B16"/>
-    <mergeCell ref="B17:B26"/>
-    <mergeCell ref="AC36:AF36"/>
-    <mergeCell ref="X44:AA44"/>
-    <mergeCell ref="AC44:AF44"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="AG36:AJ36"/>
+    <mergeCell ref="AB44:AE44"/>
+    <mergeCell ref="AG44:AJ44"/>
     <mergeCell ref="A74:A134"/>
     <mergeCell ref="B74:B83"/>
     <mergeCell ref="B84:B93"/>
@@ -7374,34 +8710,24 @@
     <mergeCell ref="B48:B57"/>
     <mergeCell ref="B58:B67"/>
     <mergeCell ref="A7:A67"/>
-    <mergeCell ref="S54:V54"/>
-    <mergeCell ref="X54:AA54"/>
-    <mergeCell ref="S65:X65"/>
-    <mergeCell ref="S9:V9"/>
-    <mergeCell ref="S36:V36"/>
-    <mergeCell ref="X36:AA36"/>
+    <mergeCell ref="W54:Z54"/>
+    <mergeCell ref="AB54:AE54"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="B27:B36"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="B7:B16"/>
+    <mergeCell ref="B17:B26"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001DB4A8D4FA53A74C8DD903E2AA11403B" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9513ce20363a6a392200d549223f9677">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e16ae15f-114f-47f3-812f-99bedbca4995" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="32ab30f1da6742da7917429fac681e44" ns2:_="">
     <xsd:import namespace="e16ae15f-114f-47f3-812f-99bedbca4995"/>
@@ -7545,24 +8871,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A47F65F-C790-4490-A4C6-39EA686EC5FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0857D451-F364-4B92-BA89-D9BE453D8776}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{535B239F-CB92-4DF0-9441-AC6CE80C8C29}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7578,4 +8902,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0857D451-F364-4B92-BA89-D9BE453D8776}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A47F65F-C790-4490-A4C6-39EA686EC5FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/eBike_controller/Results.xlsx
+++ b/eBike_controller/Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrea/Documents/GitHub/HECATE_BikeAndDrone/eBike_controller/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21180B4-1CD2-F243-8528-1A4F8C19F792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0280806D-26FB-7A49-9266-F389D0813B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="68640" yWindow="-9480" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="117">
   <si>
     <t>SA_TALIRO</t>
   </si>
@@ -643,7 +643,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -868,9 +868,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1280,7 +1277,7 @@
       </c>
       <c r="I3" s="55"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="84"/>
+      <c r="K3" s="83"/>
       <c r="L3" s="54" t="s">
         <v>4</v>
       </c>
@@ -1303,7 +1300,7 @@
       </c>
       <c r="Y3" s="55"/>
       <c r="Z3" s="56"/>
-      <c r="AA3" s="84"/>
+      <c r="AA3" s="83"/>
       <c r="AB3" s="54" t="s">
         <v>4</v>
       </c>
@@ -1324,7 +1321,7 @@
       <c r="H4" s="57"/>
       <c r="I4" s="58"/>
       <c r="J4" s="59"/>
-      <c r="K4" s="84"/>
+      <c r="K4" s="83"/>
       <c r="L4" s="57"/>
       <c r="M4" s="58"/>
       <c r="N4" s="59"/>
@@ -1339,7 +1336,7 @@
       <c r="X4" s="57"/>
       <c r="Y4" s="58"/>
       <c r="Z4" s="59"/>
-      <c r="AA4" s="84"/>
+      <c r="AA4" s="83"/>
       <c r="AB4" s="57"/>
       <c r="AC4" s="58"/>
       <c r="AD4" s="59"/>
@@ -1406,7 +1403,7 @@
       <c r="J6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="84"/>
+      <c r="K6" s="83"/>
       <c r="L6" s="5" t="s">
         <v>7</v>
       </c>
@@ -1445,7 +1442,7 @@
       <c r="Z6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="AA6" s="84"/>
+      <c r="AA6" s="83"/>
       <c r="AB6" s="5" t="s">
         <v>7</v>
       </c>
@@ -1498,7 +1495,7 @@
       <c r="J8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K8" s="87"/>
+      <c r="K8" s="86"/>
       <c r="L8" s="11" t="s">
         <v>12</v>
       </c>
@@ -1509,9 +1506,15 @@
         <v>17</v>
       </c>
       <c r="O8" s="9"/>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="67"/>
-      <c r="R8" s="68"/>
+      <c r="P8" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R8" s="68" t="s">
+        <v>17</v>
+      </c>
       <c r="T8" s="11" t="s">
         <v>12</v>
       </c>
@@ -1531,7 +1534,7 @@
       <c r="Z8" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="AA8" s="85"/>
+      <c r="AA8" s="84"/>
       <c r="AB8" s="13" t="s">
         <v>12</v>
       </c>
@@ -1542,9 +1545,15 @@
         <v>14</v>
       </c>
       <c r="AE8" s="9"/>
-      <c r="AF8" s="80"/>
-      <c r="AG8" s="80"/>
-      <c r="AH8" s="80"/>
+      <c r="AF8" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG8" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH8" s="68" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="9" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="61"/>
@@ -1570,7 +1579,7 @@
       <c r="J9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="88"/>
+      <c r="K9" s="87"/>
       <c r="L9" s="11" t="s">
         <v>12</v>
       </c>
@@ -1581,9 +1590,15 @@
         <v>17</v>
       </c>
       <c r="O9" s="9"/>
-      <c r="P9" s="66"/>
-      <c r="Q9" s="68"/>
-      <c r="R9" s="68"/>
+      <c r="P9" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q9" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R9" s="68" t="s">
+        <v>17</v>
+      </c>
       <c r="T9" s="13" t="s">
         <v>12</v>
       </c>
@@ -1603,7 +1618,7 @@
       <c r="Z9" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AA9" s="85"/>
+      <c r="AA9" s="84"/>
       <c r="AB9" s="13" t="s">
         <v>12</v>
       </c>
@@ -1614,9 +1629,15 @@
         <v>17</v>
       </c>
       <c r="AE9" s="9"/>
-      <c r="AF9" s="80"/>
-      <c r="AG9" s="80"/>
-      <c r="AH9" s="80"/>
+      <c r="AF9" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG9" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH9" s="68" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="61"/>
@@ -1642,7 +1663,7 @@
       <c r="J10" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K10" s="89"/>
+      <c r="K10" s="88"/>
       <c r="L10" s="11" t="s">
         <v>12</v>
       </c>
@@ -1653,9 +1674,15 @@
         <v>17</v>
       </c>
       <c r="O10" s="9"/>
-      <c r="P10" s="66"/>
-      <c r="Q10" s="68"/>
-      <c r="R10" s="68"/>
+      <c r="P10" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q10" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R10" s="68" t="s">
+        <v>17</v>
+      </c>
       <c r="T10" s="13" t="s">
         <v>12</v>
       </c>
@@ -1675,7 +1702,7 @@
       <c r="Z10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="AA10" s="85"/>
+      <c r="AA10" s="84"/>
       <c r="AB10" s="13" t="s">
         <v>12</v>
       </c>
@@ -1686,9 +1713,15 @@
         <v>17</v>
       </c>
       <c r="AE10" s="9"/>
-      <c r="AF10" s="80"/>
-      <c r="AG10" s="80"/>
-      <c r="AH10" s="80"/>
+      <c r="AF10" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG10" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH10" s="68" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="11" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="61"/>
@@ -1748,7 +1781,7 @@
       <c r="J12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="89"/>
+      <c r="K12" s="88"/>
       <c r="L12" s="11" t="s">
         <v>12</v>
       </c>
@@ -1759,9 +1792,15 @@
         <v>38</v>
       </c>
       <c r="O12" s="9"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="68"/>
-      <c r="R12" s="68"/>
+      <c r="P12" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R12" s="68" t="s">
+        <v>17</v>
+      </c>
       <c r="T12" s="16" t="s">
         <v>12</v>
       </c>
@@ -1781,7 +1820,7 @@
       <c r="Z12" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AA12" s="85"/>
+      <c r="AA12" s="84"/>
       <c r="AB12" s="16" t="s">
         <v>12</v>
       </c>
@@ -1792,9 +1831,15 @@
         <v>17</v>
       </c>
       <c r="AE12" s="9"/>
-      <c r="AF12" s="80"/>
-      <c r="AG12" s="80"/>
-      <c r="AH12" s="80"/>
+      <c r="AF12" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG12" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH12" s="68" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="13" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="61"/>
@@ -1820,7 +1865,7 @@
       <c r="J13" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="K13" s="89"/>
+      <c r="K13" s="88"/>
       <c r="L13" s="11" t="s">
         <v>12</v>
       </c>
@@ -1831,9 +1876,15 @@
         <v>17</v>
       </c>
       <c r="O13" s="9"/>
-      <c r="P13" s="66"/>
-      <c r="Q13" s="68"/>
-      <c r="R13" s="68"/>
+      <c r="P13" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q13" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R13" s="68" t="s">
+        <v>17</v>
+      </c>
       <c r="T13" s="11" t="s">
         <v>12</v>
       </c>
@@ -1853,7 +1904,7 @@
       <c r="Z13" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="AA13" s="85"/>
+      <c r="AA13" s="84"/>
       <c r="AB13" s="13" t="s">
         <v>12</v>
       </c>
@@ -1864,9 +1915,15 @@
         <v>17</v>
       </c>
       <c r="AE13" s="9"/>
-      <c r="AF13" s="80"/>
-      <c r="AG13" s="80"/>
-      <c r="AH13" s="80"/>
+      <c r="AF13" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG13" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH13" s="68" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="14" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="62"/>
@@ -1892,7 +1949,7 @@
       <c r="J14" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="K14" s="88"/>
+      <c r="K14" s="87"/>
       <c r="L14" s="11" t="s">
         <v>12</v>
       </c>
@@ -1903,9 +1960,15 @@
         <v>17</v>
       </c>
       <c r="O14" s="9"/>
-      <c r="P14" s="66"/>
-      <c r="Q14" s="68"/>
-      <c r="R14" s="68"/>
+      <c r="P14" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q14" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R14" s="68" t="s">
+        <v>17</v>
+      </c>
       <c r="T14" s="16" t="s">
         <v>12</v>
       </c>
@@ -1925,7 +1988,7 @@
       <c r="Z14" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="AA14" s="85"/>
+      <c r="AA14" s="84"/>
       <c r="AB14" s="13" t="s">
         <v>12</v>
       </c>
@@ -1936,9 +1999,15 @@
         <v>17</v>
       </c>
       <c r="AE14" s="9"/>
-      <c r="AF14" s="80"/>
-      <c r="AG14" s="80"/>
-      <c r="AH14" s="80"/>
+      <c r="AF14" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG14" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH14" s="68" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="15" spans="1:34" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
@@ -2028,7 +2097,7 @@
       <c r="J17" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K17" s="88"/>
+      <c r="K17" s="87"/>
       <c r="L17" s="6" t="s">
         <v>12</v>
       </c>
@@ -2042,10 +2111,10 @@
       <c r="P17" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="Q17" s="81" t="s">
+      <c r="Q17" s="80" t="s">
         <v>77</v>
       </c>
-      <c r="R17" s="81" t="s">
+      <c r="R17" s="80" t="s">
         <v>17</v>
       </c>
       <c r="T17" s="13" t="s">
@@ -2063,7 +2132,7 @@
       <c r="Z17" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="AA17" s="86"/>
+      <c r="AA17" s="85"/>
       <c r="AB17" s="14" t="s">
         <v>12</v>
       </c>
@@ -2077,10 +2146,10 @@
       <c r="AF17" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="AG17" s="81" t="s">
+      <c r="AG17" s="80" t="s">
         <v>112</v>
       </c>
-      <c r="AH17" s="81" t="s">
+      <c r="AH17" s="80" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2104,7 +2173,7 @@
       <c r="J18" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K18" s="87"/>
+      <c r="K18" s="86"/>
       <c r="L18" s="6" t="s">
         <v>12</v>
       </c>
@@ -2139,7 +2208,7 @@
       <c r="Z18" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="AA18" s="85"/>
+      <c r="AA18" s="84"/>
       <c r="AB18" s="13" t="s">
         <v>12</v>
       </c>
@@ -2180,7 +2249,7 @@
       <c r="J19" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="K19" s="89"/>
+      <c r="K19" s="88"/>
       <c r="L19" s="11" t="s">
         <v>12</v>
       </c>
@@ -2215,7 +2284,7 @@
       <c r="Z19" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="AA19" s="85"/>
+      <c r="AA19" s="84"/>
       <c r="AB19" s="13" t="s">
         <v>12</v>
       </c>
@@ -2290,7 +2359,7 @@
       <c r="J21" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="K21" s="88"/>
+      <c r="K21" s="87"/>
       <c r="L21" s="11" t="s">
         <v>12</v>
       </c>
@@ -2325,7 +2394,7 @@
       <c r="Z21" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="AA21" s="85"/>
+      <c r="AA21" s="84"/>
       <c r="AB21" s="11" t="s">
         <v>12</v>
       </c>
@@ -2366,7 +2435,7 @@
       <c r="J22" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="K22" s="88"/>
+      <c r="K22" s="87"/>
       <c r="L22" s="11" t="s">
         <v>12</v>
       </c>
@@ -2401,7 +2470,7 @@
       <c r="Z22" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="AA22" s="85"/>
+      <c r="AA22" s="84"/>
       <c r="AB22" s="11" t="s">
         <v>12</v>
       </c>
@@ -2442,7 +2511,7 @@
       <c r="J23" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="K23" s="85"/>
+      <c r="K23" s="84"/>
       <c r="L23" s="11" t="s">
         <v>12</v>
       </c>
@@ -2477,7 +2546,7 @@
       <c r="Z23" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="AA23" s="85"/>
+      <c r="AA23" s="84"/>
       <c r="AB23" s="11" t="s">
         <v>12</v>
       </c>
@@ -2687,7 +2756,9 @@
       <c r="H8" s="18">
         <v>1378</v>
       </c>
-      <c r="J8" s="21"/>
+      <c r="J8" s="21">
+        <v>354</v>
+      </c>
       <c r="K8" s="20"/>
       <c r="L8" s="18">
         <v>1146</v>
@@ -2700,7 +2771,9 @@
       <c r="P8" s="21">
         <v>1360</v>
       </c>
-      <c r="R8" s="21"/>
+      <c r="R8" s="21">
+        <v>361</v>
+      </c>
     </row>
     <row r="9" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="53"/>
@@ -2718,7 +2791,9 @@
       <c r="H9" s="18">
         <v>721</v>
       </c>
-      <c r="J9" s="21"/>
+      <c r="J9" s="21">
+        <v>345</v>
+      </c>
       <c r="K9" s="20"/>
       <c r="L9" s="21">
         <v>5441</v>
@@ -2731,7 +2806,9 @@
       <c r="P9" s="21">
         <v>716</v>
       </c>
-      <c r="R9" s="21"/>
+      <c r="R9" s="21">
+        <v>345</v>
+      </c>
     </row>
     <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="53"/>
@@ -2749,7 +2826,9 @@
       <c r="H10" s="18">
         <v>739</v>
       </c>
-      <c r="J10" s="21"/>
+      <c r="J10" s="21">
+        <v>350</v>
+      </c>
       <c r="K10" s="20"/>
       <c r="L10" s="21">
         <v>7589</v>
@@ -2762,7 +2841,9 @@
       <c r="P10" s="21">
         <v>719</v>
       </c>
-      <c r="R10" s="21"/>
+      <c r="R10" s="21">
+        <v>349</v>
+      </c>
     </row>
     <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="53"/>
@@ -2797,7 +2878,9 @@
       <c r="H12" s="18">
         <v>1699</v>
       </c>
-      <c r="J12" s="21"/>
+      <c r="J12" s="21">
+        <v>330</v>
+      </c>
       <c r="K12" s="20"/>
       <c r="L12" s="21">
         <v>6372</v>
@@ -2810,7 +2893,9 @@
       <c r="P12" s="21">
         <v>1145</v>
       </c>
-      <c r="R12" s="21"/>
+      <c r="R12" s="21">
+        <v>331</v>
+      </c>
     </row>
     <row r="13" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="53"/>
@@ -2828,7 +2913,9 @@
       <c r="H13" s="18">
         <v>650</v>
       </c>
-      <c r="J13" s="21"/>
+      <c r="J13" s="21">
+        <v>335</v>
+      </c>
       <c r="K13" s="20"/>
       <c r="L13" s="18">
         <v>10452</v>
@@ -2841,7 +2928,9 @@
       <c r="P13" s="21">
         <v>716</v>
       </c>
-      <c r="R13" s="21"/>
+      <c r="R13" s="21">
+        <v>330</v>
+      </c>
     </row>
     <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="53"/>
@@ -2859,7 +2948,9 @@
       <c r="H14" s="18">
         <v>653</v>
       </c>
-      <c r="J14" s="21"/>
+      <c r="J14" s="21">
+        <v>338</v>
+      </c>
       <c r="K14" s="20"/>
       <c r="L14" s="21">
         <v>4797</v>
@@ -2872,7 +2963,9 @@
       <c r="P14" s="21">
         <v>717</v>
       </c>
-      <c r="R14" s="21"/>
+      <c r="R14" s="21">
+        <v>336</v>
+      </c>
     </row>
     <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="53"/>
@@ -2909,9 +3002,9 @@
         <f t="shared" si="0"/>
         <v>1.1265432098765432E-2</v>
       </c>
-      <c r="J16" s="25" t="e">
+      <c r="J16" s="25">
         <f t="shared" ref="J16" si="1">AVERAGE(J8:J14)/86400</f>
-        <v>#DIV/0!</v>
+        <v>3.9583333333333337E-3</v>
       </c>
       <c r="K16" s="20"/>
       <c r="L16" s="25">
@@ -2928,9 +3021,9 @@
         <f t="shared" si="0"/>
         <v>1.0364583333333333E-2</v>
       </c>
-      <c r="R16" s="25" t="e">
+      <c r="R16" s="25">
         <f t="shared" ref="R16" si="2">AVERAGE(R8:R14)/86400</f>
-        <v>#DIV/0!</v>
+        <v>3.9583333333333337E-3</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2954,7 +3047,7 @@
       </c>
       <c r="J17" s="25">
         <f t="shared" ref="J17" si="4">MIN(J8:J14)/86400</f>
-        <v>0</v>
+        <v>3.8194444444444443E-3</v>
       </c>
       <c r="K17" s="20"/>
       <c r="L17" s="25">
@@ -2973,7 +3066,7 @@
       </c>
       <c r="R17" s="25">
         <f t="shared" ref="R17" si="5">MIN(R8:R14)/86400</f>
-        <v>0</v>
+        <v>3.8194444444444443E-3</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2998,7 +3091,7 @@
       <c r="I18" s="10"/>
       <c r="J18" s="25">
         <f t="shared" ref="J18" si="7">MAX(J8:J14)/86400</f>
-        <v>0</v>
+        <v>4.0972222222222226E-3</v>
       </c>
       <c r="K18" s="20"/>
       <c r="L18" s="25">
@@ -3018,7 +3111,7 @@
       <c r="Q18" s="10"/>
       <c r="R18" s="25">
         <f t="shared" ref="R18" si="8">MAX(R8:R14)/86400</f>
-        <v>0</v>
+        <v>4.178240740740741E-3</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3040,9 +3133,9 @@
         <f t="shared" si="9"/>
         <v>5.2175569904686506E-3</v>
       </c>
-      <c r="J19" s="25" t="e">
+      <c r="J19" s="25">
         <f t="shared" ref="J19" si="10">STDEV(J8:J14)/86400</f>
-        <v>#DIV/0!</v>
+        <v>1.0683315517791042E-4</v>
       </c>
       <c r="K19" s="20"/>
       <c r="L19" s="25">
@@ -3059,9 +3152,9 @@
         <f t="shared" si="9"/>
         <v>3.2959317415711177E-3</v>
       </c>
-      <c r="R19" s="25" t="e">
+      <c r="R19" s="25">
         <f t="shared" ref="R19" si="11">STDEV(R8:R14)/86400</f>
-        <v>#DIV/0!</v>
+        <v>1.3888888888888889E-4</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="16" x14ac:dyDescent="0.2">
@@ -3713,7 +3806,9 @@
         <v>86.371557100000004</v>
       </c>
       <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
+      <c r="J7" s="33">
+        <v>36.848300000000002</v>
+      </c>
       <c r="L7">
         <v>77.830788299999995</v>
       </c>
@@ -3724,7 +3819,9 @@
         <v>81.728998700000005</v>
       </c>
       <c r="Q7" s="36"/>
-      <c r="R7" s="33"/>
+      <c r="R7" s="89">
+        <v>38.036000000000001</v>
+      </c>
     </row>
     <row r="8" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="53"/>
@@ -3744,7 +3841,9 @@
         <v>80.167861900000005</v>
       </c>
       <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
+      <c r="J8" s="33">
+        <v>34.873800000000003</v>
+      </c>
       <c r="L8">
         <v>69.680095600000001</v>
       </c>
@@ -3753,6 +3852,9 @@
       </c>
       <c r="P8">
         <v>84.766424000000001</v>
+      </c>
+      <c r="R8" s="82">
+        <v>36.788200000000003</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="16" x14ac:dyDescent="0.2">
@@ -3773,7 +3875,9 @@
         <v>77.724527300000005</v>
       </c>
       <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
+      <c r="J9" s="33">
+        <v>35.922600000000003</v>
+      </c>
       <c r="L9">
         <v>72.386975800000002</v>
       </c>
@@ -3782,6 +3886,9 @@
       </c>
       <c r="P9">
         <v>157.49419499999999</v>
+      </c>
+      <c r="R9" s="82">
+        <v>35.093800000000002</v>
       </c>
       <c r="W9" s="51" t="s">
         <v>89</v>
@@ -3808,7 +3915,9 @@
         <v>230.29127550000001</v>
       </c>
       <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
+      <c r="J10" s="89">
+        <v>35.101999999999997</v>
+      </c>
       <c r="L10">
         <v>216.59442749999999</v>
       </c>
@@ -3817,6 +3926,9 @@
       </c>
       <c r="P10">
         <v>78.742313800000005</v>
+      </c>
+      <c r="R10" s="82">
+        <v>34.863700000000001</v>
       </c>
       <c r="X10" s="38"/>
       <c r="Y10" s="38"/>
@@ -3842,7 +3954,9 @@
         <v>299.50239399999998</v>
       </c>
       <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
+      <c r="J11" s="33">
+        <v>34.963700000000003</v>
+      </c>
       <c r="L11">
         <v>291.95927260000002</v>
       </c>
@@ -3852,16 +3966,19 @@
       <c r="P11">
         <v>153.21892299999999</v>
       </c>
+      <c r="R11" s="82">
+        <v>35.046500000000002</v>
+      </c>
       <c r="W11" s="37" t="s">
         <v>91</v>
       </c>
       <c r="X11" s="10">
         <f>AVERAGE(D38:P67,D7:P36,F74:P103,F105:H134,N105:P134)</f>
-        <v>337.29835891227754</v>
+        <v>310.51520201281267</v>
       </c>
       <c r="Z11" s="26">
         <f>TIME(,,X11)</f>
-        <v>3.9004629629629628E-3</v>
+        <v>3.5879629629629629E-3</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="16" x14ac:dyDescent="0.2">
@@ -3882,7 +3999,9 @@
         <v>73.355889099999999</v>
       </c>
       <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
+      <c r="J12" s="89">
+        <v>34.783999999999999</v>
+      </c>
       <c r="L12">
         <v>77.210132999999999</v>
       </c>
@@ -3892,16 +4011,19 @@
       <c r="P12">
         <v>155.06151919999999</v>
       </c>
+      <c r="R12" s="82">
+        <v>36.377000000000002</v>
+      </c>
       <c r="W12" s="37" t="s">
         <v>92</v>
       </c>
       <c r="X12" s="10">
         <f>MIN(D38:P67,D7:P36,F74:P103,F105:H134,N105:P134)</f>
-        <v>50.330599999999997</v>
+        <v>32.472099999999998</v>
       </c>
       <c r="Z12" s="26">
         <f t="shared" ref="Z12:Z14" si="0">TIME(,,X12)</f>
-        <v>5.7870370370370367E-4</v>
+        <v>3.7037037037037035E-4</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3922,7 +4044,9 @@
         <v>151.47417250000001</v>
       </c>
       <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
+      <c r="J13" s="33">
+        <v>34.978900000000003</v>
+      </c>
       <c r="L13">
         <v>73.184496300000006</v>
       </c>
@@ -3931,6 +4055,9 @@
       </c>
       <c r="P13">
         <v>456.90458919999998</v>
+      </c>
+      <c r="R13" s="82">
+        <v>36.636400000000002</v>
       </c>
       <c r="W13" s="37" t="s">
         <v>93</v>
@@ -3962,7 +4089,9 @@
         <v>76.544575100000003</v>
       </c>
       <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
+      <c r="J14" s="33">
+        <v>35.077300000000001</v>
+      </c>
       <c r="L14">
         <v>146.44123880000001</v>
       </c>
@@ -3972,16 +4101,19 @@
       <c r="P14">
         <v>81.961152400000003</v>
       </c>
+      <c r="R14" s="82">
+        <v>36.623100000000001</v>
+      </c>
       <c r="W14" s="37" t="s">
         <v>94</v>
       </c>
       <c r="X14" s="10">
         <f>STDEV(D38:P67,D7:P36,F74:P103,F105:H134,N105:P134)</f>
-        <v>525.50420106598369</v>
+        <v>509.04593127958617</v>
       </c>
       <c r="Z14" s="26">
         <f t="shared" si="0"/>
-        <v>6.076388888888889E-3</v>
+        <v>5.8912037037037041E-3</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4002,7 +4134,9 @@
         <v>78.093684600000003</v>
       </c>
       <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
+      <c r="J15" s="33">
+        <v>34.977499999999999</v>
+      </c>
       <c r="L15">
         <v>78.716759600000003</v>
       </c>
@@ -4011,6 +4145,9 @@
       </c>
       <c r="P15">
         <v>159.94233370000001</v>
+      </c>
+      <c r="R15" s="82">
+        <v>36.220799999999997</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4030,7 +4167,9 @@
         <v>224.6588481</v>
       </c>
       <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
+      <c r="J16" s="31">
+        <v>36.105600000000003</v>
+      </c>
       <c r="L16">
         <v>78.939935899999995</v>
       </c>
@@ -4040,8 +4179,11 @@
       <c r="P16">
         <v>77.275726899999995</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="R16" s="82">
+        <v>35.075099999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="53"/>
       <c r="B17" s="46" t="s">
         <v>86</v>
@@ -4061,7 +4203,9 @@
         <v>73.114328499999999</v>
       </c>
       <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
+      <c r="J17" s="33">
+        <v>35.970500000000001</v>
+      </c>
       <c r="L17">
         <v>207.18083060000001</v>
       </c>
@@ -4071,8 +4215,11 @@
       <c r="P17">
         <v>72.4576469</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="R17" s="82">
+        <v>35.995699999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="53"/>
       <c r="B18" s="47"/>
       <c r="C18">
@@ -4090,7 +4237,9 @@
         <v>71.188278800000006</v>
       </c>
       <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
+      <c r="J18" s="33">
+        <v>34.048900000000003</v>
+      </c>
       <c r="L18">
         <v>65.375731599999995</v>
       </c>
@@ -4100,8 +4249,11 @@
       <c r="P18">
         <v>73.037465600000004</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="R18" s="82">
+        <v>34.117800000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="53"/>
       <c r="B19" s="47"/>
       <c r="C19">
@@ -4119,7 +4271,9 @@
         <v>70.401290500000002</v>
       </c>
       <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
+      <c r="J19" s="33">
+        <v>34.010199999999998</v>
+      </c>
       <c r="L19">
         <v>586.4684383</v>
       </c>
@@ -4129,8 +4283,11 @@
       <c r="P19">
         <v>75.679750100000007</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="R19" s="82">
+        <v>34.372500000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="53"/>
       <c r="B20" s="47"/>
       <c r="C20">
@@ -4148,7 +4305,9 @@
         <v>80.338869299999999</v>
       </c>
       <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
+      <c r="J20" s="33">
+        <v>35.058799999999998</v>
+      </c>
       <c r="L20">
         <v>323.32953090000001</v>
       </c>
@@ -4158,8 +4317,11 @@
       <c r="P20">
         <v>69.004712999999995</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="R20" s="82">
+        <v>34.101599999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="53"/>
       <c r="B21" s="47"/>
       <c r="C21">
@@ -4177,7 +4339,9 @@
         <v>74.254665099999997</v>
       </c>
       <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
+      <c r="J21" s="33">
+        <v>33.995800000000003</v>
+      </c>
       <c r="L21">
         <v>129.41876830000001</v>
       </c>
@@ -4187,8 +4351,11 @@
       <c r="P21">
         <v>64.653414799999993</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="R21" s="82">
+        <v>35.322299999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="53"/>
       <c r="B22" s="47"/>
       <c r="C22">
@@ -4206,7 +4373,9 @@
         <v>70.6183075</v>
       </c>
       <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
+      <c r="J22" s="33">
+        <v>34.000700000000002</v>
+      </c>
       <c r="L22">
         <v>196.73654540000001</v>
       </c>
@@ -4216,8 +4385,11 @@
       <c r="P22">
         <v>64.707670100000001</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R22" s="82">
+        <v>34.085500000000003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="53"/>
       <c r="B23" s="47"/>
       <c r="C23">
@@ -4235,7 +4407,9 @@
         <v>69.177133299999994</v>
       </c>
       <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
+      <c r="J23" s="33">
+        <v>34.070799999999998</v>
+      </c>
       <c r="L23">
         <v>129.47770080000001</v>
       </c>
@@ -4245,8 +4419,11 @@
       <c r="P23">
         <v>66.928739100000001</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R23" s="82">
+        <v>34.142600000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="53"/>
       <c r="B24" s="47"/>
       <c r="C24">
@@ -4264,7 +4441,9 @@
         <v>70.352484700000005</v>
       </c>
       <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
+      <c r="J24" s="33">
+        <v>34.013300000000001</v>
+      </c>
       <c r="L24">
         <v>583.81888790000005</v>
       </c>
@@ -4274,8 +4453,11 @@
       <c r="P24">
         <v>85.198224800000006</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R24" s="82">
+        <v>34.6751</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="53"/>
       <c r="B25" s="47"/>
       <c r="C25">
@@ -4293,7 +4475,9 @@
         <v>70.135643900000005</v>
       </c>
       <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
+      <c r="J25" s="33">
+        <v>34.385899999999999</v>
+      </c>
       <c r="L25">
         <v>1580.9047197</v>
       </c>
@@ -4303,8 +4487,11 @@
       <c r="P25">
         <v>86.575239600000003</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R25" s="82">
+        <v>33.859900000000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="53"/>
       <c r="B26" s="48"/>
       <c r="C26">
@@ -4321,7 +4508,9 @@
         <v>70.832701700000001</v>
       </c>
       <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
+      <c r="J26" s="31">
+        <v>35.009799999999998</v>
+      </c>
       <c r="L26">
         <v>1218.9549171000001</v>
       </c>
@@ -4331,8 +4520,11 @@
       <c r="P26">
         <v>75.496478600000003</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="R26" s="82">
+        <v>34.288499999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="53"/>
       <c r="B27" s="46" t="s">
         <v>27</v>
@@ -4352,7 +4544,9 @@
         <v>81.723654499999995</v>
       </c>
       <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
+      <c r="J27" s="33">
+        <v>36.185899999999997</v>
+      </c>
       <c r="L27">
         <v>916.28107279999995</v>
       </c>
@@ -4362,8 +4556,11 @@
       <c r="P27">
         <v>75.413589000000002</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="R27" s="82">
+        <v>36.275500000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="53"/>
       <c r="B28" s="47"/>
       <c r="C28">
@@ -4381,7 +4578,9 @@
         <v>73.767661000000004</v>
       </c>
       <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
+      <c r="J28" s="33">
+        <v>34.482799999999997</v>
+      </c>
       <c r="L28">
         <v>867.80258600000002</v>
       </c>
@@ -4391,8 +4590,11 @@
       <c r="P28">
         <v>77.701590100000004</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="R28" s="82">
+        <v>34.380499999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="53"/>
       <c r="B29" s="47"/>
       <c r="C29">
@@ -4410,7 +4612,9 @@
         <v>76.209941599999993</v>
       </c>
       <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
+      <c r="J29" s="33">
+        <v>35.633299999999998</v>
+      </c>
       <c r="L29">
         <v>325.8396424</v>
       </c>
@@ -4420,8 +4624,11 @@
       <c r="P29">
         <v>78.494008300000004</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="R29" s="82">
+        <v>35.154899999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="53"/>
       <c r="B30" s="47"/>
       <c r="C30">
@@ -4439,7 +4646,9 @@
         <v>72.462500500000004</v>
       </c>
       <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
+      <c r="J30" s="33">
+        <v>35.256100000000004</v>
+      </c>
       <c r="L30">
         <v>192.90137920000001</v>
       </c>
@@ -4449,8 +4658,11 @@
       <c r="P30">
         <v>73.773346900000007</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="R30" s="82">
+        <v>35.206299999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="53"/>
       <c r="B31" s="47"/>
       <c r="C31">
@@ -4468,7 +4680,9 @@
         <v>72.456881800000005</v>
       </c>
       <c r="I31" s="33"/>
-      <c r="J31" s="33"/>
+      <c r="J31" s="33">
+        <v>34.956899999999997</v>
+      </c>
       <c r="L31">
         <v>704.56541179999999</v>
       </c>
@@ -4478,8 +4692,11 @@
       <c r="P31">
         <v>86.556363700000006</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="R31" s="82">
+        <v>34.072400000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="53"/>
       <c r="B32" s="47"/>
       <c r="C32">
@@ -4497,7 +4714,9 @@
         <v>72.692214000000007</v>
       </c>
       <c r="I32" s="33"/>
-      <c r="J32" s="33"/>
+      <c r="J32" s="33">
+        <v>35.482599999999998</v>
+      </c>
       <c r="L32">
         <v>1577.8932976000001</v>
       </c>
@@ -4506,6 +4725,9 @@
       </c>
       <c r="P32">
         <v>81.386483100000007</v>
+      </c>
+      <c r="R32" s="82">
+        <v>34.356200000000001</v>
       </c>
     </row>
     <row r="33" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4526,7 +4748,9 @@
         <v>72.928730299999998</v>
       </c>
       <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
+      <c r="J33" s="33">
+        <v>35.341500000000003</v>
+      </c>
       <c r="L33">
         <v>249.1666912</v>
       </c>
@@ -4535,6 +4759,9 @@
       </c>
       <c r="P33">
         <v>88.930410199999997</v>
+      </c>
+      <c r="R33" s="82">
+        <v>35.070900000000002</v>
       </c>
     </row>
     <row r="34" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4555,7 +4782,9 @@
         <v>70.194977100000003</v>
       </c>
       <c r="I34" s="33"/>
-      <c r="J34" s="33"/>
+      <c r="J34" s="33">
+        <v>34.115200000000002</v>
+      </c>
       <c r="L34">
         <v>485.6161606</v>
       </c>
@@ -4564,6 +4793,9 @@
       </c>
       <c r="P34">
         <v>81.324767699999995</v>
+      </c>
+      <c r="R34" s="82">
+        <v>34.187899999999999</v>
       </c>
     </row>
     <row r="35" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4584,7 +4816,9 @@
         <v>72.091733000000005</v>
       </c>
       <c r="I35" s="33"/>
-      <c r="J35" s="33"/>
+      <c r="J35" s="33">
+        <v>34.131799999999998</v>
+      </c>
       <c r="L35">
         <v>1728.0716404</v>
       </c>
@@ -4593,6 +4827,9 @@
       </c>
       <c r="P35">
         <v>84.404220199999997</v>
+      </c>
+      <c r="R35" s="82">
+        <v>35.190100000000001</v>
       </c>
     </row>
     <row r="36" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4612,7 +4849,9 @@
         <v>74.820149400000005</v>
       </c>
       <c r="I36" s="31"/>
-      <c r="J36" s="31"/>
+      <c r="J36" s="31">
+        <v>34.2742</v>
+      </c>
       <c r="L36">
         <v>399.93897140000001</v>
       </c>
@@ -4621,6 +4860,9 @@
       </c>
       <c r="P36">
         <v>78.9069042</v>
+      </c>
+      <c r="R36" s="82">
+        <v>35.302399999999999</v>
       </c>
       <c r="W36" s="51" t="s">
         <v>95</v>
@@ -4697,7 +4939,9 @@
         <v>66.098048399999996</v>
       </c>
       <c r="I38" s="33"/>
-      <c r="J38" s="33"/>
+      <c r="J38" s="33">
+        <v>34.308500000000002</v>
+      </c>
       <c r="L38">
         <v>272.02645749999999</v>
       </c>
@@ -4706,6 +4950,9 @@
       </c>
       <c r="P38">
         <v>66.911195300000003</v>
+      </c>
+      <c r="R38" s="81">
+        <v>34.2059</v>
       </c>
       <c r="W38" s="37" t="s">
         <v>91</v>
@@ -4745,14 +4992,14 @@
       <c r="AL38" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="AM38" s="42" t="e">
+      <c r="AM38" s="42">
         <f>AVERAGE(J7:J67,R7:R67)</f>
-        <v>#DIV/0!</v>
+        <v>34.205395833333334</v>
       </c>
       <c r="AN38" s="42"/>
-      <c r="AO38" s="43" t="e">
+      <c r="AO38" s="43">
         <f>TIME(,,AM38)</f>
-        <v>#DIV/0!</v>
+        <v>3.9351851851851852E-4</v>
       </c>
     </row>
     <row r="39" spans="1:41" ht="16" x14ac:dyDescent="0.2">
@@ -4773,7 +5020,9 @@
         <v>61.709756200000001</v>
       </c>
       <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
+      <c r="J39" s="33">
+        <v>33.494900000000001</v>
+      </c>
       <c r="L39">
         <v>271.00988949999999</v>
       </c>
@@ -4782,6 +5031,9 @@
       </c>
       <c r="P39">
         <v>64.378168500000001</v>
+      </c>
+      <c r="R39" s="81">
+        <v>32.802799999999998</v>
       </c>
       <c r="W39" s="37" t="s">
         <v>92</v>
@@ -4823,12 +5075,12 @@
       </c>
       <c r="AM39" s="42">
         <f>MIN(J7:J67,R7:R67)</f>
-        <v>0</v>
+        <v>32.345500000000001</v>
       </c>
       <c r="AN39" s="42"/>
       <c r="AO39" s="43">
         <f t="shared" ref="AO39:AO41" si="4">TIME(,,AM39)</f>
-        <v>0</v>
+        <v>3.7037037037037035E-4</v>
       </c>
     </row>
     <row r="40" spans="1:41" ht="16" x14ac:dyDescent="0.2">
@@ -4849,7 +5101,9 @@
         <v>188.01339630000001</v>
       </c>
       <c r="I40" s="33"/>
-      <c r="J40" s="33"/>
+      <c r="J40" s="33">
+        <v>32.552100000000003</v>
+      </c>
       <c r="L40">
         <v>726.76372800000001</v>
       </c>
@@ -4858,6 +5112,9 @@
       </c>
       <c r="P40">
         <v>66.806464399999996</v>
+      </c>
+      <c r="R40" s="81">
+        <v>32.568199999999997</v>
       </c>
       <c r="W40" s="37" t="s">
         <v>93</v>
@@ -4899,12 +5156,12 @@
       </c>
       <c r="AM40" s="42">
         <f>MAX(J7:J67,R7:R67)</f>
-        <v>0</v>
+        <v>38.036000000000001</v>
       </c>
       <c r="AN40" s="42"/>
       <c r="AO40" s="43">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4.3981481481481481E-4</v>
       </c>
     </row>
     <row r="41" spans="1:41" ht="16" x14ac:dyDescent="0.2">
@@ -4925,7 +5182,9 @@
         <v>248.90476090000001</v>
       </c>
       <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
+      <c r="J41" s="89">
+        <v>32.491</v>
+      </c>
       <c r="L41">
         <v>540.2707183</v>
       </c>
@@ -4934,6 +5193,9 @@
       </c>
       <c r="P41">
         <v>383.47915019999999</v>
+      </c>
+      <c r="R41" s="81">
+        <v>33.292000000000002</v>
       </c>
       <c r="W41" s="37" t="s">
         <v>94</v>
@@ -4973,14 +5235,14 @@
       <c r="AL41" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="AM41" s="42" t="e">
+      <c r="AM41" s="42">
         <f>STDEV(J7:J67,R7:R67)</f>
-        <v>#DIV/0!</v>
+        <v>1.2400401837075219</v>
       </c>
       <c r="AN41" s="42"/>
-      <c r="AO41" s="43" t="e">
+      <c r="AO41" s="43">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>1.1574074074074073E-5</v>
       </c>
     </row>
     <row r="42" spans="1:41" ht="16" x14ac:dyDescent="0.2">
@@ -5001,7 +5263,9 @@
         <v>61.305089099999996</v>
       </c>
       <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
+      <c r="J42" s="33">
+        <v>32.5762</v>
+      </c>
       <c r="L42">
         <v>64.362414000000001</v>
       </c>
@@ -5010,6 +5274,9 @@
       </c>
       <c r="P42">
         <v>62.552345799999998</v>
+      </c>
+      <c r="R42" s="81">
+        <v>33.485799999999998</v>
       </c>
     </row>
     <row r="43" spans="1:41" ht="16" x14ac:dyDescent="0.2">
@@ -5030,7 +5297,9 @@
         <v>310.8813571</v>
       </c>
       <c r="I43" s="33"/>
-      <c r="J43" s="33"/>
+      <c r="J43" s="33">
+        <v>33.559399999999997</v>
+      </c>
       <c r="L43">
         <v>64.178668500000001</v>
       </c>
@@ -5039,6 +5308,9 @@
       </c>
       <c r="P43">
         <v>66.208508899999998</v>
+      </c>
+      <c r="R43" s="81">
+        <v>32.621699999999997</v>
       </c>
     </row>
     <row r="44" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -5059,7 +5331,9 @@
         <v>185.79902559999999</v>
       </c>
       <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
+      <c r="J44" s="33">
+        <v>32.472099999999998</v>
+      </c>
       <c r="L44">
         <v>128.72593209999999</v>
       </c>
@@ -5068,6 +5342,9 @@
       </c>
       <c r="P44">
         <v>132.51080440000001</v>
+      </c>
+      <c r="R44" s="81">
+        <v>32.714300000000001</v>
       </c>
       <c r="W44" s="37"/>
       <c r="X44" s="37"/>
@@ -5110,7 +5387,9 @@
         <v>61.944671700000001</v>
       </c>
       <c r="I45" s="33"/>
-      <c r="J45" s="33"/>
+      <c r="J45" s="33">
+        <v>33.423200000000001</v>
+      </c>
       <c r="L45">
         <v>1315.3337303000001</v>
       </c>
@@ -5119,6 +5398,9 @@
       </c>
       <c r="P45">
         <v>67.6577901</v>
+      </c>
+      <c r="R45" s="81">
+        <v>33.65</v>
       </c>
       <c r="X45" s="38"/>
       <c r="Y45" s="38"/>
@@ -5159,7 +5441,9 @@
         <v>62.026653699999997</v>
       </c>
       <c r="I46" s="33"/>
-      <c r="J46" s="33"/>
+      <c r="J46" s="33">
+        <v>32.741500000000002</v>
+      </c>
       <c r="L46">
         <v>1165.9940234000001</v>
       </c>
@@ -5168,6 +5452,9 @@
       </c>
       <c r="P46">
         <v>65.501620900000006</v>
+      </c>
+      <c r="R46" s="81">
+        <v>33.218000000000004</v>
       </c>
       <c r="W46" s="37"/>
       <c r="Z46" s="26"/>
@@ -5225,7 +5512,9 @@
         <v>452.67738200000002</v>
       </c>
       <c r="I47" s="31"/>
-      <c r="J47" s="31"/>
+      <c r="J47" s="31">
+        <v>32.653399999999998</v>
+      </c>
       <c r="L47">
         <v>1281.4269638999999</v>
       </c>
@@ -5234,6 +5523,9 @@
       </c>
       <c r="P47">
         <v>65.377549599999995</v>
+      </c>
+      <c r="R47" s="81">
+        <v>32.382199999999997</v>
       </c>
       <c r="W47" s="37"/>
       <c r="Z47" s="26"/>
@@ -5294,7 +5586,9 @@
         <v>66.010996500000005</v>
       </c>
       <c r="I48" s="33"/>
-      <c r="J48" s="33"/>
+      <c r="J48" s="33">
+        <v>34.996899999999997</v>
+      </c>
       <c r="L48">
         <v>1067.6859191999999</v>
       </c>
@@ -5303,6 +5597,9 @@
       </c>
       <c r="P48">
         <v>75.916192300000006</v>
+      </c>
+      <c r="R48" s="81">
+        <v>34.949199999999998</v>
       </c>
       <c r="W48" s="37"/>
       <c r="Z48" s="26"/>
@@ -5361,7 +5658,9 @@
         <v>61.7772839</v>
       </c>
       <c r="I49" s="33"/>
-      <c r="J49" s="33"/>
+      <c r="J49" s="33">
+        <v>33.271099999999997</v>
+      </c>
       <c r="L49">
         <v>496.0932545</v>
       </c>
@@ -5370,6 +5669,9 @@
       </c>
       <c r="P49">
         <v>68.917741399999997</v>
+      </c>
+      <c r="R49" s="81">
+        <v>32.847999999999999</v>
       </c>
       <c r="W49" s="37"/>
       <c r="Z49" s="26"/>
@@ -5428,7 +5730,9 @@
         <v>62.869197700000001</v>
       </c>
       <c r="I50" s="33"/>
-      <c r="J50" s="33"/>
+      <c r="J50" s="33">
+        <v>34.295499999999997</v>
+      </c>
       <c r="L50">
         <v>2702.1846860999999</v>
       </c>
@@ -5437,6 +5741,9 @@
       </c>
       <c r="P50">
         <v>66.262496600000006</v>
+      </c>
+      <c r="R50" s="81">
+        <v>32.967399999999998</v>
       </c>
     </row>
     <row r="51" spans="1:41" ht="16" x14ac:dyDescent="0.2">
@@ -5457,7 +5764,9 @@
         <v>74.841529699999995</v>
       </c>
       <c r="I51" s="33"/>
-      <c r="J51" s="33"/>
+      <c r="J51" s="33">
+        <v>34.012300000000003</v>
+      </c>
       <c r="L51">
         <v>1368.3347223999999</v>
       </c>
@@ -5466,6 +5775,9 @@
       </c>
       <c r="P51">
         <v>65.344129800000005</v>
+      </c>
+      <c r="R51" s="81">
+        <v>33.582599999999999</v>
       </c>
     </row>
     <row r="52" spans="1:41" ht="16" x14ac:dyDescent="0.2">
@@ -5486,7 +5798,9 @@
         <v>65.391042400000003</v>
       </c>
       <c r="I52" s="33"/>
-      <c r="J52" s="33"/>
+      <c r="J52" s="33">
+        <v>33.0749</v>
+      </c>
       <c r="L52">
         <v>122.9923916</v>
       </c>
@@ -5495,6 +5809,9 @@
       </c>
       <c r="P52">
         <v>73.091260399999996</v>
+      </c>
+      <c r="R52" s="81">
+        <v>32.345500000000001</v>
       </c>
     </row>
     <row r="53" spans="1:41" ht="16" x14ac:dyDescent="0.2">
@@ -5515,7 +5832,9 @@
         <v>65.577701300000001</v>
       </c>
       <c r="I53" s="33"/>
-      <c r="J53" s="33"/>
+      <c r="J53" s="89">
+        <v>32.994</v>
+      </c>
       <c r="L53">
         <v>122.7202302</v>
       </c>
@@ -5524,6 +5843,9 @@
       </c>
       <c r="P53">
         <v>69.363162599999995</v>
+      </c>
+      <c r="R53" s="81">
+        <v>32.598399999999998</v>
       </c>
     </row>
     <row r="54" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -5544,7 +5866,9 @@
         <v>63.4976409</v>
       </c>
       <c r="I54" s="33"/>
-      <c r="J54" s="33"/>
+      <c r="J54" s="33">
+        <v>33.270899999999997</v>
+      </c>
       <c r="L54">
         <v>1246.0557417</v>
       </c>
@@ -5553,6 +5877,9 @@
       </c>
       <c r="P54">
         <v>66.126271200000005</v>
+      </c>
+      <c r="R54" s="81">
+        <v>32.393599999999999</v>
       </c>
       <c r="W54" s="51" t="s">
         <v>100</v>
@@ -5585,7 +5912,9 @@
         <v>64.229546999999997</v>
       </c>
       <c r="I55" s="33"/>
-      <c r="J55" s="33"/>
+      <c r="J55" s="33">
+        <v>33.130499999999998</v>
+      </c>
       <c r="L55">
         <v>123.4047491</v>
       </c>
@@ -5594,6 +5923,9 @@
       </c>
       <c r="P55">
         <v>64.695870499999998</v>
+      </c>
+      <c r="R55" s="81">
+        <v>33.694099999999999</v>
       </c>
       <c r="X55" s="38"/>
       <c r="Y55" s="38"/>
@@ -5624,7 +5956,9 @@
         <v>63.266840199999997</v>
       </c>
       <c r="I56" s="33"/>
-      <c r="J56" s="33"/>
+      <c r="J56" s="33">
+        <v>33.470799999999997</v>
+      </c>
       <c r="L56">
         <v>434.81144430000001</v>
       </c>
@@ -5634,28 +5968,31 @@
       <c r="P56">
         <v>66.252286600000005</v>
       </c>
+      <c r="R56" s="81">
+        <v>32.419600000000003</v>
+      </c>
       <c r="W56" s="37" t="s">
         <v>91</v>
       </c>
       <c r="X56" s="10">
         <f>AVERAGE(D7:J67,F74:J134)</f>
-        <v>291.95593470416668</v>
+        <v>255.13398688928572</v>
       </c>
       <c r="Z56" s="26">
         <f>TIME(,,X56)</f>
-        <v>3.3680555555555556E-3</v>
+        <v>2.9513888888888888E-3</v>
       </c>
       <c r="AB56" s="37" t="s">
         <v>91</v>
       </c>
       <c r="AC56" s="10">
         <f>AVERAGE(L7:R67,N74:R103,N105:R134)</f>
-        <v>311.41033659942678</v>
+        <v>270.74502927432758</v>
       </c>
       <c r="AD56" s="10"/>
       <c r="AE56" s="26">
         <f>TIME(,,AC56)</f>
-        <v>3.5995370370370369E-3</v>
+        <v>3.1250000000000002E-3</v>
       </c>
     </row>
     <row r="57" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -5675,7 +6012,9 @@
         <v>62.7056605</v>
       </c>
       <c r="I57" s="31"/>
-      <c r="J57" s="31"/>
+      <c r="J57" s="31">
+        <v>33.089100000000002</v>
+      </c>
       <c r="L57">
         <v>1426.1018938</v>
       </c>
@@ -5685,28 +6024,31 @@
       <c r="P57">
         <v>65.3028932</v>
       </c>
+      <c r="R57" s="81">
+        <v>32.625399999999999</v>
+      </c>
       <c r="W57" s="37" t="s">
         <v>92</v>
       </c>
       <c r="X57" s="10">
         <f>MIN(D7:J67,F74:J134)</f>
-        <v>50.256300000000003</v>
+        <v>32.472099999999998</v>
       </c>
       <c r="Z57" s="26">
         <f t="shared" ref="Z57:Z59" si="8">TIME(,,X57)</f>
-        <v>5.7870370370370367E-4</v>
+        <v>3.7037037037037035E-4</v>
       </c>
       <c r="AB57" s="37" t="s">
         <v>92</v>
       </c>
       <c r="AC57" s="10">
         <f>MIN(L7:R67,N74:R103,N105:R134)</f>
-        <v>49.9163</v>
+        <v>32.345500000000001</v>
       </c>
       <c r="AD57" s="10"/>
       <c r="AE57" s="26">
         <f t="shared" ref="AE57:AE59" si="9">TIME(,,AC57)</f>
-        <v>5.6712962962962967E-4</v>
+        <v>3.7037037037037035E-4</v>
       </c>
     </row>
     <row r="58" spans="1:41" ht="16" x14ac:dyDescent="0.2">
@@ -5729,6 +6071,9 @@
         <v>77.070805199999995</v>
       </c>
       <c r="I58" s="33"/>
+      <c r="J58" s="81">
+        <v>37.537199999999999</v>
+      </c>
       <c r="L58">
         <v>66.247412199999999</v>
       </c>
@@ -5737,6 +6082,9 @@
       </c>
       <c r="P58">
         <v>95.839778699999997</v>
+      </c>
+      <c r="R58" s="81">
+        <v>36.006500000000003</v>
       </c>
       <c r="W58" s="37" t="s">
         <v>93</v>
@@ -5780,6 +6128,9 @@
         <v>67.473517299999997</v>
       </c>
       <c r="I59" s="33"/>
+      <c r="J59">
+        <v>33.357500000000002</v>
+      </c>
       <c r="L59">
         <v>386.56979080000002</v>
       </c>
@@ -5789,28 +6140,31 @@
       <c r="P59">
         <v>110.28815590000001</v>
       </c>
+      <c r="R59" s="81">
+        <v>32.920099999999998</v>
+      </c>
       <c r="W59" s="37" t="s">
         <v>94</v>
       </c>
       <c r="X59" s="10">
         <f>STDEV(D7:J67,F74:J134)</f>
-        <v>375.39820027214569</v>
+        <v>359.02440458381642</v>
       </c>
       <c r="Z59" s="26">
         <f t="shared" si="8"/>
-        <v>4.340277777777778E-3</v>
+        <v>4.1550925925925922E-3</v>
       </c>
       <c r="AB59" s="37" t="s">
         <v>94</v>
       </c>
       <c r="AC59" s="10">
         <f>STDEV(L7:R67,N74:R103,N105:R134)</f>
-        <v>602.41664910795362</v>
+        <v>564.9601599915203</v>
       </c>
       <c r="AD59" s="10"/>
       <c r="AE59" s="26">
         <f t="shared" si="9"/>
-        <v>6.9675925925925929E-3</v>
+        <v>6.5277777777777782E-3</v>
       </c>
     </row>
     <row r="60" spans="1:41" ht="16" x14ac:dyDescent="0.2">
@@ -5831,6 +6185,9 @@
         <v>63.312723699999999</v>
       </c>
       <c r="I60" s="33"/>
+      <c r="J60">
+        <v>33.069699999999997</v>
+      </c>
       <c r="L60">
         <v>686.01692530000003</v>
       </c>
@@ -5839,6 +6196,9 @@
       </c>
       <c r="P60">
         <v>116.1841663</v>
+      </c>
+      <c r="R60" s="81">
+        <v>32.770499999999998</v>
       </c>
     </row>
     <row r="61" spans="1:41" ht="16" x14ac:dyDescent="0.2">
@@ -5859,6 +6219,9 @@
         <v>66.620741300000006</v>
       </c>
       <c r="I61" s="33"/>
+      <c r="J61">
+        <v>33.290599999999998</v>
+      </c>
       <c r="L61">
         <v>63.7846884</v>
       </c>
@@ -5867,6 +6230,9 @@
       </c>
       <c r="P61">
         <v>110.5701389</v>
+      </c>
+      <c r="R61" s="81">
+        <v>33.440100000000001</v>
       </c>
     </row>
     <row r="62" spans="1:41" ht="16" x14ac:dyDescent="0.2">
@@ -5887,6 +6253,9 @@
         <v>63.612826599999998</v>
       </c>
       <c r="I62" s="33"/>
+      <c r="J62">
+        <v>33.0623</v>
+      </c>
       <c r="L62">
         <v>560.03005040000005</v>
       </c>
@@ -5895,6 +6264,9 @@
       </c>
       <c r="P62">
         <v>112.1447738</v>
+      </c>
+      <c r="R62" s="81">
+        <v>32.965400000000002</v>
       </c>
     </row>
     <row r="63" spans="1:41" ht="16" x14ac:dyDescent="0.2">
@@ -5915,6 +6287,9 @@
         <v>62.2764235</v>
       </c>
       <c r="I63" s="33"/>
+      <c r="J63">
+        <v>33.289900000000003</v>
+      </c>
       <c r="L63">
         <v>685.14225999999996</v>
       </c>
@@ -5923,6 +6298,9 @@
       </c>
       <c r="P63">
         <v>105.71322069999999</v>
+      </c>
+      <c r="R63" s="81">
+        <v>32.902099999999997</v>
       </c>
     </row>
     <row r="64" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -5943,6 +6321,9 @@
         <v>62.672274899999998</v>
       </c>
       <c r="I64" s="33"/>
+      <c r="J64">
+        <v>33.021700000000003</v>
+      </c>
       <c r="L64">
         <v>124.58991930000001</v>
       </c>
@@ -5951,6 +6332,9 @@
       </c>
       <c r="P64">
         <v>103.50280239999999</v>
+      </c>
+      <c r="R64" s="81">
+        <v>33.018300000000004</v>
       </c>
     </row>
     <row r="65" spans="1:30" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -5971,6 +6355,9 @@
         <v>62.066623900000003</v>
       </c>
       <c r="I65" s="33"/>
+      <c r="J65">
+        <v>33.183300000000003</v>
+      </c>
       <c r="L65">
         <v>1430.3951505</v>
       </c>
@@ -5979,6 +6366,9 @@
       </c>
       <c r="P65">
         <v>89.825549699999996</v>
+      </c>
+      <c r="R65" s="81">
+        <v>34.323099999999997</v>
       </c>
       <c r="W65" s="51" t="s">
         <v>102</v>
@@ -6009,6 +6399,9 @@
         <v>62.867806299999998</v>
       </c>
       <c r="I66" s="33"/>
+      <c r="J66" s="82">
+        <v>34.238999999999997</v>
+      </c>
       <c r="L66">
         <v>124.3385308</v>
       </c>
@@ -6017,6 +6410,9 @@
       </c>
       <c r="P66">
         <v>77.588893900000002</v>
+      </c>
+      <c r="R66" s="81">
+        <v>33.968899999999998</v>
       </c>
       <c r="X66" s="38" t="s">
         <v>95</v>
@@ -6057,6 +6453,9 @@
         <v>64.716894199999999</v>
       </c>
       <c r="I67" s="31"/>
+      <c r="J67">
+        <v>34.149799999999999</v>
+      </c>
       <c r="L67">
         <v>62.1611634</v>
       </c>
@@ -6065,6 +6464,9 @@
       </c>
       <c r="P67">
         <v>79.4372781</v>
+      </c>
+      <c r="R67" s="81">
+        <v>33.910600000000002</v>
       </c>
       <c r="W67" s="37" t="s">
         <v>105</v>
@@ -6081,9 +6483,9 @@
         <f>MEDIAN(H7:H67,P7:P67)</f>
         <v>73.235108800000006</v>
       </c>
-      <c r="AA67" s="10" t="e">
+      <c r="AA67" s="10">
         <f>MEDIAN(J7:J67,R7:R67)</f>
-        <v>#NUM!</v>
+        <v>34.108400000000003</v>
       </c>
       <c r="AB67">
         <f>MEDIAN(F74:F134,N74:N134)</f>
@@ -6116,9 +6518,9 @@
         <f>AVERAGE(H7:H67,P7:P67)</f>
         <v>96.597025105833339</v>
       </c>
-      <c r="AA68" s="10" t="e">
+      <c r="AA68" s="10">
         <f>AVERAGE(J7:J67,R7:R67)</f>
-        <v>#DIV/0!</v>
+        <v>34.205395833333334</v>
       </c>
       <c r="AB68">
         <f>AVERAGE(F74:F134,N74:N134)</f>
@@ -6153,7 +6555,10 @@
         <v>97.33608582833331</v>
       </c>
       <c r="I69" s="31"/>
-      <c r="J69" s="31"/>
+      <c r="J69" s="31">
+        <f>AVERAGE(J7:J67)</f>
+        <v>34.202300000000008</v>
+      </c>
       <c r="K69" s="31"/>
       <c r="L69" s="31">
         <f t="shared" ref="L69:P69" si="11">AVERAGE(L7:L67)</f>
@@ -6170,7 +6575,10 @@
         <v>95.857964383333311</v>
       </c>
       <c r="Q69" s="31"/>
-      <c r="R69" s="31"/>
+      <c r="R69" s="31">
+        <f t="shared" ref="R69" si="12">AVERAGE(R7:R67)</f>
+        <v>34.208491666666667</v>
+      </c>
       <c r="W69" s="37" t="s">
         <v>107</v>
       </c>
@@ -6186,9 +6594,9 @@
         <f>_xlfn.QUARTILE.EXC((H7:H67,P7:P67),1)</f>
         <v>66.105104100000005</v>
       </c>
-      <c r="AA69" s="10" t="e">
+      <c r="AA69" s="10">
         <f>_xlfn.QUARTILE.EXC((J7:J67,R7:R67),1)</f>
-        <v>#NUM!</v>
+        <v>33.143699999999995</v>
       </c>
       <c r="AB69">
         <f>_xlfn.QUARTILE.EXC((F74:F134,N74:N134),1)</f>
@@ -6209,12 +6617,12 @@
         <v>81</v>
       </c>
       <c r="D70" s="31">
-        <f t="shared" ref="D70:F70" si="12">MIN(D7:D67)</f>
+        <f t="shared" ref="D70:F70" si="13">MIN(D7:D67)</f>
         <v>64.404756800000001</v>
       </c>
       <c r="E70" s="31"/>
       <c r="F70" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>59.023810400000002</v>
       </c>
       <c r="G70" s="31"/>
@@ -6223,24 +6631,30 @@
         <v>61.305089099999996</v>
       </c>
       <c r="I70" s="31"/>
-      <c r="J70" s="31"/>
+      <c r="J70" s="31">
+        <f>MIN(J7:J67)</f>
+        <v>32.472099999999998</v>
+      </c>
       <c r="K70" s="31"/>
       <c r="L70" s="31">
-        <f t="shared" ref="L70:P70" si="13">MIN(L7:L67)</f>
+        <f t="shared" ref="L70:P70" si="14">MIN(L7:L67)</f>
         <v>62.1611634</v>
       </c>
       <c r="M70" s="31"/>
       <c r="N70" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>61.419639699999998</v>
       </c>
       <c r="O70" s="31"/>
       <c r="P70" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>62.552345799999998</v>
       </c>
       <c r="Q70" s="31"/>
-      <c r="R70" s="31"/>
+      <c r="R70" s="31">
+        <f t="shared" ref="R70" si="15">MIN(R7:R67)</f>
+        <v>32.345500000000001</v>
+      </c>
       <c r="W70" s="37" t="s">
         <v>108</v>
       </c>
@@ -6256,9 +6670,9 @@
         <f>_xlfn.QUARTILE.EXC((H7:H67,P7:P67),3)</f>
         <v>84.675873050000007</v>
       </c>
-      <c r="AA70" s="10" t="e">
+      <c r="AA70" s="10">
         <f>_xlfn.QUARTILE.EXC((J7:J67,R7:R67),3)</f>
-        <v>#NUM!</v>
+        <v>35.055724999999995</v>
       </c>
       <c r="AB70">
         <f>_xlfn.QUARTILE.EXC((F74:F134,N74:N134),3)</f>
@@ -6279,12 +6693,12 @@
         <v>82</v>
       </c>
       <c r="D71" s="31">
-        <f t="shared" ref="D71:F71" si="14">MAX(D7:D67)</f>
+        <f t="shared" ref="D71:F71" si="16">MAX(D7:D67)</f>
         <v>2074.6347596000001</v>
       </c>
       <c r="E71" s="31"/>
       <c r="F71" s="31">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>932.88624049999999</v>
       </c>
       <c r="G71" s="31"/>
@@ -6293,24 +6707,30 @@
         <v>452.67738200000002</v>
       </c>
       <c r="I71" s="31"/>
-      <c r="J71" s="31"/>
+      <c r="J71" s="31">
+        <f>MAX(J7:J67)</f>
+        <v>37.537199999999999</v>
+      </c>
       <c r="K71" s="31"/>
       <c r="L71" s="31">
-        <f t="shared" ref="L71:P71" si="15">MAX(L7:L67)</f>
+        <f t="shared" ref="L71:P71" si="17">MAX(L7:L67)</f>
         <v>2702.1846860999999</v>
       </c>
       <c r="M71" s="31"/>
       <c r="N71" s="31">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>7218.0189136999998</v>
       </c>
       <c r="O71" s="31"/>
       <c r="P71" s="31">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>456.90458919999998</v>
       </c>
       <c r="Q71" s="31"/>
-      <c r="R71" s="31"/>
+      <c r="R71" s="31">
+        <f t="shared" ref="R71" si="18">MAX(R7:R67)</f>
+        <v>38.036000000000001</v>
+      </c>
       <c r="W71" s="37" t="s">
         <v>109</v>
       </c>
@@ -6319,16 +6739,16 @@
         <v>1927.3264309999997</v>
       </c>
       <c r="Y71" s="10">
-        <f t="shared" ref="Y71:AB71" si="16">Y70+1.5*(Y70-Y69)</f>
+        <f t="shared" ref="Y71:AB71" si="19">Y70+1.5*(Y70-Y69)</f>
         <v>815.54601803750006</v>
       </c>
       <c r="Z71" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>112.53202647500001</v>
       </c>
-      <c r="AA71" s="10" t="e">
+      <c r="AA71" s="10">
         <f>AA70+1.5*(AA70-AA69)</f>
-        <v>#NUM!</v>
+        <v>37.923762499999995</v>
       </c>
       <c r="AB71" s="10">
         <f>AB70+1.5*(AB70-AB69)</f>
@@ -6349,12 +6769,12 @@
         <v>83</v>
       </c>
       <c r="D72" s="31">
-        <f t="shared" ref="D72:F72" si="17">STDEV(D7:D67)</f>
+        <f t="shared" ref="D72:F72" si="20">STDEV(D7:D67)</f>
         <v>436.89147549757564</v>
       </c>
       <c r="E72" s="31"/>
       <c r="F72" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>242.69754810017969</v>
       </c>
       <c r="G72" s="31"/>
@@ -6363,24 +6783,30 @@
         <v>74.776434817048084</v>
       </c>
       <c r="I72" s="31"/>
-      <c r="J72" s="31"/>
+      <c r="J72" s="31">
+        <f>STDEV(J7:J67)</f>
+        <v>1.1431948667614942</v>
+      </c>
       <c r="K72" s="31"/>
       <c r="L72" s="31">
-        <f t="shared" ref="L72:P72" si="18">STDEV(L7:L67)</f>
+        <f t="shared" ref="L72:P72" si="21">STDEV(L7:L67)</f>
         <v>566.58008735947578</v>
       </c>
       <c r="M72" s="31"/>
       <c r="N72" s="31">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>1065.9377509710532</v>
       </c>
       <c r="O72" s="31"/>
       <c r="P72" s="31">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>65.794122050148587</v>
       </c>
       <c r="Q72" s="31"/>
-      <c r="R72" s="31"/>
+      <c r="R72" s="31">
+        <f t="shared" ref="R72" si="22">STDEV(R7:R67)</f>
+        <v>1.3396074140686463</v>
+      </c>
       <c r="W72" s="37" t="s">
         <v>110</v>
       </c>
@@ -6389,16 +6815,16 @@
         <v>0</v>
       </c>
       <c r="Y72" s="10">
-        <f t="shared" ref="Y72:AB72" si="19">IF(Y69-1.5*(Y70-Y69)&lt;0,0,Y69-1.5*(Y70-Y69))</f>
+        <f t="shared" ref="Y72:AB72" si="23">IF(Y69-1.5*(Y70-Y69)&lt;0,0,Y69-1.5*(Y70-Y69))</f>
         <v>0</v>
       </c>
       <c r="Z72" s="10">
         <f>IF(Z69-1.5*(Z70-Z69)&lt;0,0,Z69-1.5*(Z70-Z69))</f>
         <v>38.248950675000003</v>
       </c>
-      <c r="AA72" s="10" t="e">
+      <c r="AA72" s="10">
         <f>IF(AA69-1.5*(AA70-AA69)&lt;0,0,AA69-1.5*(AA70-AA69))</f>
-        <v>#NUM!</v>
+        <v>30.275662499999996</v>
       </c>
       <c r="AB72" s="10">
         <f>IF(AB69-1.5*(AB70-AB69)&lt;0,0,AB69-1.5*(AB70-AB69))</f>
@@ -6540,7 +6966,7 @@
         <v>275.11039959999999</v>
       </c>
       <c r="I77" s="33"/>
-      <c r="J77" s="90">
+      <c r="J77" s="89">
         <v>353.98700000000002</v>
       </c>
       <c r="L77" s="33" t="s">
@@ -6586,7 +7012,7 @@
       <c r="P78">
         <v>66.381577199999995</v>
       </c>
-      <c r="R78" s="83">
+      <c r="R78" s="82">
         <v>50.402000000000001</v>
       </c>
     </row>
@@ -6949,7 +7375,7 @@
         <v>73.746508800000001</v>
       </c>
       <c r="I89" s="33"/>
-      <c r="J89" s="90">
+      <c r="J89" s="89">
         <v>50.674999999999997</v>
       </c>
       <c r="L89" s="33" t="s">
@@ -7370,7 +7796,7 @@
       <c r="P101">
         <v>284.09153300000003</v>
       </c>
-      <c r="R101" s="83">
+      <c r="R101" s="82">
         <v>50.481000000000002</v>
       </c>
     </row>
@@ -7481,7 +7907,7 @@
       <c r="P105">
         <v>491.76410010000001</v>
       </c>
-      <c r="R105" s="83">
+      <c r="R105" s="82">
         <v>51.8</v>
       </c>
     </row>
@@ -7515,7 +7941,7 @@
       <c r="P106">
         <v>232.53405960000001</v>
       </c>
-      <c r="R106" s="83">
+      <c r="R106" s="82">
         <v>50.033000000000001</v>
       </c>
     </row>
@@ -7571,7 +7997,7 @@
         <v>971.69256729999995</v>
       </c>
       <c r="I108" s="33"/>
-      <c r="J108" s="90">
+      <c r="J108" s="89">
         <v>51.485999999999997</v>
       </c>
       <c r="L108" s="33" t="s">
@@ -7639,7 +8065,7 @@
         <v>145.6007726</v>
       </c>
       <c r="I110" s="33"/>
-      <c r="J110" s="90">
+      <c r="J110" s="89">
         <v>51.104999999999997</v>
       </c>
       <c r="L110" s="33" t="s">
@@ -7741,7 +8167,7 @@
         <v>780.2396066</v>
       </c>
       <c r="I113" s="33"/>
-      <c r="J113" s="91">
+      <c r="J113" s="90">
         <v>251.42080000000001</v>
       </c>
       <c r="L113" s="33" t="s">
@@ -7810,7 +8236,7 @@
         <v>86.674660399999993</v>
       </c>
       <c r="I115" s="33"/>
-      <c r="J115" s="90">
+      <c r="J115" s="89">
         <v>52.41</v>
       </c>
       <c r="L115" s="33" t="s">
@@ -7822,7 +8248,7 @@
       <c r="P115">
         <v>174.2282764</v>
       </c>
-      <c r="R115" s="82">
+      <c r="R115" s="81">
         <v>52.584600000000002</v>
       </c>
     </row>
@@ -7844,7 +8270,7 @@
         <v>166.6076999</v>
       </c>
       <c r="I116" s="33"/>
-      <c r="J116" s="90">
+      <c r="J116" s="89">
         <v>51.065199999999997</v>
       </c>
       <c r="L116" s="33" t="s">
@@ -7878,7 +8304,7 @@
         <v>83.641438399999998</v>
       </c>
       <c r="I117" s="33"/>
-      <c r="J117" s="90">
+      <c r="J117" s="89">
         <v>51.0871</v>
       </c>
       <c r="L117" s="33" t="s">
@@ -7912,7 +8338,7 @@
         <v>78.636828100000002</v>
       </c>
       <c r="I118" s="33"/>
-      <c r="J118" s="90">
+      <c r="J118" s="89">
         <v>50.910699999999999</v>
       </c>
       <c r="L118" s="33" t="s">
@@ -7946,7 +8372,7 @@
         <v>78.712250999999995</v>
       </c>
       <c r="I119" s="33"/>
-      <c r="J119" s="90">
+      <c r="J119" s="89">
         <v>50.9011</v>
       </c>
       <c r="L119" s="33" t="s">
@@ -7980,7 +8406,7 @@
         <v>396.00587339999998</v>
       </c>
       <c r="I120" s="33"/>
-      <c r="J120" s="90">
+      <c r="J120" s="89">
         <v>50.796599999999998</v>
       </c>
       <c r="L120" s="33" t="s">
@@ -7992,7 +8418,7 @@
       <c r="P120">
         <v>97.068762699999994</v>
       </c>
-      <c r="R120" s="83">
+      <c r="R120" s="82">
         <v>50.25</v>
       </c>
     </row>
@@ -8014,7 +8440,7 @@
         <v>242.74594289999999</v>
       </c>
       <c r="I121" s="33"/>
-      <c r="J121" s="90">
+      <c r="J121" s="89">
         <v>51.620199999999997</v>
       </c>
       <c r="L121" s="33" t="s">
@@ -8048,7 +8474,7 @@
         <v>78.237251799999996</v>
       </c>
       <c r="I122" s="33"/>
-      <c r="J122" s="90">
+      <c r="J122" s="89">
         <v>51.393599999999999</v>
       </c>
       <c r="L122" s="33" t="s">
@@ -8082,7 +8508,7 @@
         <v>81.641992000000002</v>
       </c>
       <c r="I123" s="33"/>
-      <c r="J123" s="90">
+      <c r="J123" s="89">
         <v>51.420200000000001</v>
       </c>
       <c r="L123" s="33" t="s">
@@ -8115,7 +8541,7 @@
         <v>78.717697200000003</v>
       </c>
       <c r="I124" s="31"/>
-      <c r="J124" s="92">
+      <c r="J124" s="91">
         <v>51.58</v>
       </c>
       <c r="L124" s="33" t="s">
@@ -8151,7 +8577,7 @@
         <v>80.974393000000006</v>
       </c>
       <c r="I125" s="33"/>
-      <c r="J125" s="93">
+      <c r="J125" s="92">
         <v>52.299199999999999</v>
       </c>
       <c r="L125" s="33" t="s">
@@ -8185,7 +8611,7 @@
         <v>87.044013899999996</v>
       </c>
       <c r="I126" s="33"/>
-      <c r="J126" s="93">
+      <c r="J126" s="92">
         <v>50.614699999999999</v>
       </c>
       <c r="L126" s="33" t="s">
@@ -8219,7 +8645,7 @@
         <v>88.587937499999995</v>
       </c>
       <c r="I127" s="33"/>
-      <c r="J127" s="93">
+      <c r="J127" s="92">
         <v>50.531399999999998</v>
       </c>
       <c r="L127" s="33" t="s">
@@ -8253,7 +8679,7 @@
         <v>83.735353000000003</v>
       </c>
       <c r="I128" s="33"/>
-      <c r="J128" s="93">
+      <c r="J128" s="92">
         <v>50.688400000000001</v>
       </c>
       <c r="L128" s="33" t="s">
@@ -8287,7 +8713,7 @@
         <v>78.882186200000007</v>
       </c>
       <c r="I129" s="33"/>
-      <c r="J129" s="93">
+      <c r="J129" s="92">
         <v>51.0458</v>
       </c>
       <c r="L129" s="33" t="s">
@@ -8321,7 +8747,7 @@
         <v>77.985264799999996</v>
       </c>
       <c r="I130" s="33"/>
-      <c r="J130" s="93">
+      <c r="J130" s="92">
         <v>51.209400000000002</v>
       </c>
       <c r="L130" s="33" t="s">
@@ -8355,7 +8781,7 @@
         <v>81.148442500000002</v>
       </c>
       <c r="I131" s="33"/>
-      <c r="J131" s="93">
+      <c r="J131" s="92">
         <v>50.741500000000002</v>
       </c>
       <c r="L131" s="33" t="s">
@@ -8389,7 +8815,7 @@
         <v>77.694044700000006</v>
       </c>
       <c r="I132" s="33"/>
-      <c r="J132" s="93">
+      <c r="J132" s="92">
         <v>50.7605</v>
       </c>
       <c r="L132" s="33" t="s">
@@ -8423,7 +8849,7 @@
         <v>79.305596800000004</v>
       </c>
       <c r="I133" s="33"/>
-      <c r="J133" s="93">
+      <c r="J133" s="92">
         <v>50.810699999999997</v>
       </c>
       <c r="L133" s="33" t="s">
@@ -8456,7 +8882,7 @@
         <v>79.388584199999997</v>
       </c>
       <c r="I134" s="31"/>
-      <c r="J134" s="93">
+      <c r="J134" s="92">
         <v>50.944000000000003</v>
       </c>
       <c r="L134" s="33" t="s">
@@ -8482,12 +8908,12 @@
         <v>87</v>
       </c>
       <c r="D136" s="31" t="e">
-        <f t="shared" ref="D136" si="20">AVERAGE(D74:D134)</f>
+        <f t="shared" ref="D136" si="24">AVERAGE(D74:D134)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E136" s="31"/>
       <c r="F136" s="31">
-        <f t="shared" ref="F136" si="21">AVERAGE(F74:F134)</f>
+        <f t="shared" ref="F136" si="25">AVERAGE(F74:F134)</f>
         <v>570.32474507166648</v>
       </c>
       <c r="G136" s="31"/>
@@ -8502,22 +8928,22 @@
       </c>
       <c r="K136" s="31"/>
       <c r="L136" s="31" t="e">
-        <f t="shared" ref="L136:P136" si="22">AVERAGE(L74:L134)</f>
+        <f t="shared" ref="L136:P136" si="26">AVERAGE(L74:L134)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M136" s="31"/>
       <c r="N136" s="31">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>424.62852865714297</v>
       </c>
       <c r="O136" s="31"/>
       <c r="P136" s="31">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>283.29640059000008</v>
       </c>
       <c r="Q136" s="31"/>
       <c r="R136" s="31">
-        <f t="shared" ref="Q136:R136" si="23">AVERAGE(R74:R134)</f>
+        <f t="shared" ref="Q136:R136" si="27">AVERAGE(R74:R134)</f>
         <v>54.376823333333355</v>
       </c>
       <c r="S136" s="31"/>
@@ -8529,12 +8955,12 @@
         <v>81</v>
       </c>
       <c r="D137" s="31">
-        <f t="shared" ref="D137" si="24">MIN(D74:D134)</f>
+        <f t="shared" ref="D137" si="28">MIN(D74:D134)</f>
         <v>0</v>
       </c>
       <c r="E137" s="31"/>
       <c r="F137" s="31">
-        <f t="shared" ref="F137" si="25">MIN(F74:F134)</f>
+        <f t="shared" ref="F137" si="29">MIN(F74:F134)</f>
         <v>64.483929500000002</v>
       </c>
       <c r="G137" s="31"/>
@@ -8549,22 +8975,22 @@
       </c>
       <c r="K137" s="31"/>
       <c r="L137" s="31">
-        <f t="shared" ref="L137:P137" si="26">MIN(L74:L134)</f>
+        <f t="shared" ref="L137:P137" si="30">MIN(L74:L134)</f>
         <v>0</v>
       </c>
       <c r="M137" s="31"/>
       <c r="N137" s="31">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>69.129179500000006</v>
       </c>
       <c r="O137" s="31"/>
       <c r="P137" s="31">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>65.962567100000001</v>
       </c>
       <c r="Q137" s="31"/>
       <c r="R137" s="31">
-        <f t="shared" ref="Q137:R137" si="27">MIN(R74:R134)</f>
+        <f t="shared" ref="Q137:R137" si="31">MIN(R74:R134)</f>
         <v>49.9163</v>
       </c>
       <c r="S137" s="31"/>
@@ -8576,12 +9002,12 @@
         <v>82</v>
       </c>
       <c r="D138" s="31">
-        <f t="shared" ref="D138" si="28">MAX(D74:D134)</f>
+        <f t="shared" ref="D138" si="32">MAX(D74:D134)</f>
         <v>0</v>
       </c>
       <c r="E138" s="31"/>
       <c r="F138" s="31">
-        <f t="shared" ref="F138" si="29">MAX(F74:F134)</f>
+        <f t="shared" ref="F138" si="33">MAX(F74:F134)</f>
         <v>2543.6004963999999</v>
       </c>
       <c r="G138" s="31"/>
@@ -8596,22 +9022,22 @@
       </c>
       <c r="K138" s="31"/>
       <c r="L138" s="31">
-        <f t="shared" ref="L138:P138" si="30">MAX(L74:L134)</f>
+        <f t="shared" ref="L138:P138" si="34">MAX(L74:L134)</f>
         <v>0</v>
       </c>
       <c r="M138" s="31"/>
       <c r="N138" s="31">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>3419.3379930999999</v>
       </c>
       <c r="O138" s="31"/>
       <c r="P138" s="31">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>2129.4957175999998</v>
       </c>
       <c r="Q138" s="31"/>
       <c r="R138" s="31">
-        <f t="shared" ref="Q138:R138" si="31">MAX(R74:R134)</f>
+        <f t="shared" ref="Q138:R138" si="35">MAX(R74:R134)</f>
         <v>102.2818</v>
       </c>
       <c r="S138" s="31"/>
@@ -8623,12 +9049,12 @@
         <v>83</v>
       </c>
       <c r="D139" s="31" t="e">
-        <f t="shared" ref="D139" si="32">STDEV(D74:D134)</f>
+        <f t="shared" ref="D139" si="36">STDEV(D74:D134)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E139" s="31"/>
       <c r="F139" s="31">
-        <f t="shared" ref="F139" si="33">STDEV(F74:F134)</f>
+        <f t="shared" ref="F139" si="37">STDEV(F74:F134)</f>
         <v>551.46046394672555</v>
       </c>
       <c r="G139" s="31"/>
@@ -8643,22 +9069,22 @@
       </c>
       <c r="K139" s="31"/>
       <c r="L139" s="31" t="e">
-        <f t="shared" ref="L139:P139" si="34">STDEV(L74:L134)</f>
+        <f t="shared" ref="L139:P139" si="38">STDEV(L74:L134)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M139" s="31"/>
       <c r="N139" s="31">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>645.77916920766768</v>
       </c>
       <c r="O139" s="31"/>
       <c r="P139" s="31">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>356.31758150072289</v>
       </c>
       <c r="Q139" s="31"/>
       <c r="R139" s="31">
-        <f t="shared" ref="Q139:R139" si="35">STDEV(R74:R134)</f>
+        <f t="shared" ref="Q139:R139" si="39">STDEV(R74:R134)</f>
         <v>12.653955605550385</v>
       </c>
       <c r="S139" s="31"/>

--- a/eBike_controller/Results.xlsx
+++ b/eBike_controller/Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrea/Documents/GitHub/HECATE_BikeAndDrone/eBike_controller/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0280806D-26FB-7A49-9266-F389D0813B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1500EFB0-5B0F-EF41-BF0B-EF8B09671D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="68640" yWindow="-9480" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="-9480" windowWidth="38400" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -399,7 +399,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="170" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -643,7 +643,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -762,34 +762,51 @@
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -810,97 +827,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1190,160 +1135,160 @@
     <col min="2" max="2" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="1.6640625" customWidth="1"/>
     <col min="7" max="7" width="1" customWidth="1"/>
-    <col min="11" max="11" width="0.83203125" style="79" customWidth="1"/>
+    <col min="11" max="11" width="0.83203125" customWidth="1"/>
     <col min="15" max="15" width="1" customWidth="1"/>
     <col min="23" max="23" width="1.33203125" customWidth="1"/>
-    <col min="27" max="27" width="0.6640625" style="79" customWidth="1"/>
+    <col min="27" max="27" width="0.6640625" customWidth="1"/>
     <col min="31" max="31" width="1.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="T1" s="44" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="T1" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
-      <c r="Y1" s="44"/>
-      <c r="Z1" s="44"/>
-      <c r="AA1" s="44"/>
-      <c r="AB1" s="44"/>
-      <c r="AC1" s="44"/>
-      <c r="AD1" s="44"/>
-      <c r="AE1" s="44"/>
-      <c r="AF1" s="44"/>
-      <c r="AG1" s="44"/>
-      <c r="AH1" s="44"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="67"/>
+      <c r="X1" s="67"/>
+      <c r="Y1" s="67"/>
+      <c r="Z1" s="67"/>
+      <c r="AA1" s="67"/>
+      <c r="AB1" s="67"/>
+      <c r="AC1" s="67"/>
+      <c r="AD1" s="67"/>
+      <c r="AE1" s="67"/>
+      <c r="AF1" s="67"/>
+      <c r="AG1" s="67"/>
+      <c r="AH1" s="67"/>
     </row>
     <row r="2" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="44"/>
-      <c r="T2" s="44"/>
-      <c r="U2" s="44"/>
-      <c r="V2" s="44"/>
-      <c r="W2" s="44"/>
-      <c r="X2" s="44"/>
-      <c r="Y2" s="44"/>
-      <c r="Z2" s="44"/>
-      <c r="AA2" s="44"/>
-      <c r="AB2" s="44"/>
-      <c r="AC2" s="44"/>
-      <c r="AD2" s="44"/>
-      <c r="AE2" s="44"/>
-      <c r="AF2" s="44"/>
-      <c r="AG2" s="44"/>
-      <c r="AH2" s="44"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
+      <c r="V2" s="67"/>
+      <c r="W2" s="67"/>
+      <c r="X2" s="67"/>
+      <c r="Y2" s="67"/>
+      <c r="Z2" s="67"/>
+      <c r="AA2" s="67"/>
+      <c r="AB2" s="67"/>
+      <c r="AC2" s="67"/>
+      <c r="AD2" s="67"/>
+      <c r="AE2" s="67"/>
+      <c r="AF2" s="67"/>
+      <c r="AG2" s="67"/>
+      <c r="AH2" s="67"/>
     </row>
     <row r="3" spans="1:34" ht="16" x14ac:dyDescent="0.2">
-      <c r="D3" s="54" t="s">
+      <c r="D3" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="55"/>
-      <c r="F3" s="56"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="63"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="54" t="s">
+      <c r="H3" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="55"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="54" t="s">
+      <c r="I3" s="62"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="55"/>
-      <c r="N3" s="56"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="63"/>
       <c r="O3" s="3"/>
-      <c r="P3" s="54" t="s">
+      <c r="P3" s="61" t="s">
         <v>111</v>
       </c>
-      <c r="Q3" s="55"/>
-      <c r="R3" s="56"/>
-      <c r="T3" s="54" t="s">
+      <c r="Q3" s="62"/>
+      <c r="R3" s="63"/>
+      <c r="T3" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="U3" s="55"/>
-      <c r="V3" s="56"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="63"/>
       <c r="W3" s="3"/>
-      <c r="X3" s="54" t="s">
+      <c r="X3" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="Y3" s="55"/>
-      <c r="Z3" s="56"/>
-      <c r="AA3" s="83"/>
-      <c r="AB3" s="54" t="s">
+      <c r="Y3" s="62"/>
+      <c r="Z3" s="63"/>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="AC3" s="55"/>
-      <c r="AD3" s="56"/>
+      <c r="AC3" s="62"/>
+      <c r="AD3" s="63"/>
       <c r="AE3" s="3"/>
-      <c r="AF3" s="71" t="s">
+      <c r="AF3" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="AG3" s="72"/>
-      <c r="AH3" s="73"/>
+      <c r="AG3" s="62"/>
+      <c r="AH3" s="63"/>
     </row>
     <row r="4" spans="1:34" ht="16" x14ac:dyDescent="0.2">
-      <c r="D4" s="57"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="59"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="66"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="59"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
       <c r="O4" s="3"/>
-      <c r="P4" s="57"/>
-      <c r="Q4" s="58"/>
-      <c r="R4" s="59"/>
-      <c r="T4" s="57"/>
-      <c r="U4" s="58"/>
-      <c r="V4" s="59"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="66"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
       <c r="W4" s="3"/>
-      <c r="X4" s="57"/>
-      <c r="Y4" s="58"/>
-      <c r="Z4" s="59"/>
-      <c r="AA4" s="83"/>
-      <c r="AB4" s="57"/>
-      <c r="AC4" s="58"/>
-      <c r="AD4" s="59"/>
+      <c r="X4" s="64"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="66"/>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="64"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="66"/>
       <c r="AE4" s="3"/>
-      <c r="AF4" s="74"/>
-      <c r="AG4" s="75"/>
-      <c r="AH4" s="76"/>
+      <c r="AF4" s="64"/>
+      <c r="AG4" s="65"/>
+      <c r="AH4" s="66"/>
     </row>
     <row r="5" spans="1:34" ht="16" x14ac:dyDescent="0.2">
       <c r="D5" s="4"/>
@@ -1353,7 +1298,7 @@
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
-      <c r="K5" s="77"/>
+      <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
@@ -1368,14 +1313,14 @@
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
-      <c r="AA5" s="77"/>
+      <c r="AA5" s="4"/>
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
       <c r="AD5" s="4"/>
       <c r="AE5" s="3"/>
-      <c r="AF5" s="77"/>
-      <c r="AG5" s="77"/>
-      <c r="AH5" s="77"/>
+      <c r="AF5" s="4"/>
+      <c r="AG5" s="4"/>
+      <c r="AH5" s="4"/>
     </row>
     <row r="6" spans="1:34" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
@@ -1403,7 +1348,7 @@
       <c r="J6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="83"/>
+      <c r="K6" s="4"/>
       <c r="L6" s="5" t="s">
         <v>7</v>
       </c>
@@ -1442,7 +1387,7 @@
       <c r="Z6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="AA6" s="83"/>
+      <c r="AA6" s="4"/>
       <c r="AB6" s="5" t="s">
         <v>7</v>
       </c>
@@ -1453,24 +1398,21 @@
         <v>9</v>
       </c>
       <c r="AE6" s="3"/>
-      <c r="AF6" s="78" t="s">
+      <c r="AF6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="AG6" s="78" t="s">
+      <c r="AG6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="AH6" s="78" t="s">
+      <c r="AH6" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4"/>
-      <c r="AF7" s="79"/>
-      <c r="AG7" s="79"/>
-      <c r="AH7" s="79"/>
     </row>
     <row r="8" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="60" t="s">
+      <c r="A8" s="58" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1495,7 +1437,7 @@
       <c r="J8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K8" s="86"/>
+      <c r="K8" s="9"/>
       <c r="L8" s="11" t="s">
         <v>12</v>
       </c>
@@ -1506,13 +1448,13 @@
         <v>17</v>
       </c>
       <c r="O8" s="9"/>
-      <c r="P8" s="66" t="s">
+      <c r="P8" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Q8" s="68" t="s">
+      <c r="Q8" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="R8" s="68" t="s">
+      <c r="R8" s="15" t="s">
         <v>17</v>
       </c>
       <c r="T8" s="11" t="s">
@@ -1534,7 +1476,7 @@
       <c r="Z8" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="AA8" s="84"/>
+      <c r="AA8" s="46"/>
       <c r="AB8" s="13" t="s">
         <v>12</v>
       </c>
@@ -1545,18 +1487,18 @@
         <v>14</v>
       </c>
       <c r="AE8" s="9"/>
-      <c r="AF8" s="66" t="s">
+      <c r="AF8" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AG8" s="68" t="s">
+      <c r="AG8" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="AH8" s="68" t="s">
+      <c r="AH8" s="15" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="61"/>
+      <c r="A9" s="59"/>
       <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
@@ -1579,7 +1521,7 @@
       <c r="J9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="87"/>
+      <c r="K9" s="10"/>
       <c r="L9" s="11" t="s">
         <v>12</v>
       </c>
@@ -1590,13 +1532,13 @@
         <v>17</v>
       </c>
       <c r="O9" s="9"/>
-      <c r="P9" s="66" t="s">
+      <c r="P9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Q9" s="68" t="s">
+      <c r="Q9" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="R9" s="68" t="s">
+      <c r="R9" s="15" t="s">
         <v>17</v>
       </c>
       <c r="T9" s="13" t="s">
@@ -1618,7 +1560,7 @@
       <c r="Z9" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AA9" s="84"/>
+      <c r="AA9" s="46"/>
       <c r="AB9" s="13" t="s">
         <v>12</v>
       </c>
@@ -1629,18 +1571,18 @@
         <v>17</v>
       </c>
       <c r="AE9" s="9"/>
-      <c r="AF9" s="66" t="s">
+      <c r="AF9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AG9" s="68" t="s">
+      <c r="AG9" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="AH9" s="68" t="s">
+      <c r="AH9" s="15" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="61"/>
+      <c r="A10" s="59"/>
       <c r="B10" s="2" t="s">
         <v>27</v>
       </c>
@@ -1663,7 +1605,7 @@
       <c r="J10" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K10" s="88"/>
+      <c r="K10" s="48"/>
       <c r="L10" s="11" t="s">
         <v>12</v>
       </c>
@@ -1674,13 +1616,13 @@
         <v>17</v>
       </c>
       <c r="O10" s="9"/>
-      <c r="P10" s="66" t="s">
+      <c r="P10" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Q10" s="68" t="s">
+      <c r="Q10" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="R10" s="68" t="s">
+      <c r="R10" s="15" t="s">
         <v>17</v>
       </c>
       <c r="T10" s="13" t="s">
@@ -1702,7 +1644,7 @@
       <c r="Z10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="AA10" s="84"/>
+      <c r="AA10" s="46"/>
       <c r="AB10" s="13" t="s">
         <v>12</v>
       </c>
@@ -1713,18 +1655,18 @@
         <v>17</v>
       </c>
       <c r="AE10" s="9"/>
-      <c r="AF10" s="66" t="s">
+      <c r="AF10" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AG10" s="68" t="s">
+      <c r="AG10" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="AH10" s="68" t="s">
+      <c r="AH10" s="15" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="61"/>
+      <c r="A11" s="59"/>
       <c r="B11" s="2"/>
       <c r="D11" s="9"/>
       <c r="E11" s="10"/>
@@ -1733,14 +1675,14 @@
       <c r="H11" s="9"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
-      <c r="K11" s="70"/>
+      <c r="K11" s="10"/>
       <c r="L11" s="9"/>
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
       <c r="O11" s="9"/>
-      <c r="P11" s="69"/>
-      <c r="Q11" s="70"/>
-      <c r="R11" s="70"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
       <c r="T11" s="9"/>
       <c r="U11" s="10"/>
       <c r="V11" s="10"/>
@@ -1748,17 +1690,17 @@
       <c r="X11" s="9"/>
       <c r="Y11" s="10"/>
       <c r="Z11" s="10"/>
-      <c r="AA11" s="70"/>
+      <c r="AA11" s="10"/>
       <c r="AB11" s="9"/>
       <c r="AC11" s="10"/>
       <c r="AD11" s="10"/>
       <c r="AE11" s="9"/>
-      <c r="AF11" s="69"/>
-      <c r="AG11" s="70"/>
-      <c r="AH11" s="70"/>
+      <c r="AF11" s="9"/>
+      <c r="AG11" s="10"/>
+      <c r="AH11" s="10"/>
     </row>
     <row r="12" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="61"/>
+      <c r="A12" s="59"/>
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
@@ -1781,7 +1723,7 @@
       <c r="J12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="88"/>
+      <c r="K12" s="48"/>
       <c r="L12" s="11" t="s">
         <v>12</v>
       </c>
@@ -1792,13 +1734,13 @@
         <v>38</v>
       </c>
       <c r="O12" s="9"/>
-      <c r="P12" s="66" t="s">
+      <c r="P12" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Q12" s="68" t="s">
+      <c r="Q12" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="R12" s="68" t="s">
+      <c r="R12" s="15" t="s">
         <v>17</v>
       </c>
       <c r="T12" s="16" t="s">
@@ -1820,7 +1762,7 @@
       <c r="Z12" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AA12" s="84"/>
+      <c r="AA12" s="46"/>
       <c r="AB12" s="16" t="s">
         <v>12</v>
       </c>
@@ -1831,18 +1773,18 @@
         <v>17</v>
       </c>
       <c r="AE12" s="9"/>
-      <c r="AF12" s="66" t="s">
+      <c r="AF12" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AG12" s="68" t="s">
+      <c r="AG12" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="AH12" s="68" t="s">
+      <c r="AH12" s="15" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="61"/>
+      <c r="A13" s="59"/>
       <c r="B13" s="2" t="s">
         <v>42</v>
       </c>
@@ -1865,7 +1807,7 @@
       <c r="J13" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="K13" s="88"/>
+      <c r="K13" s="48"/>
       <c r="L13" s="11" t="s">
         <v>12</v>
       </c>
@@ -1876,13 +1818,13 @@
         <v>17</v>
       </c>
       <c r="O13" s="9"/>
-      <c r="P13" s="66" t="s">
+      <c r="P13" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Q13" s="68" t="s">
+      <c r="Q13" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="R13" s="68" t="s">
+      <c r="R13" s="15" t="s">
         <v>17</v>
       </c>
       <c r="T13" s="11" t="s">
@@ -1904,7 +1846,7 @@
       <c r="Z13" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="AA13" s="84"/>
+      <c r="AA13" s="46"/>
       <c r="AB13" s="13" t="s">
         <v>12</v>
       </c>
@@ -1915,18 +1857,18 @@
         <v>17</v>
       </c>
       <c r="AE13" s="9"/>
-      <c r="AF13" s="66" t="s">
+      <c r="AF13" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AG13" s="68" t="s">
+      <c r="AG13" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="AH13" s="68" t="s">
+      <c r="AH13" s="15" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="62"/>
+      <c r="A14" s="60"/>
       <c r="B14" s="2" t="s">
         <v>48</v>
       </c>
@@ -1949,7 +1891,7 @@
       <c r="J14" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="K14" s="87"/>
+      <c r="K14" s="10"/>
       <c r="L14" s="11" t="s">
         <v>12</v>
       </c>
@@ -1960,13 +1902,13 @@
         <v>17</v>
       </c>
       <c r="O14" s="9"/>
-      <c r="P14" s="66" t="s">
+      <c r="P14" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Q14" s="68" t="s">
+      <c r="Q14" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="R14" s="68" t="s">
+      <c r="R14" s="15" t="s">
         <v>17</v>
       </c>
       <c r="T14" s="16" t="s">
@@ -1988,7 +1930,7 @@
       <c r="Z14" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="AA14" s="84"/>
+      <c r="AA14" s="46"/>
       <c r="AB14" s="13" t="s">
         <v>12</v>
       </c>
@@ -1999,13 +1941,13 @@
         <v>17</v>
       </c>
       <c r="AE14" s="9"/>
-      <c r="AF14" s="66" t="s">
+      <c r="AF14" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AG14" s="68" t="s">
+      <c r="AG14" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="AH14" s="68" t="s">
+      <c r="AH14" s="15" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2018,14 +1960,14 @@
       <c r="H15" s="9"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
-      <c r="K15" s="70"/>
+      <c r="K15" s="10"/>
       <c r="L15" s="9"/>
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
       <c r="O15" s="9"/>
-      <c r="P15" s="69"/>
-      <c r="Q15" s="70"/>
-      <c r="R15" s="70"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
       <c r="T15" s="9"/>
       <c r="U15" s="10"/>
       <c r="V15" s="10"/>
@@ -2033,14 +1975,14 @@
       <c r="X15" s="9"/>
       <c r="Y15" s="10"/>
       <c r="Z15" s="10"/>
-      <c r="AA15" s="70"/>
+      <c r="AA15" s="10"/>
       <c r="AB15" s="9"/>
       <c r="AC15" s="10"/>
       <c r="AD15" s="10"/>
       <c r="AE15" s="9"/>
-      <c r="AF15" s="69"/>
-      <c r="AG15" s="70"/>
-      <c r="AH15" s="70"/>
+      <c r="AF15" s="9"/>
+      <c r="AG15" s="10"/>
+      <c r="AH15" s="10"/>
     </row>
     <row r="16" spans="1:34" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
@@ -2051,14 +1993,14 @@
       <c r="H16" s="9"/>
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
-      <c r="K16" s="70"/>
+      <c r="K16" s="10"/>
       <c r="L16" s="9"/>
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
       <c r="O16" s="9"/>
-      <c r="P16" s="69"/>
-      <c r="Q16" s="70"/>
-      <c r="R16" s="70"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
       <c r="T16" s="9"/>
       <c r="U16" s="10"/>
       <c r="V16" s="10"/>
@@ -2066,17 +2008,17 @@
       <c r="X16" s="9"/>
       <c r="Y16" s="10"/>
       <c r="Z16" s="10"/>
-      <c r="AA16" s="70"/>
+      <c r="AA16" s="10"/>
       <c r="AB16" s="9"/>
       <c r="AC16" s="10"/>
       <c r="AD16" s="10"/>
       <c r="AE16" s="9"/>
-      <c r="AF16" s="69"/>
-      <c r="AG16" s="70"/>
-      <c r="AH16" s="70"/>
+      <c r="AF16" s="9"/>
+      <c r="AG16" s="10"/>
+      <c r="AH16" s="10"/>
     </row>
     <row r="17" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="60" t="s">
+      <c r="A17" s="58" t="s">
         <v>54</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -2097,7 +2039,7 @@
       <c r="J17" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K17" s="87"/>
+      <c r="K17" s="10"/>
       <c r="L17" s="6" t="s">
         <v>12</v>
       </c>
@@ -2108,13 +2050,13 @@
         <v>38</v>
       </c>
       <c r="O17" s="9"/>
-      <c r="P17" s="66" t="s">
+      <c r="P17" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Q17" s="80" t="s">
+      <c r="Q17" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="R17" s="80" t="s">
+      <c r="R17" s="14" t="s">
         <v>17</v>
       </c>
       <c r="T17" s="13" t="s">
@@ -2132,7 +2074,7 @@
       <c r="Z17" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="AA17" s="85"/>
+      <c r="AA17" s="47"/>
       <c r="AB17" s="14" t="s">
         <v>12</v>
       </c>
@@ -2143,18 +2085,18 @@
         <v>24</v>
       </c>
       <c r="AE17" s="9"/>
-      <c r="AF17" s="66" t="s">
+      <c r="AF17" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AG17" s="80" t="s">
+      <c r="AG17" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="AH17" s="80" t="s">
+      <c r="AH17" s="14" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="61"/>
+      <c r="A18" s="59"/>
       <c r="B18" s="2" t="s">
         <v>22</v>
       </c>
@@ -2173,7 +2115,7 @@
       <c r="J18" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K18" s="86"/>
+      <c r="K18" s="9"/>
       <c r="L18" s="6" t="s">
         <v>12</v>
       </c>
@@ -2184,13 +2126,13 @@
         <v>47</v>
       </c>
       <c r="O18" s="9"/>
-      <c r="P18" s="66" t="s">
+      <c r="P18" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Q18" s="68" t="s">
+      <c r="Q18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="R18" s="68" t="s">
+      <c r="R18" s="15" t="s">
         <v>17</v>
       </c>
       <c r="T18" s="13" t="s">
@@ -2208,7 +2150,7 @@
       <c r="Z18" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="AA18" s="84"/>
+      <c r="AA18" s="46"/>
       <c r="AB18" s="13" t="s">
         <v>12</v>
       </c>
@@ -2219,18 +2161,18 @@
         <v>20</v>
       </c>
       <c r="AE18" s="9"/>
-      <c r="AF18" s="66" t="s">
+      <c r="AF18" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AG18" s="68" t="s">
+      <c r="AG18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="AH18" s="68" t="s">
+      <c r="AH18" s="15" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="61"/>
+      <c r="A19" s="59"/>
       <c r="B19" s="2" t="s">
         <v>27</v>
       </c>
@@ -2249,7 +2191,7 @@
       <c r="J19" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="K19" s="88"/>
+      <c r="K19" s="48"/>
       <c r="L19" s="11" t="s">
         <v>12</v>
       </c>
@@ -2260,13 +2202,13 @@
         <v>17</v>
       </c>
       <c r="O19" s="9"/>
-      <c r="P19" s="66" t="s">
+      <c r="P19" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Q19" s="68" t="s">
+      <c r="Q19" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="R19" s="68" t="s">
+      <c r="R19" s="15" t="s">
         <v>17</v>
       </c>
       <c r="T19" s="13" t="s">
@@ -2284,7 +2226,7 @@
       <c r="Z19" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="AA19" s="84"/>
+      <c r="AA19" s="46"/>
       <c r="AB19" s="13" t="s">
         <v>12</v>
       </c>
@@ -2295,18 +2237,18 @@
         <v>14</v>
       </c>
       <c r="AE19" s="9"/>
-      <c r="AF19" s="66" t="s">
+      <c r="AF19" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AG19" s="68" t="s">
+      <c r="AG19" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="AH19" s="68" t="s">
+      <c r="AH19" s="15" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="61"/>
+      <c r="A20" s="59"/>
       <c r="B20" s="2"/>
       <c r="D20" s="9"/>
       <c r="E20" s="10"/>
@@ -2315,14 +2257,14 @@
       <c r="H20" s="9"/>
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
-      <c r="K20" s="70"/>
+      <c r="K20" s="10"/>
       <c r="L20" s="9"/>
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
       <c r="O20" s="9"/>
-      <c r="P20" s="69"/>
-      <c r="Q20" s="70"/>
-      <c r="R20" s="70"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
@@ -2330,17 +2272,17 @@
       <c r="X20" s="9"/>
       <c r="Y20" s="10"/>
       <c r="Z20" s="10"/>
-      <c r="AA20" s="70"/>
+      <c r="AA20" s="10"/>
       <c r="AB20" s="9"/>
       <c r="AC20" s="10"/>
       <c r="AD20" s="10"/>
       <c r="AE20" s="9"/>
-      <c r="AF20" s="69"/>
-      <c r="AG20" s="70"/>
-      <c r="AH20" s="70"/>
+      <c r="AF20" s="9"/>
+      <c r="AG20" s="10"/>
+      <c r="AH20" s="10"/>
     </row>
     <row r="21" spans="1:34" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="61"/>
+      <c r="A21" s="59"/>
       <c r="B21" s="2" t="s">
         <v>33</v>
       </c>
@@ -2359,7 +2301,7 @@
       <c r="J21" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="K21" s="87"/>
+      <c r="K21" s="10"/>
       <c r="L21" s="11" t="s">
         <v>12</v>
       </c>
@@ -2370,13 +2312,13 @@
         <v>50</v>
       </c>
       <c r="O21" s="9"/>
-      <c r="P21" s="66" t="s">
+      <c r="P21" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Q21" s="67" t="s">
+      <c r="Q21" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="R21" s="67" t="s">
+      <c r="R21" s="12" t="s">
         <v>17</v>
       </c>
       <c r="T21" s="13" t="s">
@@ -2394,7 +2336,7 @@
       <c r="Z21" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="AA21" s="84"/>
+      <c r="AA21" s="46"/>
       <c r="AB21" s="11" t="s">
         <v>12</v>
       </c>
@@ -2405,18 +2347,18 @@
         <v>16</v>
       </c>
       <c r="AE21" s="9"/>
-      <c r="AF21" s="66" t="s">
+      <c r="AF21" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AG21" s="67" t="s">
+      <c r="AG21" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="AH21" s="67" t="s">
+      <c r="AH21" s="12" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="61"/>
+      <c r="A22" s="59"/>
       <c r="B22" s="2" t="s">
         <v>42</v>
       </c>
@@ -2435,7 +2377,7 @@
       <c r="J22" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="K22" s="87"/>
+      <c r="K22" s="10"/>
       <c r="L22" s="11" t="s">
         <v>12</v>
       </c>
@@ -2446,13 +2388,13 @@
         <v>17</v>
       </c>
       <c r="O22" s="9"/>
-      <c r="P22" s="66" t="s">
+      <c r="P22" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Q22" s="68" t="s">
+      <c r="Q22" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="R22" s="68" t="s">
+      <c r="R22" s="15" t="s">
         <v>17</v>
       </c>
       <c r="T22" s="13" t="s">
@@ -2470,7 +2412,7 @@
       <c r="Z22" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="AA22" s="84"/>
+      <c r="AA22" s="46"/>
       <c r="AB22" s="11" t="s">
         <v>12</v>
       </c>
@@ -2481,18 +2423,18 @@
         <v>14</v>
       </c>
       <c r="AE22" s="9"/>
-      <c r="AF22" s="66" t="s">
+      <c r="AF22" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AG22" s="68" t="s">
+      <c r="AG22" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="AH22" s="68" t="s">
+      <c r="AH22" s="15" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="62"/>
+      <c r="A23" s="60"/>
       <c r="B23" s="2" t="s">
         <v>48</v>
       </c>
@@ -2511,7 +2453,7 @@
       <c r="J23" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="K23" s="84"/>
+      <c r="K23" s="46"/>
       <c r="L23" s="11" t="s">
         <v>12</v>
       </c>
@@ -2522,13 +2464,13 @@
         <v>17</v>
       </c>
       <c r="O23" s="9"/>
-      <c r="P23" s="66" t="s">
+      <c r="P23" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Q23" s="68" t="s">
+      <c r="Q23" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="R23" s="68" t="s">
+      <c r="R23" s="15" t="s">
         <v>17</v>
       </c>
       <c r="T23" s="13" t="s">
@@ -2546,7 +2488,7 @@
       <c r="Z23" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="AA23" s="84"/>
+      <c r="AA23" s="46"/>
       <c r="AB23" s="11" t="s">
         <v>12</v>
       </c>
@@ -2557,23 +2499,18 @@
         <v>17</v>
       </c>
       <c r="AE23" s="9"/>
-      <c r="AF23" s="66" t="s">
+      <c r="AF23" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AG23" s="68" t="s">
+      <c r="AG23" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="AH23" s="68" t="s">
+      <c r="AH23" s="15" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="D3:F4"/>
-    <mergeCell ref="H3:J4"/>
-    <mergeCell ref="L3:N4"/>
-    <mergeCell ref="A8:A14"/>
     <mergeCell ref="D1:R2"/>
     <mergeCell ref="T1:AH2"/>
     <mergeCell ref="T3:V4"/>
@@ -2581,6 +2518,11 @@
     <mergeCell ref="AB3:AD4"/>
     <mergeCell ref="P3:R4"/>
     <mergeCell ref="AF3:AH4"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="D3:F4"/>
+    <mergeCell ref="H3:J4"/>
+    <mergeCell ref="L3:N4"/>
+    <mergeCell ref="A8:A14"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2606,84 +2548,84 @@
   <sheetData>
     <row r="1" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="27"/>
-      <c r="D1" s="64" t="s">
+      <c r="D1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="L1" s="64" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="L1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
     </row>
     <row r="2" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D2" s="64"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="L2" s="64"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
     </row>
     <row r="3" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="D3" s="45" t="s">
+      <c r="D3" s="53" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="45" t="s">
+      <c r="F3" s="53" t="s">
         <v>3</v>
       </c>
       <c r="G3" s="3"/>
-      <c r="H3" s="45" t="s">
+      <c r="H3" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="45" t="s">
+      <c r="J3" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="L3" s="45" t="s">
+      <c r="L3" s="53" t="s">
         <v>2</v>
       </c>
       <c r="M3" s="3"/>
-      <c r="N3" s="45" t="s">
+      <c r="N3" s="53" t="s">
         <v>3</v>
       </c>
       <c r="O3" s="3"/>
-      <c r="P3" s="45" t="s">
+      <c r="P3" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="R3" s="45" t="s">
+      <c r="R3" s="53" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="D4" s="45"/>
+      <c r="D4" s="53"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="45"/>
+      <c r="F4" s="53"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="L4" s="45"/>
+      <c r="H4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="L4" s="53"/>
       <c r="M4" s="3"/>
-      <c r="N4" s="45"/>
+      <c r="N4" s="53"/>
       <c r="O4" s="3"/>
-      <c r="P4" s="45"/>
-      <c r="R4" s="45"/>
+      <c r="P4" s="53"/>
+      <c r="R4" s="53"/>
     </row>
     <row r="5" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="D5" s="4"/>
@@ -2739,7 +2681,7 @@
       <c r="A7" s="4"/>
     </row>
     <row r="8" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="56" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -2776,7 +2718,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="53"/>
+      <c r="A9" s="57"/>
       <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
@@ -2811,7 +2753,7 @@
       </c>
     </row>
     <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="53"/>
+      <c r="A10" s="57"/>
       <c r="B10" s="2" t="s">
         <v>27</v>
       </c>
@@ -2846,7 +2788,7 @@
       </c>
     </row>
     <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="53"/>
+      <c r="A11" s="57"/>
       <c r="B11" s="2"/>
       <c r="D11" s="19"/>
       <c r="E11" s="19"/>
@@ -2863,7 +2805,7 @@
       <c r="R11" s="19"/>
     </row>
     <row r="12" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="53"/>
+      <c r="A12" s="57"/>
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
@@ -2898,7 +2840,7 @@
       </c>
     </row>
     <row r="13" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="53"/>
+      <c r="A13" s="57"/>
       <c r="B13" s="2" t="s">
         <v>42</v>
       </c>
@@ -2933,7 +2875,7 @@
       </c>
     </row>
     <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="53"/>
+      <c r="A14" s="57"/>
       <c r="B14" s="2" t="s">
         <v>48</v>
       </c>
@@ -2968,7 +2910,7 @@
       </c>
     </row>
     <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="53"/>
+      <c r="A15" s="57"/>
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
@@ -2984,7 +2926,7 @@
       <c r="R15" s="24"/>
     </row>
     <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="53"/>
+      <c r="A16" s="57"/>
       <c r="B16" s="12" t="s">
         <v>80</v>
       </c>
@@ -3027,7 +2969,7 @@
       </c>
     </row>
     <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="53"/>
+      <c r="A17" s="57"/>
       <c r="B17" s="12" t="s">
         <v>81</v>
       </c>
@@ -3070,7 +3012,7 @@
       </c>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="53"/>
+      <c r="A18" s="57"/>
       <c r="B18" s="12" t="s">
         <v>82</v>
       </c>
@@ -3115,7 +3057,7 @@
       </c>
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="53"/>
+      <c r="A19" s="57"/>
       <c r="B19" s="12" t="s">
         <v>83</v>
       </c>
@@ -3190,7 +3132,7 @@
       <c r="R21" s="19"/>
     </row>
     <row r="22" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="52" t="s">
+      <c r="A22" s="56" t="s">
         <v>54</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -3227,7 +3169,7 @@
       </c>
     </row>
     <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="53"/>
+      <c r="A23" s="57"/>
       <c r="B23" s="2" t="s">
         <v>22</v>
       </c>
@@ -3262,7 +3204,7 @@
       </c>
     </row>
     <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="53"/>
+      <c r="A24" s="57"/>
       <c r="B24" s="2" t="s">
         <v>27</v>
       </c>
@@ -3297,7 +3239,7 @@
       </c>
     </row>
     <row r="25" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="53"/>
+      <c r="A25" s="57"/>
       <c r="B25" s="2"/>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
@@ -3314,7 +3256,7 @@
       <c r="R25" s="19"/>
     </row>
     <row r="26" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="53"/>
+      <c r="A26" s="57"/>
       <c r="B26" s="2" t="s">
         <v>33</v>
       </c>
@@ -3349,7 +3291,7 @@
       </c>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="53"/>
+      <c r="A27" s="57"/>
       <c r="B27" s="2" t="s">
         <v>42</v>
       </c>
@@ -3384,7 +3326,7 @@
       </c>
     </row>
     <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="53"/>
+      <c r="A28" s="57"/>
       <c r="B28" s="2" t="s">
         <v>48</v>
       </c>
@@ -3419,10 +3361,10 @@
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A29" s="53"/>
+      <c r="A29" s="57"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A30" s="53"/>
+      <c r="A30" s="57"/>
       <c r="B30" s="12" t="s">
         <v>80</v>
       </c>
@@ -3467,7 +3409,7 @@
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A31" s="53"/>
+      <c r="A31" s="57"/>
       <c r="B31" s="12" t="s">
         <v>81</v>
       </c>
@@ -3512,7 +3454,7 @@
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A32" s="53"/>
+      <c r="A32" s="57"/>
       <c r="B32" s="12" t="s">
         <v>82</v>
       </c>
@@ -3557,7 +3499,7 @@
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A33" s="53"/>
+      <c r="A33" s="57"/>
       <c r="B33" s="12" t="s">
         <v>83</v>
       </c>
@@ -3603,16 +3545,16 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A22:A33"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="L3:L4"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="L1:R2"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="D1:J2"/>
     <mergeCell ref="A8:A19"/>
-    <mergeCell ref="A22:A33"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="L3:L4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="P3:P4"/>
   </mergeCells>
@@ -3644,88 +3586,88 @@
   <sheetData>
     <row r="1" spans="1:26" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="27"/>
-      <c r="D1" s="64" t="s">
+      <c r="D1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="L1" s="64" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="L1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
     </row>
     <row r="2" spans="1:26" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D2" s="64"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="L2" s="64"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
     </row>
     <row r="3" spans="1:26" ht="16" x14ac:dyDescent="0.2">
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="73" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="45" t="s">
+      <c r="F3" s="53" t="s">
         <v>3</v>
       </c>
       <c r="G3" s="3"/>
-      <c r="H3" s="45" t="s">
+      <c r="H3" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="63"/>
-      <c r="J3" s="45" t="s">
+      <c r="I3" s="4"/>
+      <c r="J3" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="L3" s="45" t="s">
+      <c r="L3" s="53" t="s">
         <v>2</v>
       </c>
       <c r="M3" s="3"/>
-      <c r="N3" s="45" t="s">
+      <c r="N3" s="53" t="s">
         <v>3</v>
       </c>
       <c r="O3" s="3"/>
-      <c r="P3" s="45" t="s">
+      <c r="P3" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="45" t="s">
+      <c r="Q3" s="4"/>
+      <c r="R3" s="53" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="16" x14ac:dyDescent="0.2">
-      <c r="D4" s="49"/>
+      <c r="D4" s="73"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="45"/>
+      <c r="F4" s="53"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="45"/>
-      <c r="L4" s="45"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="53"/>
+      <c r="L4" s="53"/>
       <c r="M4" s="3"/>
-      <c r="N4" s="45"/>
+      <c r="N4" s="53"/>
       <c r="O4" s="3"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="45"/>
+      <c r="P4" s="53"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="53"/>
     </row>
     <row r="5" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="D5" s="30"/>
@@ -3764,7 +3706,7 @@
       <c r="H6" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="I6" s="63"/>
+      <c r="I6" s="4"/>
       <c r="J6" s="5" t="s">
         <v>79</v>
       </c>
@@ -3779,16 +3721,16 @@
       <c r="P6" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="Q6" s="63"/>
+      <c r="Q6" s="4"/>
       <c r="R6" s="5" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="70" t="s">
         <v>11</v>
       </c>
       <c r="C7">
@@ -3819,13 +3761,13 @@
         <v>81.728998700000005</v>
       </c>
       <c r="Q7" s="36"/>
-      <c r="R7" s="89">
+      <c r="R7" s="49">
         <v>38.036000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="53"/>
-      <c r="B8" s="47"/>
+      <c r="A8" s="57"/>
+      <c r="B8" s="71"/>
       <c r="C8">
         <v>2</v>
       </c>
@@ -3853,13 +3795,13 @@
       <c r="P8">
         <v>84.766424000000001</v>
       </c>
-      <c r="R8" s="82">
+      <c r="R8" s="45">
         <v>36.788200000000003</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="53"/>
-      <c r="B9" s="47"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="71"/>
       <c r="C9">
         <v>3</v>
       </c>
@@ -3887,19 +3829,19 @@
       <c r="P9">
         <v>157.49419499999999</v>
       </c>
-      <c r="R9" s="82">
+      <c r="R9" s="45">
         <v>35.093800000000002</v>
       </c>
-      <c r="W9" s="51" t="s">
+      <c r="W9" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="X9" s="51"/>
-      <c r="Y9" s="51"/>
-      <c r="Z9" s="51"/>
+      <c r="X9" s="69"/>
+      <c r="Y9" s="69"/>
+      <c r="Z9" s="69"/>
     </row>
     <row r="10" spans="1:26" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="53"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="57"/>
+      <c r="B10" s="71"/>
       <c r="C10">
         <v>4</v>
       </c>
@@ -3915,7 +3857,7 @@
         <v>230.29127550000001</v>
       </c>
       <c r="I10" s="33"/>
-      <c r="J10" s="89">
+      <c r="J10" s="49">
         <v>35.101999999999997</v>
       </c>
       <c r="L10">
@@ -3927,7 +3869,7 @@
       <c r="P10">
         <v>78.742313800000005</v>
       </c>
-      <c r="R10" s="82">
+      <c r="R10" s="45">
         <v>34.863700000000001</v>
       </c>
       <c r="X10" s="38"/>
@@ -3937,8 +3879,8 @@
       </c>
     </row>
     <row r="11" spans="1:26" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="53"/>
-      <c r="B11" s="47"/>
+      <c r="A11" s="57"/>
+      <c r="B11" s="71"/>
       <c r="C11">
         <v>5</v>
       </c>
@@ -3966,7 +3908,7 @@
       <c r="P11">
         <v>153.21892299999999</v>
       </c>
-      <c r="R11" s="82">
+      <c r="R11" s="45">
         <v>35.046500000000002</v>
       </c>
       <c r="W11" s="37" t="s">
@@ -3982,8 +3924,8 @@
       </c>
     </row>
     <row r="12" spans="1:26" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="53"/>
-      <c r="B12" s="47"/>
+      <c r="A12" s="57"/>
+      <c r="B12" s="71"/>
       <c r="C12">
         <v>6</v>
       </c>
@@ -3999,7 +3941,7 @@
         <v>73.355889099999999</v>
       </c>
       <c r="I12" s="33"/>
-      <c r="J12" s="89">
+      <c r="J12" s="49">
         <v>34.783999999999999</v>
       </c>
       <c r="L12">
@@ -4011,7 +3953,7 @@
       <c r="P12">
         <v>155.06151919999999</v>
       </c>
-      <c r="R12" s="82">
+      <c r="R12" s="45">
         <v>36.377000000000002</v>
       </c>
       <c r="W12" s="37" t="s">
@@ -4027,8 +3969,8 @@
       </c>
     </row>
     <row r="13" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="53"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="57"/>
+      <c r="B13" s="71"/>
       <c r="C13">
         <v>7</v>
       </c>
@@ -4056,7 +3998,7 @@
       <c r="P13">
         <v>456.90458919999998</v>
       </c>
-      <c r="R13" s="82">
+      <c r="R13" s="45">
         <v>36.636400000000002</v>
       </c>
       <c r="W13" s="37" t="s">
@@ -4072,8 +4014,8 @@
       </c>
     </row>
     <row r="14" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="53"/>
-      <c r="B14" s="47"/>
+      <c r="A14" s="57"/>
+      <c r="B14" s="71"/>
       <c r="C14">
         <v>8</v>
       </c>
@@ -4101,7 +4043,7 @@
       <c r="P14">
         <v>81.961152400000003</v>
       </c>
-      <c r="R14" s="82">
+      <c r="R14" s="45">
         <v>36.623100000000001</v>
       </c>
       <c r="W14" s="37" t="s">
@@ -4117,8 +4059,8 @@
       </c>
     </row>
     <row r="15" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="53"/>
-      <c r="B15" s="47"/>
+      <c r="A15" s="57"/>
+      <c r="B15" s="71"/>
       <c r="C15">
         <v>9</v>
       </c>
@@ -4146,13 +4088,13 @@
       <c r="P15">
         <v>159.94233370000001</v>
       </c>
-      <c r="R15" s="82">
+      <c r="R15" s="45">
         <v>36.220799999999997</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="53"/>
-      <c r="B16" s="48"/>
+      <c r="A16" s="57"/>
+      <c r="B16" s="72"/>
       <c r="C16">
         <v>10</v>
       </c>
@@ -4179,13 +4121,13 @@
       <c r="P16">
         <v>77.275726899999995</v>
       </c>
-      <c r="R16" s="82">
+      <c r="R16" s="45">
         <v>35.075099999999999</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="53"/>
-      <c r="B17" s="46" t="s">
+      <c r="A17" s="57"/>
+      <c r="B17" s="70" t="s">
         <v>86</v>
       </c>
       <c r="C17">
@@ -4215,13 +4157,13 @@
       <c r="P17">
         <v>72.4576469</v>
       </c>
-      <c r="R17" s="82">
+      <c r="R17" s="45">
         <v>35.995699999999999</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="53"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="57"/>
+      <c r="B18" s="71"/>
       <c r="C18">
         <v>2</v>
       </c>
@@ -4249,13 +4191,13 @@
       <c r="P18">
         <v>73.037465600000004</v>
       </c>
-      <c r="R18" s="82">
+      <c r="R18" s="45">
         <v>34.117800000000003</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="53"/>
-      <c r="B19" s="47"/>
+      <c r="A19" s="57"/>
+      <c r="B19" s="71"/>
       <c r="C19">
         <v>3</v>
       </c>
@@ -4283,13 +4225,13 @@
       <c r="P19">
         <v>75.679750100000007</v>
       </c>
-      <c r="R19" s="82">
+      <c r="R19" s="45">
         <v>34.372500000000002</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="53"/>
-      <c r="B20" s="47"/>
+      <c r="A20" s="57"/>
+      <c r="B20" s="71"/>
       <c r="C20">
         <v>4</v>
       </c>
@@ -4317,13 +4259,13 @@
       <c r="P20">
         <v>69.004712999999995</v>
       </c>
-      <c r="R20" s="82">
+      <c r="R20" s="45">
         <v>34.101599999999998</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="53"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="57"/>
+      <c r="B21" s="71"/>
       <c r="C21">
         <v>5</v>
       </c>
@@ -4351,13 +4293,13 @@
       <c r="P21">
         <v>64.653414799999993</v>
       </c>
-      <c r="R21" s="82">
+      <c r="R21" s="45">
         <v>35.322299999999998</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="53"/>
-      <c r="B22" s="47"/>
+      <c r="A22" s="57"/>
+      <c r="B22" s="71"/>
       <c r="C22">
         <v>6</v>
       </c>
@@ -4385,13 +4327,13 @@
       <c r="P22">
         <v>64.707670100000001</v>
       </c>
-      <c r="R22" s="82">
+      <c r="R22" s="45">
         <v>34.085500000000003</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="53"/>
-      <c r="B23" s="47"/>
+      <c r="A23" s="57"/>
+      <c r="B23" s="71"/>
       <c r="C23">
         <v>7</v>
       </c>
@@ -4419,13 +4361,13 @@
       <c r="P23">
         <v>66.928739100000001</v>
       </c>
-      <c r="R23" s="82">
+      <c r="R23" s="45">
         <v>34.142600000000002</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="53"/>
-      <c r="B24" s="47"/>
+      <c r="A24" s="57"/>
+      <c r="B24" s="71"/>
       <c r="C24">
         <v>8</v>
       </c>
@@ -4453,13 +4395,13 @@
       <c r="P24">
         <v>85.198224800000006</v>
       </c>
-      <c r="R24" s="82">
+      <c r="R24" s="45">
         <v>34.6751</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="53"/>
-      <c r="B25" s="47"/>
+      <c r="A25" s="57"/>
+      <c r="B25" s="71"/>
       <c r="C25">
         <v>9</v>
       </c>
@@ -4487,13 +4429,13 @@
       <c r="P25">
         <v>86.575239600000003</v>
       </c>
-      <c r="R25" s="82">
+      <c r="R25" s="45">
         <v>33.859900000000003</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="53"/>
-      <c r="B26" s="48"/>
+      <c r="A26" s="57"/>
+      <c r="B26" s="72"/>
       <c r="C26">
         <v>10</v>
       </c>
@@ -4520,13 +4462,13 @@
       <c r="P26">
         <v>75.496478600000003</v>
       </c>
-      <c r="R26" s="82">
+      <c r="R26" s="45">
         <v>34.288499999999999</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" s="53"/>
-      <c r="B27" s="46" t="s">
+      <c r="A27" s="57"/>
+      <c r="B27" s="70" t="s">
         <v>27</v>
       </c>
       <c r="C27">
@@ -4556,13 +4498,13 @@
       <c r="P27">
         <v>75.413589000000002</v>
       </c>
-      <c r="R27" s="82">
+      <c r="R27" s="45">
         <v>36.275500000000001</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="53"/>
-      <c r="B28" s="47"/>
+      <c r="A28" s="57"/>
+      <c r="B28" s="71"/>
       <c r="C28">
         <v>2</v>
       </c>
@@ -4590,13 +4532,13 @@
       <c r="P28">
         <v>77.701590100000004</v>
       </c>
-      <c r="R28" s="82">
+      <c r="R28" s="45">
         <v>34.380499999999998</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="53"/>
-      <c r="B29" s="47"/>
+      <c r="A29" s="57"/>
+      <c r="B29" s="71"/>
       <c r="C29">
         <v>3</v>
       </c>
@@ -4624,13 +4566,13 @@
       <c r="P29">
         <v>78.494008300000004</v>
       </c>
-      <c r="R29" s="82">
+      <c r="R29" s="45">
         <v>35.154899999999998</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="53"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="57"/>
+      <c r="B30" s="71"/>
       <c r="C30">
         <v>4</v>
       </c>
@@ -4658,13 +4600,13 @@
       <c r="P30">
         <v>73.773346900000007</v>
       </c>
-      <c r="R30" s="82">
+      <c r="R30" s="45">
         <v>35.206299999999999</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A31" s="53"/>
-      <c r="B31" s="47"/>
+      <c r="A31" s="57"/>
+      <c r="B31" s="71"/>
       <c r="C31">
         <v>5</v>
       </c>
@@ -4692,13 +4634,13 @@
       <c r="P31">
         <v>86.556363700000006</v>
       </c>
-      <c r="R31" s="82">
+      <c r="R31" s="45">
         <v>34.072400000000002</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="53"/>
-      <c r="B32" s="47"/>
+      <c r="A32" s="57"/>
+      <c r="B32" s="71"/>
       <c r="C32">
         <v>6</v>
       </c>
@@ -4726,13 +4668,13 @@
       <c r="P32">
         <v>81.386483100000007</v>
       </c>
-      <c r="R32" s="82">
+      <c r="R32" s="45">
         <v>34.356200000000001</v>
       </c>
     </row>
     <row r="33" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="53"/>
-      <c r="B33" s="47"/>
+      <c r="A33" s="57"/>
+      <c r="B33" s="71"/>
       <c r="C33">
         <v>7</v>
       </c>
@@ -4760,13 +4702,13 @@
       <c r="P33">
         <v>88.930410199999997</v>
       </c>
-      <c r="R33" s="82">
+      <c r="R33" s="45">
         <v>35.070900000000002</v>
       </c>
     </row>
     <row r="34" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="53"/>
-      <c r="B34" s="47"/>
+      <c r="A34" s="57"/>
+      <c r="B34" s="71"/>
       <c r="C34">
         <v>8</v>
       </c>
@@ -4794,13 +4736,13 @@
       <c r="P34">
         <v>81.324767699999995</v>
       </c>
-      <c r="R34" s="82">
+      <c r="R34" s="45">
         <v>34.187899999999999</v>
       </c>
     </row>
     <row r="35" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="53"/>
-      <c r="B35" s="47"/>
+      <c r="A35" s="57"/>
+      <c r="B35" s="71"/>
       <c r="C35">
         <v>9</v>
       </c>
@@ -4828,13 +4770,13 @@
       <c r="P35">
         <v>84.404220199999997</v>
       </c>
-      <c r="R35" s="82">
+      <c r="R35" s="45">
         <v>35.190100000000001</v>
       </c>
     </row>
     <row r="36" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="53"/>
-      <c r="B36" s="48"/>
+      <c r="A36" s="57"/>
+      <c r="B36" s="72"/>
       <c r="C36">
         <v>10</v>
       </c>
@@ -4861,36 +4803,36 @@
       <c r="P36">
         <v>78.9069042</v>
       </c>
-      <c r="R36" s="82">
+      <c r="R36" s="45">
         <v>35.302399999999999</v>
       </c>
-      <c r="W36" s="51" t="s">
+      <c r="W36" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="X36" s="51"/>
-      <c r="Y36" s="51"/>
-      <c r="Z36" s="51"/>
-      <c r="AB36" s="51" t="s">
+      <c r="X36" s="69"/>
+      <c r="Y36" s="69"/>
+      <c r="Z36" s="69"/>
+      <c r="AB36" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="AC36" s="51"/>
-      <c r="AD36" s="51"/>
-      <c r="AE36" s="51"/>
-      <c r="AG36" s="50" t="s">
+      <c r="AC36" s="69"/>
+      <c r="AD36" s="69"/>
+      <c r="AE36" s="69"/>
+      <c r="AG36" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="AH36" s="50"/>
-      <c r="AI36" s="50"/>
-      <c r="AJ36" s="50"/>
-      <c r="AL36" s="50" t="s">
+      <c r="AH36" s="68"/>
+      <c r="AI36" s="68"/>
+      <c r="AJ36" s="68"/>
+      <c r="AL36" s="68" t="s">
         <v>114</v>
       </c>
-      <c r="AM36" s="50"/>
-      <c r="AN36" s="50"/>
-      <c r="AO36" s="50"/>
+      <c r="AM36" s="68"/>
+      <c r="AN36" s="68"/>
+      <c r="AO36" s="68"/>
     </row>
     <row r="37" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="53"/>
+      <c r="A37" s="57"/>
       <c r="F37" s="31"/>
       <c r="G37" s="31"/>
       <c r="H37" s="31"/>
@@ -4920,8 +4862,8 @@
       </c>
     </row>
     <row r="38" spans="1:41" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="53"/>
-      <c r="B38" s="46" t="s">
+      <c r="A38" s="57"/>
+      <c r="B38" s="70" t="s">
         <v>33</v>
       </c>
       <c r="C38">
@@ -4951,7 +4893,7 @@
       <c r="P38">
         <v>66.911195300000003</v>
       </c>
-      <c r="R38" s="81">
+      <c r="R38" s="44">
         <v>34.2059</v>
       </c>
       <c r="W38" s="37" t="s">
@@ -5003,8 +4945,8 @@
       </c>
     </row>
     <row r="39" spans="1:41" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="53"/>
-      <c r="B39" s="47"/>
+      <c r="A39" s="57"/>
+      <c r="B39" s="71"/>
       <c r="C39">
         <v>2</v>
       </c>
@@ -5032,7 +4974,7 @@
       <c r="P39">
         <v>64.378168500000001</v>
       </c>
-      <c r="R39" s="81">
+      <c r="R39" s="44">
         <v>32.802799999999998</v>
       </c>
       <c r="W39" s="37" t="s">
@@ -5084,8 +5026,8 @@
       </c>
     </row>
     <row r="40" spans="1:41" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="53"/>
-      <c r="B40" s="47"/>
+      <c r="A40" s="57"/>
+      <c r="B40" s="71"/>
       <c r="C40">
         <v>3</v>
       </c>
@@ -5113,7 +5055,7 @@
       <c r="P40">
         <v>66.806464399999996</v>
       </c>
-      <c r="R40" s="81">
+      <c r="R40" s="44">
         <v>32.568199999999997</v>
       </c>
       <c r="W40" s="37" t="s">
@@ -5165,8 +5107,8 @@
       </c>
     </row>
     <row r="41" spans="1:41" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="53"/>
-      <c r="B41" s="47"/>
+      <c r="A41" s="57"/>
+      <c r="B41" s="71"/>
       <c r="C41">
         <v>4</v>
       </c>
@@ -5182,7 +5124,7 @@
         <v>248.90476090000001</v>
       </c>
       <c r="I41" s="33"/>
-      <c r="J41" s="89">
+      <c r="J41" s="49">
         <v>32.491</v>
       </c>
       <c r="L41">
@@ -5194,7 +5136,7 @@
       <c r="P41">
         <v>383.47915019999999</v>
       </c>
-      <c r="R41" s="81">
+      <c r="R41" s="44">
         <v>33.292000000000002</v>
       </c>
       <c r="W41" s="37" t="s">
@@ -5246,8 +5188,8 @@
       </c>
     </row>
     <row r="42" spans="1:41" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="53"/>
-      <c r="B42" s="47"/>
+      <c r="A42" s="57"/>
+      <c r="B42" s="71"/>
       <c r="C42">
         <v>5</v>
       </c>
@@ -5275,13 +5217,13 @@
       <c r="P42">
         <v>62.552345799999998</v>
       </c>
-      <c r="R42" s="81">
+      <c r="R42" s="44">
         <v>33.485799999999998</v>
       </c>
     </row>
     <row r="43" spans="1:41" ht="16" x14ac:dyDescent="0.2">
-      <c r="A43" s="53"/>
-      <c r="B43" s="47"/>
+      <c r="A43" s="57"/>
+      <c r="B43" s="71"/>
       <c r="C43">
         <v>6</v>
       </c>
@@ -5309,13 +5251,13 @@
       <c r="P43">
         <v>66.208508899999998</v>
       </c>
-      <c r="R43" s="81">
+      <c r="R43" s="44">
         <v>32.621699999999997</v>
       </c>
     </row>
     <row r="44" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="53"/>
-      <c r="B44" s="47"/>
+      <c r="A44" s="57"/>
+      <c r="B44" s="71"/>
       <c r="C44">
         <v>7</v>
       </c>
@@ -5343,35 +5285,35 @@
       <c r="P44">
         <v>132.51080440000001</v>
       </c>
-      <c r="R44" s="81">
+      <c r="R44" s="44">
         <v>32.714300000000001</v>
       </c>
       <c r="W44" s="37"/>
       <c r="X44" s="37"/>
       <c r="Y44" s="37"/>
       <c r="Z44" s="37"/>
-      <c r="AB44" s="51" t="s">
+      <c r="AB44" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="AC44" s="51"/>
-      <c r="AD44" s="51"/>
-      <c r="AE44" s="51"/>
-      <c r="AG44" s="50" t="s">
+      <c r="AC44" s="69"/>
+      <c r="AD44" s="69"/>
+      <c r="AE44" s="69"/>
+      <c r="AG44" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="AH44" s="50"/>
-      <c r="AI44" s="50"/>
-      <c r="AJ44" s="50"/>
-      <c r="AL44" s="50" t="s">
+      <c r="AH44" s="68"/>
+      <c r="AI44" s="68"/>
+      <c r="AJ44" s="68"/>
+      <c r="AL44" s="68" t="s">
         <v>113</v>
       </c>
-      <c r="AM44" s="50"/>
-      <c r="AN44" s="50"/>
-      <c r="AO44" s="50"/>
+      <c r="AM44" s="68"/>
+      <c r="AN44" s="68"/>
+      <c r="AO44" s="68"/>
     </row>
     <row r="45" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="53"/>
-      <c r="B45" s="47"/>
+      <c r="A45" s="57"/>
+      <c r="B45" s="71"/>
       <c r="C45">
         <v>8</v>
       </c>
@@ -5399,7 +5341,7 @@
       <c r="P45">
         <v>67.6577901</v>
       </c>
-      <c r="R45" s="81">
+      <c r="R45" s="44">
         <v>33.65</v>
       </c>
       <c r="X45" s="38"/>
@@ -5424,8 +5366,8 @@
       </c>
     </row>
     <row r="46" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="53"/>
-      <c r="B46" s="47"/>
+      <c r="A46" s="57"/>
+      <c r="B46" s="71"/>
       <c r="C46">
         <v>9</v>
       </c>
@@ -5453,7 +5395,7 @@
       <c r="P46">
         <v>65.501620900000006</v>
       </c>
-      <c r="R46" s="81">
+      <c r="R46" s="44">
         <v>33.218000000000004</v>
       </c>
       <c r="W46" s="37"/>
@@ -5496,8 +5438,8 @@
       </c>
     </row>
     <row r="47" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="53"/>
-      <c r="B47" s="48"/>
+      <c r="A47" s="57"/>
+      <c r="B47" s="72"/>
       <c r="C47">
         <v>10</v>
       </c>
@@ -5524,7 +5466,7 @@
       <c r="P47">
         <v>65.377549599999995</v>
       </c>
-      <c r="R47" s="81">
+      <c r="R47" s="44">
         <v>32.382199999999997</v>
       </c>
       <c r="W47" s="37"/>
@@ -5567,8 +5509,8 @@
       </c>
     </row>
     <row r="48" spans="1:41" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="53"/>
-      <c r="B48" s="46" t="s">
+      <c r="A48" s="57"/>
+      <c r="B48" s="70" t="s">
         <v>42</v>
       </c>
       <c r="C48">
@@ -5598,7 +5540,7 @@
       <c r="P48">
         <v>75.916192300000006</v>
       </c>
-      <c r="R48" s="81">
+      <c r="R48" s="44">
         <v>34.949199999999998</v>
       </c>
       <c r="W48" s="37"/>
@@ -5641,8 +5583,8 @@
       </c>
     </row>
     <row r="49" spans="1:41" ht="16" x14ac:dyDescent="0.2">
-      <c r="A49" s="53"/>
-      <c r="B49" s="47"/>
+      <c r="A49" s="57"/>
+      <c r="B49" s="71"/>
       <c r="C49">
         <v>2</v>
       </c>
@@ -5670,7 +5612,7 @@
       <c r="P49">
         <v>68.917741399999997</v>
       </c>
-      <c r="R49" s="81">
+      <c r="R49" s="44">
         <v>32.847999999999999</v>
       </c>
       <c r="W49" s="37"/>
@@ -5713,8 +5655,8 @@
       </c>
     </row>
     <row r="50" spans="1:41" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="53"/>
-      <c r="B50" s="47"/>
+      <c r="A50" s="57"/>
+      <c r="B50" s="71"/>
       <c r="C50">
         <v>3</v>
       </c>
@@ -5742,13 +5684,13 @@
       <c r="P50">
         <v>66.262496600000006</v>
       </c>
-      <c r="R50" s="81">
+      <c r="R50" s="44">
         <v>32.967399999999998</v>
       </c>
     </row>
     <row r="51" spans="1:41" ht="16" x14ac:dyDescent="0.2">
-      <c r="A51" s="53"/>
-      <c r="B51" s="47"/>
+      <c r="A51" s="57"/>
+      <c r="B51" s="71"/>
       <c r="C51">
         <v>4</v>
       </c>
@@ -5776,13 +5718,13 @@
       <c r="P51">
         <v>65.344129800000005</v>
       </c>
-      <c r="R51" s="81">
+      <c r="R51" s="44">
         <v>33.582599999999999</v>
       </c>
     </row>
     <row r="52" spans="1:41" ht="16" x14ac:dyDescent="0.2">
-      <c r="A52" s="53"/>
-      <c r="B52" s="47"/>
+      <c r="A52" s="57"/>
+      <c r="B52" s="71"/>
       <c r="C52">
         <v>5</v>
       </c>
@@ -5810,13 +5752,13 @@
       <c r="P52">
         <v>73.091260399999996</v>
       </c>
-      <c r="R52" s="81">
+      <c r="R52" s="44">
         <v>32.345500000000001</v>
       </c>
     </row>
     <row r="53" spans="1:41" ht="16" x14ac:dyDescent="0.2">
-      <c r="A53" s="53"/>
-      <c r="B53" s="47"/>
+      <c r="A53" s="57"/>
+      <c r="B53" s="71"/>
       <c r="C53">
         <v>6</v>
       </c>
@@ -5832,7 +5774,7 @@
         <v>65.577701300000001</v>
       </c>
       <c r="I53" s="33"/>
-      <c r="J53" s="89">
+      <c r="J53" s="49">
         <v>32.994</v>
       </c>
       <c r="L53">
@@ -5844,13 +5786,13 @@
       <c r="P53">
         <v>69.363162599999995</v>
       </c>
-      <c r="R53" s="81">
+      <c r="R53" s="44">
         <v>32.598399999999998</v>
       </c>
     </row>
     <row r="54" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="53"/>
-      <c r="B54" s="47"/>
+      <c r="A54" s="57"/>
+      <c r="B54" s="71"/>
       <c r="C54">
         <v>7</v>
       </c>
@@ -5878,25 +5820,25 @@
       <c r="P54">
         <v>66.126271200000005</v>
       </c>
-      <c r="R54" s="81">
+      <c r="R54" s="44">
         <v>32.393599999999999</v>
       </c>
-      <c r="W54" s="51" t="s">
+      <c r="W54" s="69" t="s">
         <v>100</v>
       </c>
-      <c r="X54" s="51"/>
-      <c r="Y54" s="51"/>
-      <c r="Z54" s="51"/>
-      <c r="AB54" s="51" t="s">
+      <c r="X54" s="69"/>
+      <c r="Y54" s="69"/>
+      <c r="Z54" s="69"/>
+      <c r="AB54" s="69" t="s">
         <v>101</v>
       </c>
-      <c r="AC54" s="51"/>
-      <c r="AD54" s="51"/>
-      <c r="AE54" s="51"/>
+      <c r="AC54" s="69"/>
+      <c r="AD54" s="69"/>
+      <c r="AE54" s="69"/>
     </row>
     <row r="55" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="53"/>
-      <c r="B55" s="47"/>
+      <c r="A55" s="57"/>
+      <c r="B55" s="71"/>
       <c r="C55">
         <v>8</v>
       </c>
@@ -5924,7 +5866,7 @@
       <c r="P55">
         <v>64.695870499999998</v>
       </c>
-      <c r="R55" s="81">
+      <c r="R55" s="44">
         <v>33.694099999999999</v>
       </c>
       <c r="X55" s="38"/>
@@ -5939,8 +5881,8 @@
       </c>
     </row>
     <row r="56" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="53"/>
-      <c r="B56" s="47"/>
+      <c r="A56" s="57"/>
+      <c r="B56" s="71"/>
       <c r="C56">
         <v>9</v>
       </c>
@@ -5968,7 +5910,7 @@
       <c r="P56">
         <v>66.252286600000005</v>
       </c>
-      <c r="R56" s="81">
+      <c r="R56" s="44">
         <v>32.419600000000003</v>
       </c>
       <c r="W56" s="37" t="s">
@@ -5996,8 +5938,8 @@
       </c>
     </row>
     <row r="57" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="53"/>
-      <c r="B57" s="48"/>
+      <c r="A57" s="57"/>
+      <c r="B57" s="72"/>
       <c r="C57">
         <v>10</v>
       </c>
@@ -6024,7 +5966,7 @@
       <c r="P57">
         <v>65.3028932</v>
       </c>
-      <c r="R57" s="81">
+      <c r="R57" s="44">
         <v>32.625399999999999</v>
       </c>
       <c r="W57" s="37" t="s">
@@ -6052,8 +5994,8 @@
       </c>
     </row>
     <row r="58" spans="1:41" ht="16" x14ac:dyDescent="0.2">
-      <c r="A58" s="53"/>
-      <c r="B58" s="46" t="s">
+      <c r="A58" s="57"/>
+      <c r="B58" s="70" t="s">
         <v>48</v>
       </c>
       <c r="C58">
@@ -6071,7 +6013,7 @@
         <v>77.070805199999995</v>
       </c>
       <c r="I58" s="33"/>
-      <c r="J58" s="81">
+      <c r="J58" s="44">
         <v>37.537199999999999</v>
       </c>
       <c r="L58">
@@ -6083,7 +6025,7 @@
       <c r="P58">
         <v>95.839778699999997</v>
       </c>
-      <c r="R58" s="81">
+      <c r="R58" s="44">
         <v>36.006500000000003</v>
       </c>
       <c r="W58" s="37" t="s">
@@ -6111,8 +6053,8 @@
       </c>
     </row>
     <row r="59" spans="1:41" ht="16" x14ac:dyDescent="0.2">
-      <c r="A59" s="53"/>
-      <c r="B59" s="47"/>
+      <c r="A59" s="57"/>
+      <c r="B59" s="71"/>
       <c r="C59">
         <v>2</v>
       </c>
@@ -6140,7 +6082,7 @@
       <c r="P59">
         <v>110.28815590000001</v>
       </c>
-      <c r="R59" s="81">
+      <c r="R59" s="44">
         <v>32.920099999999998</v>
       </c>
       <c r="W59" s="37" t="s">
@@ -6168,8 +6110,8 @@
       </c>
     </row>
     <row r="60" spans="1:41" ht="16" x14ac:dyDescent="0.2">
-      <c r="A60" s="53"/>
-      <c r="B60" s="47"/>
+      <c r="A60" s="57"/>
+      <c r="B60" s="71"/>
       <c r="C60">
         <v>3</v>
       </c>
@@ -6197,13 +6139,13 @@
       <c r="P60">
         <v>116.1841663</v>
       </c>
-      <c r="R60" s="81">
+      <c r="R60" s="44">
         <v>32.770499999999998</v>
       </c>
     </row>
     <row r="61" spans="1:41" ht="16" x14ac:dyDescent="0.2">
-      <c r="A61" s="53"/>
-      <c r="B61" s="47"/>
+      <c r="A61" s="57"/>
+      <c r="B61" s="71"/>
       <c r="C61">
         <v>4</v>
       </c>
@@ -6231,13 +6173,13 @@
       <c r="P61">
         <v>110.5701389</v>
       </c>
-      <c r="R61" s="81">
+      <c r="R61" s="44">
         <v>33.440100000000001</v>
       </c>
     </row>
     <row r="62" spans="1:41" ht="16" x14ac:dyDescent="0.2">
-      <c r="A62" s="53"/>
-      <c r="B62" s="47"/>
+      <c r="A62" s="57"/>
+      <c r="B62" s="71"/>
       <c r="C62">
         <v>5</v>
       </c>
@@ -6265,13 +6207,13 @@
       <c r="P62">
         <v>112.1447738</v>
       </c>
-      <c r="R62" s="81">
+      <c r="R62" s="44">
         <v>32.965400000000002</v>
       </c>
     </row>
     <row r="63" spans="1:41" ht="16" x14ac:dyDescent="0.2">
-      <c r="A63" s="53"/>
-      <c r="B63" s="47"/>
+      <c r="A63" s="57"/>
+      <c r="B63" s="71"/>
       <c r="C63">
         <v>6</v>
       </c>
@@ -6299,13 +6241,13 @@
       <c r="P63">
         <v>105.71322069999999</v>
       </c>
-      <c r="R63" s="81">
+      <c r="R63" s="44">
         <v>32.902099999999997</v>
       </c>
     </row>
     <row r="64" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="53"/>
-      <c r="B64" s="47"/>
+      <c r="A64" s="57"/>
+      <c r="B64" s="71"/>
       <c r="C64">
         <v>7</v>
       </c>
@@ -6333,13 +6275,13 @@
       <c r="P64">
         <v>103.50280239999999</v>
       </c>
-      <c r="R64" s="81">
+      <c r="R64" s="44">
         <v>33.018300000000004</v>
       </c>
     </row>
     <row r="65" spans="1:30" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="53"/>
-      <c r="B65" s="47"/>
+      <c r="A65" s="57"/>
+      <c r="B65" s="71"/>
       <c r="C65">
         <v>8</v>
       </c>
@@ -6367,23 +6309,23 @@
       <c r="P65">
         <v>89.825549699999996</v>
       </c>
-      <c r="R65" s="81">
+      <c r="R65" s="44">
         <v>34.323099999999997</v>
       </c>
-      <c r="W65" s="51" t="s">
+      <c r="W65" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="X65" s="51"/>
-      <c r="Y65" s="51"/>
-      <c r="Z65" s="51"/>
-      <c r="AA65" s="51"/>
-      <c r="AB65" s="51"/>
-      <c r="AC65" s="51"/>
-      <c r="AD65" s="51"/>
+      <c r="X65" s="69"/>
+      <c r="Y65" s="69"/>
+      <c r="Z65" s="69"/>
+      <c r="AA65" s="69"/>
+      <c r="AB65" s="69"/>
+      <c r="AC65" s="69"/>
+      <c r="AD65" s="69"/>
     </row>
     <row r="66" spans="1:30" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="53"/>
-      <c r="B66" s="47"/>
+      <c r="A66" s="57"/>
+      <c r="B66" s="71"/>
       <c r="C66">
         <v>9</v>
       </c>
@@ -6399,7 +6341,7 @@
         <v>62.867806299999998</v>
       </c>
       <c r="I66" s="33"/>
-      <c r="J66" s="82">
+      <c r="J66" s="45">
         <v>34.238999999999997</v>
       </c>
       <c r="L66">
@@ -6411,7 +6353,7 @@
       <c r="P66">
         <v>77.588893900000002</v>
       </c>
-      <c r="R66" s="81">
+      <c r="R66" s="44">
         <v>33.968899999999998</v>
       </c>
       <c r="X66" s="38" t="s">
@@ -6437,8 +6379,8 @@
       </c>
     </row>
     <row r="67" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="53"/>
-      <c r="B67" s="48"/>
+      <c r="A67" s="57"/>
+      <c r="B67" s="72"/>
       <c r="C67">
         <v>10</v>
       </c>
@@ -6465,7 +6407,7 @@
       <c r="P67">
         <v>79.4372781</v>
       </c>
-      <c r="R67" s="81">
+      <c r="R67" s="44">
         <v>33.910600000000002</v>
       </c>
       <c r="W67" s="37" t="s">
@@ -6739,7 +6681,7 @@
         <v>1927.3264309999997</v>
       </c>
       <c r="Y71" s="10">
-        <f t="shared" ref="Y71:AB71" si="19">Y70+1.5*(Y70-Y69)</f>
+        <f t="shared" ref="Y71:Z71" si="19">Y70+1.5*(Y70-Y69)</f>
         <v>815.54601803750006</v>
       </c>
       <c r="Z71" s="10">
@@ -6815,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="Y72" s="10">
-        <f t="shared" ref="Y72:AB72" si="23">IF(Y69-1.5*(Y70-Y69)&lt;0,0,Y69-1.5*(Y70-Y69))</f>
+        <f t="shared" ref="Y72" si="23">IF(Y69-1.5*(Y70-Y69)&lt;0,0,Y69-1.5*(Y70-Y69))</f>
         <v>0</v>
       </c>
       <c r="Z72" s="10">
@@ -6843,10 +6785,10 @@
       <c r="A73" s="4"/>
     </row>
     <row r="74" spans="1:30" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="52" t="s">
+      <c r="A74" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="B74" s="46" t="s">
+      <c r="B74" s="70" t="s">
         <v>11</v>
       </c>
       <c r="C74">
@@ -6881,8 +6823,8 @@
       </c>
     </row>
     <row r="75" spans="1:30" ht="16" x14ac:dyDescent="0.2">
-      <c r="A75" s="53"/>
-      <c r="B75" s="47"/>
+      <c r="A75" s="57"/>
+      <c r="B75" s="71"/>
       <c r="C75">
         <v>2</v>
       </c>
@@ -6915,8 +6857,8 @@
       </c>
     </row>
     <row r="76" spans="1:30" ht="16" x14ac:dyDescent="0.2">
-      <c r="A76" s="53"/>
-      <c r="B76" s="47"/>
+      <c r="A76" s="57"/>
+      <c r="B76" s="71"/>
       <c r="C76">
         <v>3</v>
       </c>
@@ -6949,8 +6891,8 @@
       </c>
     </row>
     <row r="77" spans="1:30" ht="16" x14ac:dyDescent="0.2">
-      <c r="A77" s="53"/>
-      <c r="B77" s="47"/>
+      <c r="A77" s="57"/>
+      <c r="B77" s="71"/>
       <c r="C77">
         <v>4</v>
       </c>
@@ -6966,7 +6908,7 @@
         <v>275.11039959999999</v>
       </c>
       <c r="I77" s="33"/>
-      <c r="J77" s="89">
+      <c r="J77" s="49">
         <v>353.98700000000002</v>
       </c>
       <c r="L77" s="33" t="s">
@@ -6983,8 +6925,8 @@
       </c>
     </row>
     <row r="78" spans="1:30" ht="16" x14ac:dyDescent="0.2">
-      <c r="A78" s="53"/>
-      <c r="B78" s="47"/>
+      <c r="A78" s="57"/>
+      <c r="B78" s="71"/>
       <c r="C78">
         <v>5</v>
       </c>
@@ -7012,13 +6954,13 @@
       <c r="P78">
         <v>66.381577199999995</v>
       </c>
-      <c r="R78" s="82">
+      <c r="R78" s="45">
         <v>50.402000000000001</v>
       </c>
     </row>
     <row r="79" spans="1:30" ht="16" x14ac:dyDescent="0.2">
-      <c r="A79" s="53"/>
-      <c r="B79" s="47"/>
+      <c r="A79" s="57"/>
+      <c r="B79" s="71"/>
       <c r="C79">
         <v>6</v>
       </c>
@@ -7051,8 +6993,8 @@
       </c>
     </row>
     <row r="80" spans="1:30" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="53"/>
-      <c r="B80" s="47"/>
+      <c r="A80" s="57"/>
+      <c r="B80" s="71"/>
       <c r="C80">
         <v>7</v>
       </c>
@@ -7085,8 +7027,8 @@
       </c>
     </row>
     <row r="81" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="53"/>
-      <c r="B81" s="47"/>
+      <c r="A81" s="57"/>
+      <c r="B81" s="71"/>
       <c r="C81">
         <v>8</v>
       </c>
@@ -7119,8 +7061,8 @@
       </c>
     </row>
     <row r="82" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="53"/>
-      <c r="B82" s="47"/>
+      <c r="A82" s="57"/>
+      <c r="B82" s="71"/>
       <c r="C82">
         <v>9</v>
       </c>
@@ -7153,8 +7095,8 @@
       </c>
     </row>
     <row r="83" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="53"/>
-      <c r="B83" s="48"/>
+      <c r="A83" s="57"/>
+      <c r="B83" s="72"/>
       <c r="C83">
         <v>10</v>
       </c>
@@ -7186,8 +7128,8 @@
       </c>
     </row>
     <row r="84" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A84" s="53"/>
-      <c r="B84" s="46" t="s">
+      <c r="A84" s="57"/>
+      <c r="B84" s="70" t="s">
         <v>86</v>
       </c>
       <c r="C84">
@@ -7222,8 +7164,8 @@
       </c>
     </row>
     <row r="85" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A85" s="53"/>
-      <c r="B85" s="47"/>
+      <c r="A85" s="57"/>
+      <c r="B85" s="71"/>
       <c r="C85">
         <v>2</v>
       </c>
@@ -7256,8 +7198,8 @@
       </c>
     </row>
     <row r="86" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A86" s="53"/>
-      <c r="B86" s="47"/>
+      <c r="A86" s="57"/>
+      <c r="B86" s="71"/>
       <c r="C86">
         <v>3</v>
       </c>
@@ -7290,8 +7232,8 @@
       </c>
     </row>
     <row r="87" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A87" s="53"/>
-      <c r="B87" s="47"/>
+      <c r="A87" s="57"/>
+      <c r="B87" s="71"/>
       <c r="C87">
         <v>4</v>
       </c>
@@ -7324,8 +7266,8 @@
       </c>
     </row>
     <row r="88" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A88" s="53"/>
-      <c r="B88" s="47"/>
+      <c r="A88" s="57"/>
+      <c r="B88" s="71"/>
       <c r="C88">
         <v>5</v>
       </c>
@@ -7358,8 +7300,8 @@
       </c>
     </row>
     <row r="89" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A89" s="53"/>
-      <c r="B89" s="47"/>
+      <c r="A89" s="57"/>
+      <c r="B89" s="71"/>
       <c r="C89">
         <v>6</v>
       </c>
@@ -7375,7 +7317,7 @@
         <v>73.746508800000001</v>
       </c>
       <c r="I89" s="33"/>
-      <c r="J89" s="89">
+      <c r="J89" s="49">
         <v>50.674999999999997</v>
       </c>
       <c r="L89" s="33" t="s">
@@ -7392,8 +7334,8 @@
       </c>
     </row>
     <row r="90" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="53"/>
-      <c r="B90" s="47"/>
+      <c r="A90" s="57"/>
+      <c r="B90" s="71"/>
       <c r="C90">
         <v>7</v>
       </c>
@@ -7426,8 +7368,8 @@
       </c>
     </row>
     <row r="91" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="53"/>
-      <c r="B91" s="47"/>
+      <c r="A91" s="57"/>
+      <c r="B91" s="71"/>
       <c r="C91">
         <v>8</v>
       </c>
@@ -7460,8 +7402,8 @@
       </c>
     </row>
     <row r="92" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="53"/>
-      <c r="B92" s="47"/>
+      <c r="A92" s="57"/>
+      <c r="B92" s="71"/>
       <c r="C92">
         <v>9</v>
       </c>
@@ -7494,8 +7436,8 @@
       </c>
     </row>
     <row r="93" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="53"/>
-      <c r="B93" s="48"/>
+      <c r="A93" s="57"/>
+      <c r="B93" s="72"/>
       <c r="C93">
         <v>10</v>
       </c>
@@ -7527,8 +7469,8 @@
       </c>
     </row>
     <row r="94" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A94" s="53"/>
-      <c r="B94" s="46" t="s">
+      <c r="A94" s="57"/>
+      <c r="B94" s="70" t="s">
         <v>27</v>
       </c>
       <c r="C94">
@@ -7563,8 +7505,8 @@
       </c>
     </row>
     <row r="95" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A95" s="53"/>
-      <c r="B95" s="47"/>
+      <c r="A95" s="57"/>
+      <c r="B95" s="71"/>
       <c r="C95">
         <v>2</v>
       </c>
@@ -7597,8 +7539,8 @@
       </c>
     </row>
     <row r="96" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A96" s="53"/>
-      <c r="B96" s="47"/>
+      <c r="A96" s="57"/>
+      <c r="B96" s="71"/>
       <c r="C96">
         <v>3</v>
       </c>
@@ -7631,8 +7573,8 @@
       </c>
     </row>
     <row r="97" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A97" s="53"/>
-      <c r="B97" s="47"/>
+      <c r="A97" s="57"/>
+      <c r="B97" s="71"/>
       <c r="C97">
         <v>4</v>
       </c>
@@ -7665,8 +7607,8 @@
       </c>
     </row>
     <row r="98" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A98" s="53"/>
-      <c r="B98" s="47"/>
+      <c r="A98" s="57"/>
+      <c r="B98" s="71"/>
       <c r="C98">
         <v>5</v>
       </c>
@@ -7699,8 +7641,8 @@
       </c>
     </row>
     <row r="99" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A99" s="53"/>
-      <c r="B99" s="47"/>
+      <c r="A99" s="57"/>
+      <c r="B99" s="71"/>
       <c r="C99">
         <v>6</v>
       </c>
@@ -7733,8 +7675,8 @@
       </c>
     </row>
     <row r="100" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="53"/>
-      <c r="B100" s="47"/>
+      <c r="A100" s="57"/>
+      <c r="B100" s="71"/>
       <c r="C100">
         <v>7</v>
       </c>
@@ -7767,8 +7709,8 @@
       </c>
     </row>
     <row r="101" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="53"/>
-      <c r="B101" s="47"/>
+      <c r="A101" s="57"/>
+      <c r="B101" s="71"/>
       <c r="C101">
         <v>8</v>
       </c>
@@ -7796,13 +7738,13 @@
       <c r="P101">
         <v>284.09153300000003</v>
       </c>
-      <c r="R101" s="82">
+      <c r="R101" s="45">
         <v>50.481000000000002</v>
       </c>
     </row>
     <row r="102" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="53"/>
-      <c r="B102" s="47"/>
+      <c r="A102" s="57"/>
+      <c r="B102" s="71"/>
       <c r="C102">
         <v>9</v>
       </c>
@@ -7835,8 +7777,8 @@
       </c>
     </row>
     <row r="103" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="53"/>
-      <c r="B103" s="48"/>
+      <c r="A103" s="57"/>
+      <c r="B103" s="72"/>
       <c r="C103">
         <v>10</v>
       </c>
@@ -7868,7 +7810,7 @@
       </c>
     </row>
     <row r="104" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="53"/>
+      <c r="A104" s="57"/>
       <c r="F104" s="31"/>
       <c r="G104" s="31"/>
       <c r="H104" s="31"/>
@@ -7876,8 +7818,8 @@
       <c r="J104" s="31"/>
     </row>
     <row r="105" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A105" s="53"/>
-      <c r="B105" s="46" t="s">
+      <c r="A105" s="57"/>
+      <c r="B105" s="70" t="s">
         <v>33</v>
       </c>
       <c r="C105">
@@ -7907,13 +7849,13 @@
       <c r="P105">
         <v>491.76410010000001</v>
       </c>
-      <c r="R105" s="82">
+      <c r="R105" s="45">
         <v>51.8</v>
       </c>
     </row>
     <row r="106" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A106" s="53"/>
-      <c r="B106" s="47"/>
+      <c r="A106" s="57"/>
+      <c r="B106" s="71"/>
       <c r="C106">
         <v>2</v>
       </c>
@@ -7941,13 +7883,13 @@
       <c r="P106">
         <v>232.53405960000001</v>
       </c>
-      <c r="R106" s="82">
+      <c r="R106" s="45">
         <v>50.033000000000001</v>
       </c>
     </row>
     <row r="107" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A107" s="53"/>
-      <c r="B107" s="47"/>
+      <c r="A107" s="57"/>
+      <c r="B107" s="71"/>
       <c r="C107">
         <v>3</v>
       </c>
@@ -7980,8 +7922,8 @@
       </c>
     </row>
     <row r="108" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A108" s="53"/>
-      <c r="B108" s="47"/>
+      <c r="A108" s="57"/>
+      <c r="B108" s="71"/>
       <c r="C108">
         <v>4</v>
       </c>
@@ -7997,7 +7939,7 @@
         <v>971.69256729999995</v>
       </c>
       <c r="I108" s="33"/>
-      <c r="J108" s="89">
+      <c r="J108" s="49">
         <v>51.485999999999997</v>
       </c>
       <c r="L108" s="33" t="s">
@@ -8014,8 +7956,8 @@
       </c>
     </row>
     <row r="109" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A109" s="53"/>
-      <c r="B109" s="47"/>
+      <c r="A109" s="57"/>
+      <c r="B109" s="71"/>
       <c r="C109">
         <v>5</v>
       </c>
@@ -8048,8 +7990,8 @@
       </c>
     </row>
     <row r="110" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A110" s="53"/>
-      <c r="B110" s="47"/>
+      <c r="A110" s="57"/>
+      <c r="B110" s="71"/>
       <c r="C110">
         <v>6</v>
       </c>
@@ -8065,7 +8007,7 @@
         <v>145.6007726</v>
       </c>
       <c r="I110" s="33"/>
-      <c r="J110" s="89">
+      <c r="J110" s="49">
         <v>51.104999999999997</v>
       </c>
       <c r="L110" s="33" t="s">
@@ -8082,8 +8024,8 @@
       </c>
     </row>
     <row r="111" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="53"/>
-      <c r="B111" s="47"/>
+      <c r="A111" s="57"/>
+      <c r="B111" s="71"/>
       <c r="C111">
         <v>7</v>
       </c>
@@ -8116,8 +8058,8 @@
       </c>
     </row>
     <row r="112" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="53"/>
-      <c r="B112" s="47"/>
+      <c r="A112" s="57"/>
+      <c r="B112" s="71"/>
       <c r="C112">
         <v>8</v>
       </c>
@@ -8150,8 +8092,8 @@
       </c>
     </row>
     <row r="113" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="53"/>
-      <c r="B113" s="47"/>
+      <c r="A113" s="57"/>
+      <c r="B113" s="71"/>
       <c r="C113">
         <v>9</v>
       </c>
@@ -8167,7 +8109,7 @@
         <v>780.2396066</v>
       </c>
       <c r="I113" s="33"/>
-      <c r="J113" s="90">
+      <c r="J113" s="50">
         <v>251.42080000000001</v>
       </c>
       <c r="L113" s="33" t="s">
@@ -8184,8 +8126,8 @@
       </c>
     </row>
     <row r="114" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="53"/>
-      <c r="B114" s="48"/>
+      <c r="A114" s="57"/>
+      <c r="B114" s="72"/>
       <c r="C114">
         <v>10</v>
       </c>
@@ -8217,8 +8159,8 @@
       </c>
     </row>
     <row r="115" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A115" s="53"/>
-      <c r="B115" s="46" t="s">
+      <c r="A115" s="57"/>
+      <c r="B115" s="70" t="s">
         <v>42</v>
       </c>
       <c r="C115">
@@ -8236,7 +8178,7 @@
         <v>86.674660399999993</v>
       </c>
       <c r="I115" s="33"/>
-      <c r="J115" s="89">
+      <c r="J115" s="49">
         <v>52.41</v>
       </c>
       <c r="L115" s="33" t="s">
@@ -8248,13 +8190,13 @@
       <c r="P115">
         <v>174.2282764</v>
       </c>
-      <c r="R115" s="81">
+      <c r="R115" s="44">
         <v>52.584600000000002</v>
       </c>
     </row>
     <row r="116" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A116" s="53"/>
-      <c r="B116" s="47"/>
+      <c r="A116" s="57"/>
+      <c r="B116" s="71"/>
       <c r="C116">
         <v>2</v>
       </c>
@@ -8270,7 +8212,7 @@
         <v>166.6076999</v>
       </c>
       <c r="I116" s="33"/>
-      <c r="J116" s="89">
+      <c r="J116" s="49">
         <v>51.065199999999997</v>
       </c>
       <c r="L116" s="33" t="s">
@@ -8287,8 +8229,8 @@
       </c>
     </row>
     <row r="117" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A117" s="53"/>
-      <c r="B117" s="47"/>
+      <c r="A117" s="57"/>
+      <c r="B117" s="71"/>
       <c r="C117">
         <v>3</v>
       </c>
@@ -8304,7 +8246,7 @@
         <v>83.641438399999998</v>
       </c>
       <c r="I117" s="33"/>
-      <c r="J117" s="89">
+      <c r="J117" s="49">
         <v>51.0871</v>
       </c>
       <c r="L117" s="33" t="s">
@@ -8321,8 +8263,8 @@
       </c>
     </row>
     <row r="118" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A118" s="53"/>
-      <c r="B118" s="47"/>
+      <c r="A118" s="57"/>
+      <c r="B118" s="71"/>
       <c r="C118">
         <v>4</v>
       </c>
@@ -8338,7 +8280,7 @@
         <v>78.636828100000002</v>
       </c>
       <c r="I118" s="33"/>
-      <c r="J118" s="89">
+      <c r="J118" s="49">
         <v>50.910699999999999</v>
       </c>
       <c r="L118" s="33" t="s">
@@ -8355,8 +8297,8 @@
       </c>
     </row>
     <row r="119" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A119" s="53"/>
-      <c r="B119" s="47"/>
+      <c r="A119" s="57"/>
+      <c r="B119" s="71"/>
       <c r="C119">
         <v>5</v>
       </c>
@@ -8372,7 +8314,7 @@
         <v>78.712250999999995</v>
       </c>
       <c r="I119" s="33"/>
-      <c r="J119" s="89">
+      <c r="J119" s="49">
         <v>50.9011</v>
       </c>
       <c r="L119" s="33" t="s">
@@ -8389,8 +8331,8 @@
       </c>
     </row>
     <row r="120" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A120" s="53"/>
-      <c r="B120" s="47"/>
+      <c r="A120" s="57"/>
+      <c r="B120" s="71"/>
       <c r="C120">
         <v>6</v>
       </c>
@@ -8406,7 +8348,7 @@
         <v>396.00587339999998</v>
       </c>
       <c r="I120" s="33"/>
-      <c r="J120" s="89">
+      <c r="J120" s="49">
         <v>50.796599999999998</v>
       </c>
       <c r="L120" s="33" t="s">
@@ -8418,13 +8360,13 @@
       <c r="P120">
         <v>97.068762699999994</v>
       </c>
-      <c r="R120" s="82">
+      <c r="R120" s="45">
         <v>50.25</v>
       </c>
     </row>
     <row r="121" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="53"/>
-      <c r="B121" s="47"/>
+      <c r="A121" s="57"/>
+      <c r="B121" s="71"/>
       <c r="C121">
         <v>7</v>
       </c>
@@ -8440,7 +8382,7 @@
         <v>242.74594289999999</v>
       </c>
       <c r="I121" s="33"/>
-      <c r="J121" s="89">
+      <c r="J121" s="49">
         <v>51.620199999999997</v>
       </c>
       <c r="L121" s="33" t="s">
@@ -8457,8 +8399,8 @@
       </c>
     </row>
     <row r="122" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="53"/>
-      <c r="B122" s="47"/>
+      <c r="A122" s="57"/>
+      <c r="B122" s="71"/>
       <c r="C122">
         <v>8</v>
       </c>
@@ -8474,7 +8416,7 @@
         <v>78.237251799999996</v>
       </c>
       <c r="I122" s="33"/>
-      <c r="J122" s="89">
+      <c r="J122" s="49">
         <v>51.393599999999999</v>
       </c>
       <c r="L122" s="33" t="s">
@@ -8491,8 +8433,8 @@
       </c>
     </row>
     <row r="123" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="53"/>
-      <c r="B123" s="47"/>
+      <c r="A123" s="57"/>
+      <c r="B123" s="71"/>
       <c r="C123">
         <v>9</v>
       </c>
@@ -8508,7 +8450,7 @@
         <v>81.641992000000002</v>
       </c>
       <c r="I123" s="33"/>
-      <c r="J123" s="89">
+      <c r="J123" s="49">
         <v>51.420200000000001</v>
       </c>
       <c r="L123" s="33" t="s">
@@ -8525,8 +8467,8 @@
       </c>
     </row>
     <row r="124" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="53"/>
-      <c r="B124" s="48"/>
+      <c r="A124" s="57"/>
+      <c r="B124" s="72"/>
       <c r="C124">
         <v>10</v>
       </c>
@@ -8541,7 +8483,7 @@
         <v>78.717697200000003</v>
       </c>
       <c r="I124" s="31"/>
-      <c r="J124" s="91">
+      <c r="J124" s="51">
         <v>51.58</v>
       </c>
       <c r="L124" s="33" t="s">
@@ -8558,8 +8500,8 @@
       </c>
     </row>
     <row r="125" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A125" s="53"/>
-      <c r="B125" s="46" t="s">
+      <c r="A125" s="57"/>
+      <c r="B125" s="70" t="s">
         <v>48</v>
       </c>
       <c r="C125">
@@ -8577,7 +8519,7 @@
         <v>80.974393000000006</v>
       </c>
       <c r="I125" s="33"/>
-      <c r="J125" s="92">
+      <c r="J125" s="52">
         <v>52.299199999999999</v>
       </c>
       <c r="L125" s="33" t="s">
@@ -8594,8 +8536,8 @@
       </c>
     </row>
     <row r="126" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A126" s="53"/>
-      <c r="B126" s="47"/>
+      <c r="A126" s="57"/>
+      <c r="B126" s="71"/>
       <c r="C126">
         <v>2</v>
       </c>
@@ -8611,7 +8553,7 @@
         <v>87.044013899999996</v>
       </c>
       <c r="I126" s="33"/>
-      <c r="J126" s="92">
+      <c r="J126" s="52">
         <v>50.614699999999999</v>
       </c>
       <c r="L126" s="33" t="s">
@@ -8628,8 +8570,8 @@
       </c>
     </row>
     <row r="127" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A127" s="53"/>
-      <c r="B127" s="47"/>
+      <c r="A127" s="57"/>
+      <c r="B127" s="71"/>
       <c r="C127">
         <v>3</v>
       </c>
@@ -8645,7 +8587,7 @@
         <v>88.587937499999995</v>
       </c>
       <c r="I127" s="33"/>
-      <c r="J127" s="92">
+      <c r="J127" s="52">
         <v>50.531399999999998</v>
       </c>
       <c r="L127" s="33" t="s">
@@ -8662,8 +8604,8 @@
       </c>
     </row>
     <row r="128" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A128" s="53"/>
-      <c r="B128" s="47"/>
+      <c r="A128" s="57"/>
+      <c r="B128" s="71"/>
       <c r="C128">
         <v>4</v>
       </c>
@@ -8679,7 +8621,7 @@
         <v>83.735353000000003</v>
       </c>
       <c r="I128" s="33"/>
-      <c r="J128" s="92">
+      <c r="J128" s="52">
         <v>50.688400000000001</v>
       </c>
       <c r="L128" s="33" t="s">
@@ -8696,8 +8638,8 @@
       </c>
     </row>
     <row r="129" spans="1:20" ht="16" x14ac:dyDescent="0.2">
-      <c r="A129" s="53"/>
-      <c r="B129" s="47"/>
+      <c r="A129" s="57"/>
+      <c r="B129" s="71"/>
       <c r="C129">
         <v>5</v>
       </c>
@@ -8713,7 +8655,7 @@
         <v>78.882186200000007</v>
       </c>
       <c r="I129" s="33"/>
-      <c r="J129" s="92">
+      <c r="J129" s="52">
         <v>51.0458</v>
       </c>
       <c r="L129" s="33" t="s">
@@ -8730,8 +8672,8 @@
       </c>
     </row>
     <row r="130" spans="1:20" ht="16" x14ac:dyDescent="0.2">
-      <c r="A130" s="53"/>
-      <c r="B130" s="47"/>
+      <c r="A130" s="57"/>
+      <c r="B130" s="71"/>
       <c r="C130">
         <v>6</v>
       </c>
@@ -8747,7 +8689,7 @@
         <v>77.985264799999996</v>
       </c>
       <c r="I130" s="33"/>
-      <c r="J130" s="92">
+      <c r="J130" s="52">
         <v>51.209400000000002</v>
       </c>
       <c r="L130" s="33" t="s">
@@ -8764,8 +8706,8 @@
       </c>
     </row>
     <row r="131" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="53"/>
-      <c r="B131" s="47"/>
+      <c r="A131" s="57"/>
+      <c r="B131" s="71"/>
       <c r="C131">
         <v>7</v>
       </c>
@@ -8781,7 +8723,7 @@
         <v>81.148442500000002</v>
       </c>
       <c r="I131" s="33"/>
-      <c r="J131" s="92">
+      <c r="J131" s="52">
         <v>50.741500000000002</v>
       </c>
       <c r="L131" s="33" t="s">
@@ -8798,8 +8740,8 @@
       </c>
     </row>
     <row r="132" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="53"/>
-      <c r="B132" s="47"/>
+      <c r="A132" s="57"/>
+      <c r="B132" s="71"/>
       <c r="C132">
         <v>8</v>
       </c>
@@ -8815,7 +8757,7 @@
         <v>77.694044700000006</v>
       </c>
       <c r="I132" s="33"/>
-      <c r="J132" s="92">
+      <c r="J132" s="52">
         <v>50.7605</v>
       </c>
       <c r="L132" s="33" t="s">
@@ -8832,8 +8774,8 @@
       </c>
     </row>
     <row r="133" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="53"/>
-      <c r="B133" s="47"/>
+      <c r="A133" s="57"/>
+      <c r="B133" s="71"/>
       <c r="C133">
         <v>9</v>
       </c>
@@ -8849,7 +8791,7 @@
         <v>79.305596800000004</v>
       </c>
       <c r="I133" s="33"/>
-      <c r="J133" s="92">
+      <c r="J133" s="52">
         <v>50.810699999999997</v>
       </c>
       <c r="L133" s="33" t="s">
@@ -8866,8 +8808,8 @@
       </c>
     </row>
     <row r="134" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="53"/>
-      <c r="B134" s="48"/>
+      <c r="A134" s="57"/>
+      <c r="B134" s="72"/>
       <c r="C134">
         <v>10</v>
       </c>
@@ -8882,7 +8824,7 @@
         <v>79.388584199999997</v>
       </c>
       <c r="I134" s="31"/>
-      <c r="J134" s="92">
+      <c r="J134" s="52">
         <v>50.944000000000003</v>
       </c>
       <c r="L134" s="33" t="s">
@@ -8943,7 +8885,7 @@
       </c>
       <c r="Q136" s="31"/>
       <c r="R136" s="31">
-        <f t="shared" ref="Q136:R136" si="27">AVERAGE(R74:R134)</f>
+        <f t="shared" ref="R136" si="27">AVERAGE(R74:R134)</f>
         <v>54.376823333333355</v>
       </c>
       <c r="S136" s="31"/>
@@ -8990,7 +8932,7 @@
       </c>
       <c r="Q137" s="31"/>
       <c r="R137" s="31">
-        <f t="shared" ref="Q137:R137" si="31">MIN(R74:R134)</f>
+        <f t="shared" ref="R137" si="31">MIN(R74:R134)</f>
         <v>49.9163</v>
       </c>
       <c r="S137" s="31"/>
@@ -9037,7 +8979,7 @@
       </c>
       <c r="Q138" s="31"/>
       <c r="R138" s="31">
-        <f t="shared" ref="Q138:R138" si="35">MAX(R74:R134)</f>
+        <f t="shared" ref="R138" si="35">MAX(R74:R134)</f>
         <v>102.2818</v>
       </c>
       <c r="S138" s="31"/>
@@ -9084,7 +9026,7 @@
       </c>
       <c r="Q139" s="31"/>
       <c r="R139" s="31">
-        <f t="shared" ref="Q139:R139" si="39">STDEV(R74:R134)</f>
+        <f t="shared" ref="R139" si="39">STDEV(R74:R134)</f>
         <v>12.653955605550385</v>
       </c>
       <c r="S139" s="31"/>
@@ -9112,19 +9054,14 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="AL44:AO44"/>
-    <mergeCell ref="AL36:AO36"/>
-    <mergeCell ref="W65:AD65"/>
-    <mergeCell ref="W9:Z9"/>
-    <mergeCell ref="W36:Z36"/>
-    <mergeCell ref="AB36:AE36"/>
-    <mergeCell ref="D1:J2"/>
-    <mergeCell ref="L1:R2"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="AG36:AJ36"/>
-    <mergeCell ref="AB44:AE44"/>
-    <mergeCell ref="AG44:AJ44"/>
+    <mergeCell ref="B38:B47"/>
+    <mergeCell ref="B48:B57"/>
+    <mergeCell ref="B58:B67"/>
+    <mergeCell ref="A7:A67"/>
+    <mergeCell ref="W54:Z54"/>
+    <mergeCell ref="B27:B36"/>
+    <mergeCell ref="B7:B16"/>
+    <mergeCell ref="B17:B26"/>
     <mergeCell ref="A74:A134"/>
     <mergeCell ref="B74:B83"/>
     <mergeCell ref="B84:B93"/>
@@ -9132,21 +9069,26 @@
     <mergeCell ref="B115:B124"/>
     <mergeCell ref="B105:B114"/>
     <mergeCell ref="B94:B103"/>
-    <mergeCell ref="B38:B47"/>
-    <mergeCell ref="B48:B57"/>
-    <mergeCell ref="B58:B67"/>
-    <mergeCell ref="A7:A67"/>
-    <mergeCell ref="W54:Z54"/>
-    <mergeCell ref="AB54:AE54"/>
+    <mergeCell ref="D1:J2"/>
+    <mergeCell ref="L1:R2"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="AG36:AJ36"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="P3:P4"/>
-    <mergeCell ref="B27:B36"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="B7:B16"/>
-    <mergeCell ref="B17:B26"/>
+    <mergeCell ref="AL44:AO44"/>
+    <mergeCell ref="AL36:AO36"/>
+    <mergeCell ref="W65:AD65"/>
+    <mergeCell ref="W9:Z9"/>
+    <mergeCell ref="W36:Z36"/>
+    <mergeCell ref="AB36:AE36"/>
+    <mergeCell ref="AB44:AE44"/>
+    <mergeCell ref="AG44:AJ44"/>
+    <mergeCell ref="AB54:AE54"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9154,6 +9096,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001DB4A8D4FA53A74C8DD903E2AA11403B" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9513ce20363a6a392200d549223f9677">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e16ae15f-114f-47f3-812f-99bedbca4995" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="32ab30f1da6742da7917429fac681e44" ns2:_="">
     <xsd:import namespace="e16ae15f-114f-47f3-812f-99bedbca4995"/>
@@ -9297,22 +9254,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A47F65F-C790-4490-A4C6-39EA686EC5FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0857D451-F364-4B92-BA89-D9BE453D8776}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{535B239F-CB92-4DF0-9441-AC6CE80C8C29}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9328,21 +9287,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0857D451-F364-4B92-BA89-D9BE453D8776}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A47F65F-C790-4490-A4C6-39EA686EC5FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>